--- a/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.060170960951030736,33.55936901291673,-1860.0,1.0,1.0,4.0,-1.0],[33.55936901291673,34.67600894798226,-1187.2576,0.0,1.0,5.0,-1.0],[34.67600894798226,38.58424872071159,0.0,0.0,0.0,6.0,-1.0],[38.58424872071159,55.333847746694445,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,57.67476174696917,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06465534703439174,33.23411054699684,-1860.0,1.0,1.0,1.0,-1.0],[33.23411054699684,37.30755241365889,0.0,0.0,0.0,3.0,-1.0],[37.30755241365889,40.79907401365494,788.5,0.0,0.0,0.0,-1.0],[40.79907401365494,57.67476174696917,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,58.987782650693504,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06616840205486296,32.800398540187444,-1860.0,1.0,1.0,2.0,-1.0],[32.800398540187444,33.395566360880764,-1187.2576,0.0,1.0,1.0,-1.0],[33.395566360880764,36.96657328504068,0.0,0.0,0.0,2.0,-1.0],[36.96657328504068,37.561741105734,788.5,0.0,0.0,0.0,-1.0],[37.561741105734,58.987782650693504,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,57.9708129470626,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.0670736637155955,33.99047647618151,-1860.0,1.0,1.0,1.0,-1.0],[33.99047647618151,38.08468026389292,0.0,0.0,0.0,1.0,-1.0],[38.08468026389292,42.17888405160432,788.5,0.0,0.0,0.0,-1.0],[42.17888405160432,57.9708129470626,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,53.57247979561111,788.5,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06497865084935292,33.03424703297528,-1860.0,1.0,1.0,0.0,-1.0],[33.03424703297528,36.817605699776614,0.0,0.0,0.0,2.0,-1.0],[36.817605699776614,40.600964366577955,788.5,0.0,0.0,0.0,-1.0],[40.600964366577955,53.57247979561111,788.5001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[0.06779395822912662,19.75227599612784,-1860.0,8.0,0.0,0.0,1.0],[19.75227599612784,30.489266198618044,-733.6842,8.0,0.0,0.0,1.0],[30.489266198618044,34.068262932781444,0.0,8.0,8.0,1.0,-1.0],[34.068262932781444,36.454260755557044,227.85,8.0,8.0,0.0,-1.0],[36.454260755557044,59.12124007192525,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,7 +724,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[0.06653263779102629,20.630675151460323,-1860.0,6.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,6.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,6.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,6.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06653263779102629,20.630675151460323,-1860.0,5.0,0.0,0.0,1.0],[20.630675151460323,31.190640226047257,-733.6842,5.0,0.0,0.0,1.0],[31.190640226047257,34.52536603907471,0.0,5.0,8.0,1.0,-1.0],[34.52536603907471,36.192728945588435,227.85,5.0,8.0,0.0,-1.0],[36.192728945588435,55.08950855274401,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[[0.06338621875704924,20.490649315513156,-1860.0,5.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,5.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,5.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,5.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06338621875704924,20.490649315513156,-1860.0,4.0,0.0,0.0,1.0],[20.490649315513156,32.16337108508807,-733.6842,4.0,0.0,0.0,1.0],[32.16337108508807,35.66518761596055,0.0,4.0,8.0,1.0,-1.0],[35.66518761596055,36.83245979291804,227.85,4.0,8.0,0.0,-1.0],[36.83245979291804,57.84335897815289,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[[0.06528634851762935,20.146638897019525,-1860.0,4.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,4.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,4.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,4.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[0.06528634851762935,20.146638897019525,-1860.0,3.0,0.0,0.0,1.0],[20.146638897019525,30.47419163624907,-733.6842,3.0,0.0,0.0,1.0],[30.47419163624907,33.916709215992256,0.0,3.0,8.0,3.0,-1.0],[33.916709215992256,36.21172093582105,227.85,3.0,8.0,0.0,-1.0],[36.21172093582105,56.86682641428014,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -793,7 +793,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[[1.8166138653001007,30.920474953362262,-1860.0,4.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,3.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,3.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,3.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,3.0,7.0,0.0,-1.0]]</t>
+          <t>[[1.8166138653001007,30.920474953362262,-1860.0,3.0,8.0,0.0,-1.0],[30.920474953362262,32.01873386234574,-1607.5346,2.0,8.0,0.0,-1.0],[32.01873386234574,35.86264004378791,0.0,2.0,7.0,1.0,-1.0],[35.86264004378791,36.41176949827965,409.2,2.0,7.0,0.0,-1.0],[36.41176949827965,56.18042985998225,1860.0,2.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,2.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.7155904815176586,31.762469445016727,-1860.0,3.0,8.0,0.0,-1.0],[31.762469445016727,33.4632361787997,-1607.5346,2.0,8.0,0.0,-1.0],[33.4632361787997,36.86476964636562,0.0,1.0,7.0,1.0,-1.0],[36.86476964636562,37.43169189095995,409.2,2.0,7.0,1.0,-1.0],[37.43169189095995,57.840892696355546,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -839,7 +839,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[[1.9317174431021071,32.937582659746525,-1860.0,2.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[1.9317174431021071,32.937582659746525,-1860.0,1.0,8.0,0.0,-1.0],[32.937582659746525,36.32004068338047,0.0,1.0,7.0,1.0,-1.0],[36.32004068338047,36.88378368731946,409.2,1.0,7.0,1.0,-1.0],[36.88378368731946,57.74227483306207,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[[-1.9424211562153533,28.423180474808113,-733.6842,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-1.9424211562153533,28.423180474808113,-733.6843,0.0,0.0,0.0,1.0],[28.423180474808113,31.400200242555513,0.0,0.0,8.0,3.0,-1.0],[31.400200242555513,35.56802791740187,227.85,0.0,8.0,0.0,-1.0],[35.56802791740187,57.00257024518314,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[[-2.012018185287039,28.64544107970071,-733.6842,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-2.012018185287039,28.64544107970071,-733.6843,0.0,0.0,0.0,1.0],[28.64544107970071,31.94701361593016,0.0,0.0,8.0,2.0,-1.0],[31.94701361593016,32.41866683539151,227.85,0.0,8.0,1.0,-1.0],[32.41866683539151,44.68165054138661,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,1.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-1.8995333109743828,27.960678930205635,-1860.0,0.0,2.0,0.0,-1.0],[27.960678930205635,28.38725339079392,-1808.4765,0.0,2.0,1.0,-1.0],[28.38725339079392,31.37327461491192,0.0,0.0,1.0,2.0,-1.0],[31.37327461491192,32.2264235360885,227.85,0.0,1.0,1.0,-1.0],[32.2264235360885,40.33133828726593,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,37.487261692266024,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.908971127352784,25.94695106833728,-1860.0,1.0,1.0,0.0,-1.0],[25.94695106833728,27.936659796600857,-1808.4765,0.0,1.0,0.0,-1.0],[27.936659796600857,31.120193761822577,0.0,0.0,0.0,1.0,-1.0],[31.120193761822577,34.70166947269701,227.85,0.0,0.0,0.0,-1.0],[34.70166947269701,37.487261692266024,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[[-1.988261951986372,10.563100188026741,-1860.0,8.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,8.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,8.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-1.988261951986372,10.563100188026741,-1860.0,6.0,0.0,0.0,1.0],[10.563100188026741,28.377936773851808,-733.6842,7.0,0.0,0.0,1.0],[28.377936773851808,31.616997971274543,0.0,6.0,8.0,4.0,-1.0],[31.616997971274543,38.09512036612002,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,8.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,7.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
+          <t>[[-2.1054115346025535,28.216056015357637,-1860.0,7.0,0.0,0.0,1.0],[28.216056015357637,31.163976471603767,0.0,6.0,7.0,3.0,-1.0],[31.163976471603767,31.585107965353217,1071.35,7.0,7.0,0.0,-1.0],[31.585107965353217,39.58660634659271,1860.0,7.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,7.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,6.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.0111242358530035,28.172706093507696,-1860.0,6.0,0.0,0.0,1.0],[28.172706093507696,31.34995139133514,0.0,5.0,7.0,4.0,-1.0],[31.34995139133514,37.30728632476159,1860.0,6.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[[-2.018065211083488,27.27166340726742,-1860.0,6.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,5.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,5.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-2.018065211083488,27.27166340726742,-1860.0,5.0,0.0,0.0,1.0],[27.27166340726742,28.45908483774111,-873.8504,4.0,8.0,3.0,-1.0],[28.45908483774111,31.625541985670935,0.0,4.0,7.0,4.0,-1.0],[31.625541985670935,32.41715627265339,1071.35,5.0,7.0,4.0,-1.0],[32.41715627265339,37.166841994548136,1860.0,4.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,5.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,4.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,4.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,4.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,4.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.0098448650053102,28.070507245416543,-1860.0,4.0,0.0,0.0,1.0],[28.070507245416543,28.906072581817153,-873.8504,3.0,8.0,3.0,-1.0],[28.906072581817153,31.830551259219273,0.0,3.0,7.0,4.0,-1.0],[31.830551259219273,32.24833392741957,1071.35,3.0,7.0,4.0,-1.0],[32.24833392741957,39.35063928682474,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,4.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,3.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,3.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,3.0,7.0,2.0,-1.0]]</t>
+          <t>[[-1.9825007850115588,27.619586495747388,-1860.0,3.0,0.0,0.0,1.0],[27.619586495747388,28.430602585631195,-873.8504,2.0,8.0,4.0,-1.0],[28.430602585631195,31.269158900224518,0.0,2.0,7.0,5.0,-1.0],[31.269158900224518,38.162795664236874,1860.0,2.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[[-2.012203340280024,27.527594329197264,-1860.0,2.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[-2.012203340280024,27.527594329197264,-1860.0,1.0,0.0,0.0,1.0],[27.527594329197264,28.348144264460522,-873.8504,1.0,8.0,3.0,-1.0],[28.348144264460522,31.630344005513557,0.0,1.0,7.0,4.0,-1.0],[31.630344005513557,38.60501845525125,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[[8.810626718004732,30.5894160099191,-0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[8.810626718004732,30.5894160099191,0.0,0.0,0.0,1.0,1.0],[30.5894160099191,31.460567581595676,890.0,0.0,8.0,3.0,-1.0],[31.460567581595676,37.558628583331696,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[[9.00210244527421,27.343315870579815,-1860.0,1.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
+          <t>[[9.00210244527421,27.343315870579815,-1860.0,0.0,8.0,1.0,-1.0],[27.343315870579815,27.93496791655742,-1074.7923,0.0,8.0,2.0,-1.0],[27.93496791655742,30.893228146445416,0.0,0.0,7.0,3.0,-1.0],[30.893228146445416,31.189054169434222,890.0,0.0,7.0,3.0,-1.0],[31.189054169434222,38.288878721165425,1860.0,0.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,-0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[9.000932317558064,27.535632913147765,-1860.0,1.0,6.0,1.0,-1.0],[27.535632913147765,30.855280781014578,0.0,0.0,5.0,3.0,-1.0],[30.855280781014578,36.38802722745927,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,-0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
+          <t>[[9.123094998532288,27.032695158751824,-1860.0,1.0,5.0,1.0,-1.0],[27.032695158751824,30.719965779973496,0.0,0.0,4.0,3.0,-1.0],[30.719965779973496,35.19736582002838,1860.0,0.0,4.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[[8.912042912743143,27.59932076443066,-1860.0,1.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,-0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[8.912042912743143,27.59932076443066,-1860.0,0.0,4.0,1.0,-1.0],[27.59932076443066,30.757733922462357,0.0,0.0,3.0,3.0,-1.0],[30.757733922462357,34.96895146650461,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,-0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.097615965395647,27.415981424534454,-1860.0,1.0,3.0,1.0,-1.0],[27.415981424534454,31.48672930434308,0.0,0.0,2.0,3.0,-1.0],[31.48672930434308,34.28536847171151,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>[[8.817587694406777,27.848276135806955,-1860.0,1.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,-0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.817587694406777,27.848276135806955,-1860.0,0.0,2.0,0.0,-1.0],[27.848276135806955,31.497997206760417,0.0,0.0,1.0,2.0,-1.0],[31.497997206760417,34.62632955329195,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>[[8.74419367151912,26.17242353912569,-1860.0,1.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,-0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[8.74419367151912,26.17242353912569,-1860.0,0.0,2.0,0.0,-1.0],[26.17242353912569,30.70853816220137,0.0,0.0,1.0,1.0,-1.0],[30.70853816220137,32.37973828649241,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>[[9.066043689600008,22.674963057544133,-1860.0,9.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.066043689600008,22.674963057544133,-1860.0,8.0,2.0,2.0,1.0],[22.674963057544133,23.567351212819155,-733.6842,9.0,2.0,2.0,1.0],[23.567351212819155,29.367874222106813,0.0,0.0,2.0,1.0,-1.0],[29.367874222106813,31.152650532656864,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.266816283516683,0.0,0.0,1.0,1.0,-1.0],[27.266816283516683,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.171067817334693,23.91575175274224,-1860.0,10.0,1.0,1.0,1.0],[23.91575175274224,24.585964658897126,-733.6842,9.0,1.0,2.0,1.0],[24.585964658897126,27.49022058556831,0.0,0.0,1.0,1.0,-1.0],[27.49022058556831,28.830646397878084,0.0,0.0,0.0,1.0,-1.0],[28.830646397878084,31.28809372044601,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,9.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.041946005126093,20.28750270023145,-1860.0,9.0,0.0,0.0,1.0],[20.28750270023145,22.756039535742385,-733.6842,8.0,0.0,1.0,1.0],[22.756039535742385,25.224576371253317,0.0,8.0,0.0,1.0,1.0],[25.224576371253317,27.69311320676425,1016.5,8.0,0.0,0.0,1.0],[27.69311320676425,36.19585119574635,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[[8.856569223926636,26.629476736272274,-1860.0,9.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,11.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.856569223926636,26.629476736272274,-1860.0,8.0,0.0,0.0,1.0],[26.629476736272274,26.894744012575934,-1275.7341,10.0,10.0,2.0,-1.0],[26.894744012575934,29.812684051916264,0.0,10.0,10.0,2.0,-1.0],[29.812684051916264,30.077951328219932,527.3,10.0,10.0,1.0,-1.0],[30.077951328219932,35.11802957798959,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,9.0,9.0,4.0,-1.0]]</t>
+          <t>[[8.883721641699175,26.023060795421237,-1860.0,8.0,0.0,0.0,1.0],[26.023060795421237,26.308716447983272,-1074.7923,8.0,9.0,5.0,-1.0],[26.308716447983272,28.879617321041582,0.0,8.0,9.0,5.0,-1.0],[28.879617321041582,37.16363124534058,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>[[-5.818061373212677,25.915850407123074,-1860.0,7.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,7.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
+          <t>[[-5.818061373212677,25.915850407123074,-1860.0,6.0,0.0,0.0,1.0],[25.915850407123074,28.917706926884563,0.0,6.0,9.0,5.0,-1.0],[28.917706926884563,29.346543572564777,708.65,8.0,9.0,4.0,-1.0],[29.346543572564777,36.636766549128396,1860.0,8.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>[[-6.662870971355539,26.731532219809445,-1860.0,6.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,6.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,6.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-6.662870971355539,26.731532219809445,-1860.0,4.0,0.0,0.0,1.0],[26.731532219809445,29.439186532606605,0.0,5.0,8.0,6.0,-1.0],[29.439186532606605,29.890462251406134,890.0,5.0,8.0,5.0,-1.0],[29.890462251406134,38.013425189797616,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>[[-6.50381465897646,26.412303512129107,-1860.0,5.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,5.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,5.0,8.0,5.0,-1.0]]</t>
+          <t>[[-6.50381465897646,26.412303512129107,-1860.0,4.0,0.0,0.0,1.0],[26.412303512129107,29.444051238415142,0.0,4.0,8.0,5.0,-1.0],[29.444051238415142,36.37376032706895,1860.0,4.0,8.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,4.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,4.0,9.0,5.0,-1.0]]</t>
+          <t>[[-7.334748459522696,25.94414888309117,-1860.0,4.0,0.0,0.0,1.0],[25.94414888309117,26.382029111283455,-1074.7923,4.0,9.0,5.0,-1.0],[26.382029111283455,29.009310480437183,0.0,3.0,8.0,6.0,-1.0],[29.009310480437183,30.32295116501405,890.0,4.0,8.0,6.0,-1.0],[30.32295116501405,36.015394131513794,1860.0,3.0,9.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>[[-7.005196674078064,25.867468543704604,-1860.0,3.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.005196674078064,25.867468543704604,-1860.0,2.0,0.0,0.0,1.0],[25.867468543704604,28.60685731185316,0.0,3.0,9.0,4.0,-1.0],[28.60685731185316,29.51998690123601,708.65,4.0,9.0,3.0,-1.0],[29.51998690123601,38.19471800037311,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>[[-7.267607775967381,27.574744159808855,-0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
+          <t>[[-7.267607775967381,27.574744159808855,0.0,0.0,0.0,1.0,1.0],[27.574744159808855,29.36153143856661,708.65,1.0,9.0,4.0,-1.0],[29.36153143856661,36.95537737328708,1860.0,1.0,10.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,2.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-7.3821907424165625,25.733054553881573,-1860.0,1.0,9.0,2.0,-1.0],[25.733054553881573,26.18668805109114,-1275.7341,1.0,9.0,2.0,-1.0],[26.18668805109114,28.908489034348513,0.0,1.0,9.0,2.0,-1.0],[28.908489034348513,37.52752548133022,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,2.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
+          <t>[[-6.608616881100971,26.200571197575094,-1860.0,2.0,7.0,1.0,-1.0],[26.200571197575094,26.713214761304407,-1476.6759,2.0,7.0,1.0,-1.0],[26.713214761304407,29.276432579950978,0.0,1.0,6.0,2.0,-1.0],[29.276432579950978,44.14309592810107,1860.0,2.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,1.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-6.98926725343526,25.153675226563507,-1860.0,2.0,6.0,1.0,-1.0],[25.153675226563507,25.65590870281349,-1275.7341,1.0,6.0,2.0,-1.0],[25.65590870281349,28.669309560313373,0.0,1.0,5.0,3.0,-1.0],[28.669309560313373,29.17154303656335,708.65,0.0,5.0,3.0,-1.0],[29.17154303656335,42.73184689531283,1860.0,0.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>[[-7.282536128271969,25.780529853585662,-1860.0,2.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,1.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,1.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[-7.282536128271969,25.780529853585662,-1860.0,1.0,5.0,1.0,-1.0],[25.780529853585662,28.880192289384816,0.0,0.0,4.0,3.0,-1.0],[28.880192289384816,29.39680269535134,708.65,0.0,4.0,2.0,-1.0],[29.39680269535134,43.86189406241405,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[[-6.931448681315284,26.766024967401567,-1860.0,9.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,1.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,1.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
+          <t>[[-6.931448681315284,26.766024967401567,-1860.0,8.0,12.0,2.0,0.0],[26.766024967401567,27.787160532514203,-1275.7341,0.0,5.0,1.0,-1.0],[27.787160532514203,30.8505672278521,0.0,0.0,4.0,2.0,-1.0],[30.8505672278521,43.614761791759996,1860.0,1.0,4.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>[[-7.031478070497841,25.3124637578032,-1860.0,8.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,9.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.031478070497841,25.3124637578032,-1860.0,7.0,1.0,1.0,1.0],[25.3124637578032,26.877493201108088,-1808.4765,8.0,1.0,1.0,1.0],[26.877493201108088,27.399169682209717,-1023.2687,9.0,10.0,4.0,0.0],[27.399169682209717,30.529228568819498,0.0,8.0,9.0,5.0,0.0],[30.529228568819498,44.6144935585635,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.95385357622328,27.934473498843133,-1860.0,8.0,0.0,1.0,1.0],[27.934473498843133,28.45519479847099,-1808.4765,8.0,0.0,1.0,1.0],[28.45519479847099,31.579522596238135,0.0,8.0,0.0,1.0,1.0],[31.579522596238135,32.100243895865994,46.5,9.0,0.0,0.0,1.0],[32.100243895865994,44.59755508693456,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-6.973173071348222,28.30589884125289,-1860.0,8.0,0.0,0.0,1.0],[28.30589884125289,29.35900546550964,-1023.2687,9.0,9.0,4.0,-1.0],[29.35900546550964,32.51832533827989,0.0,9.0,9.0,4.0,-1.0],[32.51832533827989,45.155604829360875,708.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>[[-7.080457594970696,27.59013405290203,-1860.0,7.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080457594970696,27.59013405290203,-1860.0,6.0,0.0,0.0,1.0],[27.59013405290203,29.600023423793203,-1808.4765,7.0,0.0,0.0,1.0],[29.600023423793203,30.102495766516,-1023.2687,8.0,9.0,4.0,-1.0],[30.102495766516,33.11732982285276,0.0,8.0,9.0,4.0,-1.0],[33.11732982285276,34.624746851021136,755.15,9.0,9.0,3.0,-1.0],[34.624746851021136,42.66430433458583,1860.0,9.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,6.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,8.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-7.080243864962062,27.00854689121286,-1860.0,6.0,0.0,0.0,1.0],[27.00854689121286,28.4694950664775,-1808.4765,5.0,0.0,0.0,1.0],[28.4694950664775,31.39139141700678,0.0,7.0,9.0,3.0,-1.0],[31.39139141700678,32.36535686718321,755.15,8.0,9.0,3.0,-1.0],[32.36535686718321,41.13104591877104,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>[[-2.266535582554761,27.53854110422391,-1860.0,5.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,5.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,6.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,6.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,6.0,9.0,4.0,-1.0]]</t>
+          <t>[[-2.266535582554761,27.53854110422391,-1860.0,4.0,0.0,0.0,1.0],[27.53854110422391,29.372699669564135,-1808.4765,4.0,0.0,0.0,1.0],[29.372699669564135,29.831239310899193,-1023.2687,5.0,9.0,4.0,-1.0],[29.831239310899193,33.041016800244584,0.0,5.0,8.0,5.0,-1.0],[33.041016800244584,43.128888909615824,1860.0,5.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>[[3.36619092463286,29.340287645617497,-1860.0,7.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,6.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,6.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,7.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,4.0,6.0,1.0,-1.0]]</t>
+          <t>[[3.36619092463286,29.340287645617497,-1860.0,6.0,9.0,2.0,-1.0],[29.340287645617497,29.72796073100533,-1023.2687,5.0,9.0,3.0,-1.0],[29.72796073100533,32.82934541410797,0.0,5.0,9.0,3.0,-1.0],[32.82934541410797,33.99236467027146,755.15,6.0,9.0,2.0,-1.0],[33.99236467027146,41.74582637802807,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[[6.098201703062192,29.545879098244402,-1860.0,5.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,5.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,5.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,6.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,3.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.098201703062192,29.545879098244402,-1860.0,4.0,9.0,3.0,-1.0],[29.545879098244402,30.30225578841157,-1023.2687,4.0,9.0,3.0,-1.0],[30.30225578841157,33.70595089416383,0.0,4.0,9.0,3.0,-1.0],[33.70595089416383,34.08413923924741,755.15,5.0,9.0,2.0,-1.0],[34.08413923924741,34.84051592941458,1299.2,2.0,6.0,1.0,-1.0],[34.84051592941458,43.538847866337015,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,5.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,5.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
+          <t>[[6.385288520844072,29.8579772501956,-1860.0,5.0,10.0,2.0,-1.0],[29.8579772501956,30.230559610978958,-1224.2105,4.0,10.0,2.0,-1.0],[30.230559610978958,33.58380085802918,0.0,4.0,10.0,2.0,-1.0],[33.58380085802918,34.70154794037925,1299.2,2.0,6.0,1.0,-1.0],[34.70154794037925,43.27094223839647,1860.0,2.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>[[6.398895967454417,29.52315472353404,-1860.0,4.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,3.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,3.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.398895967454417,29.52315472353404,-1860.0,3.0,9.0,3.0,-1.0],[29.52315472353404,30.574257394264933,-1023.2687,2.0,9.0,3.0,-1.0],[30.574257394264933,33.72756540645761,0.0,3.0,8.0,4.0,-1.0],[33.72756540645761,34.07793296336791,936.5,2.0,8.0,4.0,-1.0],[34.07793296336791,41.08528410157385,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[[6.71034681312255,28.479060754392393,-1808.4765,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
+          <t>[[6.71034681312255,28.479060754392393,-1808.4766,0.0,0.0,0.0,1.0],[28.479060754392393,28.848022007634256,-1023.2687,1.0,9.0,3.0,-1.0],[28.848022007634256,32.168673286811014,0.0,1.0,9.0,3.0,-1.0],[32.168673286811014,34.013479553020325,755.15,2.0,9.0,2.0,-1.0],[34.013479553020325,43.237510884066864,1860.0,2.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>[[6.187173382665312,28.758009927775554,-1808.4765,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.187173382665312,28.758009927775554,-1808.4766,0.0,0.0,0.0,1.0],[28.758009927775554,29.48610142923072,-822.3269,0.0,8.0,4.0,-1.0],[29.48610142923072,32.398467435051394,0.0,0.0,8.0,4.0,-1.0],[32.398467435051394,42.22770270469618,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,-0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
+          <t>[[6.094123538194833,29.680539472691198,-1860.0,9.0,11.0,3.0,0.0],[29.680539472691198,30.134124394508436,-1607.5346,9.0,11.0,3.0,0.0],[30.134124394508436,34.21638869086358,0.0,1.0,2.0,1.0,-1.0],[34.21638869086358,50.99903079810138,1860.0,1.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>[[6.05963658236621,26.560727622221183,-1860.0,9.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
+          <t>[[6.05963658236621,26.560727622221183,-1860.0,8.0,3.0,0.0,1.0],[26.560727622221183,28.51321248315975,-733.6842,8.0,3.0,1.0,1.0],[28.51321248315975,31.930060989802246,0.0,8.0,2.0,2.0,1.0],[31.930060989802246,32.90630342027153,1197.85,8.0,2.0,2.0,1.0],[32.90630342027153,54.38363689059579,1860.0,8.0,3.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>[[6.457575473822436,25.83903520552078,-1860.0,9.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,8.0,1.0,1.0,1.0]]</t>
+          <t>[[6.457575473822436,25.83903520552078,-1860.0,8.0,1.0,0.0,1.0],[25.83903520552078,27.879188861489027,-733.6842,8.0,1.0,1.0,1.0],[27.879188861489027,30.9394193454414,0.0,8.0,0.0,2.0,1.0],[30.9394193454414,31.95949617342552,1197.85,8.0,0.0,2.0,1.0],[31.95949617342552,56.951378459036555,1860.0,7.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>[[6.31652131096733,26.269679136685227,-1860.0,9.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,8.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.31652131096733,26.269679136685227,-1860.0,8.0,0.0,0.0,1.0],[26.269679136685227,28.702991066650824,-733.6842,8.0,0.0,1.0,1.0],[28.702991066650824,32.10962776860266,0.0,7.0,0.0,1.0,1.0],[32.10962776860266,39.40956355849945,1016.5,9.0,0.0,0.0,1.0],[39.40956355849945,54.49609752428615,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>[[6.186252771594396,29.884053141634652,-1860.0,8.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,8.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.186252771594396,29.884053141634652,-1860.0,7.0,0.0,0.0,1.0],[29.884053141634652,31.742704151049576,-733.6842,8.0,0.0,0.0,1.0],[31.742704151049576,34.99534341752569,0.0,7.0,0.0,1.0,1.0],[34.99534341752569,40.106633693416725,1016.5,9.0,0.0,0.0,1.0],[40.106633693416725,52.18786525461372,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[[6.042334770243211,30.736623411644523,-1860.0,7.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,7.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.042334770243211,30.736623411644523,-1860.0,6.0,0.0,0.0,1.0],[30.736623411644523,34.53574474109087,-733.6842,7.0,0.0,0.0,1.0],[34.53574474109087,37.85997590435644,0.0,6.0,0.0,1.0,1.0],[37.85997590435644,40.709316901441206,1016.5,8.0,0.0,0.0,1.0],[40.709316901441206,53.056461222141856,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,6.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.200485742445525,29.17403952937586,-1860.0,6.0,0.0,0.0,1.0],[29.17403952937586,31.618034613091854,-733.6842,5.0,0.0,0.0,1.0],[31.618034613091854,35.03962773029424,0.0,6.0,0.0,1.0,1.0],[35.03962773029424,39.92761789772622,1016.5,7.0,0.0,0.0,1.0],[39.92761789772622,41.394014947955824,1725.15,8.0,9.0,2.0,-1.0],[41.394014947955824,54.59158840002218,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>[[6.225850190061506,28.014124484041044,-1860.0,5.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,5.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,5.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,6.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[6.225850190061506,28.014124484041044,-1860.0,4.0,0.0,0.0,1.0],[28.014124484041044,33.58786907087302,-733.6842,4.0,0.0,0.0,1.0],[33.58786907087302,37.134797444311545,0.0,4.0,0.0,1.0,1.0],[37.134797444311545,39.668317711053355,1016.5,4.0,0.0,0.0,1.0],[39.668317711053355,56.389551471549275,1860.0,6.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>[[10.044765917111793,29.85788793471034,-1860.0,4.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,4.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,4.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,5.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[10.044765917111793,29.85788793471034,-1860.0,3.0,0.0,0.0,1.0],[29.85788793471034,33.0832798910636,-733.6842,3.0,0.0,0.0,1.0],[33.0832798910636,36.76944212689588,0.0,3.0,0.0,1.0,1.0],[36.76944212689588,40.45560436272817,1016.5,4.0,0.0,0.0,1.0],[40.45560436272817,55.661023585536356,1860.0,4.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,3.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,3.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,4.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,4.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.222657630748097,29.500499044187904,-1860.0,3.0,0.0,0.0,1.0],[29.500499044187904,31.70461224130092,-733.6842,2.0,0.0,0.0,1.0],[31.70461224130092,35.23119335668176,0.0,2.0,0.0,1.0,1.0],[35.23119335668176,40.08024239033041,1016.5,3.0,0.0,0.0,1.0],[40.08024239033041,52.864098933585936,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,2.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,3.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[9.953973035437304,23.008611728590267,-1860.0,2.0,0.0,0.0,1.0],[23.008611728590267,31.56165087238014,-733.6842,2.0,0.0,0.0,1.0],[31.56165087238014,35.16293051187061,0.0,1.0,0.0,1.0,1.0],[35.16293051187061,38.764210151361084,1016.5,2.0,0.0,0.0,1.0],[38.764210151361084,54.5198085741319,1860.0,2.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>[[9.73102477340215,32.031469719122335,-1860.0,2.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,-0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.73102477340215,32.031469719122335,-1860.0,1.0,0.0,0.0,1.0],[32.031469719122335,40.45608225417218,0.0,2.0,0.0,1.0,1.0],[40.45608225417218,58.79200365398655,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,-0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
+          <t>[[9.503965080018071,31.57908898205053,-1860.0,1.0,0.0,0.0,1.0],[31.57908898205053,40.77705727456405,0.0,1.0,0.0,1.0,1.0],[40.77705727456405,41.6968541038154,890.0,1.0,8.0,4.0,-1.0],[41.6968541038154,55.03390812796001,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>[[9.515455611933138,40.31012682184718,-0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[9.515455611933138,40.31012682184718,0.0,0.0,0.0,1.0,1.0],[40.31012682184718,55.707462426804184,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>[[9.58124836654681,39.921888996433026,-0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.58124836654681,39.921888996433026,0.0,0.0,0.0,1.0,1.0],[39.921888996433026,53.75365163652822,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>[[9.718753169976825,33.57171765706868,-1860.0,1.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[9.718753169976825,33.57171765706868,-1860.0,0.0,4.0,1.0,-1.0],[33.57171765706868,34.471829524506106,-1074.7923,0.0,4.0,2.0,-1.0],[34.471829524506106,38.07227699425582,0.0,0.0,3.0,3.0,-1.0],[38.07227699425582,38.972388861693254,890.0,0.0,3.0,3.0,-1.0],[38.972388861693254,54.27429060812954,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>[[9.23685406081708,22.48916018283284,-1860.0,9.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.23685406081708,22.48916018283284,-1860.0,8.0,1.0,0.0,1.0],[22.48916018283284,22.930903720233367,-733.6842,9.0,1.0,0.0,1.0],[22.930903720233367,31.765774468243873,0.0,0.0,1.0,1.0,-1.0],[31.765774468243873,52.96946426346909,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>[[9.519828571434266,20.530027531303,-1860.0,9.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[9.519828571434266,20.530027531303,-1860.0,8.0,0.0,0.0,1.0],[20.530027531303,21.753382971288413,-532.7423,8.0,0.0,1.0,1.0],[21.753382971288413,24.200093851259243,0.0,8.0,0.0,2.0,1.0],[24.200093851259243,25.42344929124466,1197.85,9.0,0.0,1.0,1.0],[25.42344929124466,49.89055809095296,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>[[9.52167137946254,22.842992102229722,-1860.0,9.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[9.52167137946254,22.842992102229722,-1860.0,7.0,0.0,0.0,1.0],[22.842992102229722,35.33173027982396,-733.6842,9.0,0.0,0.0,1.0],[35.33173027982396,50.73450736552351,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>[[9.796336877994353,22.046653992895312,-1860.0,8.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,8.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,8.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[9.796336877994353,22.046653992895312,-1860.0,6.0,0.0,0.0,1.0],[22.046653992895312,36.21108315699955,-733.6842,7.0,0.0,0.0,1.0],[36.21108315699955,40.039307255406094,0.0,6.0,8.0,3.0,-1.0],[40.039307255406094,47.695755452219196,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>[[9.584146004254329,23.43552812007446,-1860.0,7.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,8.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[9.584146004254329,23.43552812007446,-1860.0,6.0,0.0,0.0,1.0],[23.43552812007446,36.09964891168144,-733.6842,7.0,0.0,0.0,1.0],[36.09964891168144,40.057186659058615,0.0,7.0,9.0,1.0,-1.0],[40.057186659058615,40.452940433796336,46.5,8.0,9.0,1.0,-1.0],[40.452940433796336,40.848694208534056,227.85,7.0,8.0,0.0,-1.0],[40.848694208534056,48.76376970328842,1860.0,7.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>[[8.64397061757689,23.05043299389458,-1860.0,6.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,6.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,6.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,6.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.64397061757689,23.05043299389458,-1860.0,5.0,0.0,0.0,1.0],[23.05043299389458,36.25635683885246,-733.6842,5.0,0.0,0.0,1.0],[36.25635683885246,40.25815194338516,0.0,5.0,8.0,3.0,-1.0],[40.25815194338516,41.45869047474496,227.85,5.0,8.0,0.0,-1.0],[41.45869047474496,48.26174215245054,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>[[5.862221143019794,23.2250913812518,-1860.0,5.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,5.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,5.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,5.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.862221143019794,23.2250913812518,-1860.0,3.0,0.0,0.0,1.0],[23.2250913812518,34.95676046113829,-733.6842,4.0,0.0,0.0,1.0],[34.95676046113829,39.18016132989743,0.0,4.0,8.0,4.0,-1.0],[39.18016132989743,41.05722838267927,227.85,4.0,8.0,0.0,-1.0],[41.05722838267927,52.3196306993703,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>[[5.627116174204419,23.219334010162427,-1860.0,4.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,4.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,4.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,4.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.627116174204419,23.219334010162427,-1860.0,3.0,0.0,0.0,1.0],[23.219334010162427,35.256114634765275,-733.6842,3.0,0.0,0.0,1.0],[35.256114634765275,38.95973944233538,0.0,3.0,8.0,3.0,-1.0],[38.95973944233538,40.34859874517417,227.85,3.0,8.0,3.0,-1.0],[40.34859874517417,51.4594731678845,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,3.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,3.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,3.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.9884784494145846,22.881439909653615,-1860.0,3.0,0.0,0.0,1.0],[22.881439909653615,35.815177956468254,-733.6842,2.0,0.0,0.0,1.0],[35.815177956468254,39.79478966318045,0.0,2.0,8.0,1.0,-1.0],[39.79478966318045,41.78459551653655,227.85,2.0,8.0,0.0,-1.0],[41.78459551653655,51.236173319978015,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>[[1.8387703061257163,21.71229952226691,-1860.0,2.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.8387703061257163,21.71229952226691,-1860.0,1.0,0.0,0.0,1.0],[21.71229952226691,36.73862649056879,-733.6842,2.0,0.0,0.0,1.0],[36.73862649056879,41.101108513624176,0.0,2.0,8.0,3.0,-1.0],[41.101108513624176,49.82607255973494,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>[[-4.5925615795403685,36.02884467400938,-733.6842,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-4.5925615795403685,36.02884467400938,-733.6843,0.0,0.0,0.0,1.0],[36.02884467400938,39.97814805977116,0.0,0.0,9.0,2.0,-1.0],[39.97814805977116,41.1065204557031,46.5,1.0,9.0,1.0,-1.0],[41.1065204557031,41.670706653669065,227.85,0.0,8.0,0.0,-1.0],[41.670706653669065,51.26187201909054,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7922,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[-4.112252481348731,33.34138079507791,-1860.0,1.0,8.0,1.0,-1.0],[33.34138079507791,35.64621976593494,-1074.7921,0.0,8.0,1.0,-1.0],[35.64621976593494,39.103478222220474,0.0,0.0,7.0,2.0,-1.0],[39.103478222220474,39.67968796493473,890.0001,0.0,7.0,2.0,-1.0],[39.67968796493473,52.93251204736262,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7922,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-4.895667298450673,33.63212204143139,-1860.0,1.0,7.0,0.0,-1.0],[33.63212204143139,34.17476696171142,-1074.7921,0.0,7.0,1.0,-1.0],[34.17476696171142,37.97328140367162,0.0,0.0,6.0,2.0,-1.0],[37.97328140367162,40.14386108479174,890.0001,0.0,6.0,2.0,-1.0],[40.14386108479174,48.826179809272205,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7922,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-4.4881139493366,33.648967563900946,-1860.0,1.0,6.0,1.0,-1.0],[33.648967563900946,34.75439021645856,-1074.7921,0.0,6.0,1.0,-1.0],[34.75439021645856,38.62336950041019,0.0,0.0,5.0,2.0,-1.0],[38.62336950041019,50.23030735226509,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7922,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-4.548724307462819,33.33541867154124,-1860.0,1.0,5.0,1.0,-1.0],[33.33541867154124,35.00677792061495,-1074.7921,0.0,5.0,1.0,-1.0],[35.00677792061495,38.90661616845361,0.0,0.0,4.0,2.0,-1.0],[38.90661616845361,40.02085566783608,890.0001,0.0,4.0,0.0,-1.0],[40.02085566783608,50.60613091196957,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7922,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[-4.436531506642835,32.42116870133077,-1860.0,1.0,5.0,0.0,-1.0],[32.42116870133077,33.978536315752194,-1074.7921,0.0,5.0,0.0,-1.0],[33.978536315752194,37.612394082735506,0.0,0.0,4.0,1.0,-1.0],[37.612394082735506,38.13151662087598,890.0001,0.0,4.0,1.0,-1.0],[38.13151662087598,46.956599769264024,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7922,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-4.513958606228754,32.934685247909954,-1860.0,1.0,4.0,0.0,-1.0],[32.934685247909954,34.93194625346402,-1074.7921,0.0,4.0,1.0,-1.0],[34.93194625346402,38.427153013183634,0.0,0.0,3.0,2.0,-1.0],[38.427153013183634,38.92646826457215,890.0001,0.0,3.0,2.0,-1.0],[38.92646826457215,44.91825128123434,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-4.810640504202817,32.86100263542682,-1860.0,1.0,3.0,0.0,-1.0],[32.86100263542682,36.581658747982836,0.0,0.0,2.0,1.0,-1.0],[36.581658747982836,37.04674076205234,890.0001,0.0,2.0,1.0,-1.0],[37.04674076205234,41.23247888867785,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7922,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-4.701487278192305,32.52958542222231,-1860.0,1.0,2.0,0.0,-1.0],[32.52958542222231,33.56378188612272,-1074.7921,0.0,2.0,1.0,-1.0],[33.56378188612272,37.18346950977414,0.0,0.0,1.0,2.0,-1.0],[37.18346950977414,39.76896066952516,890.0001,0.0,1.0,1.0,-1.0],[39.76896066952516,46.49123768487779,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>[[-4.495298292173052,24.796358250910963,-1860.0,9.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,9.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-4.495298292173052,24.796358250910963,-1860.0,8.0,0.0,0.0,1.0],[24.796358250910963,35.718670860196525,0.0,7.0,0.0,1.0,1.0],[35.718670860196525,44.65510844961199,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,8.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,8.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[-4.3981422541550295,24.77468043619473,-1860.0,7.0,0.0,0.0,1.0],[24.77468043619473,35.714488945075885,0.0,6.0,0.0,1.0,1.0],[35.714488945075885,40.72856784497975,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>[[-4.571120265029684,25.75084319835525,-1860.0,7.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,7.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.571120265029684,25.75084319835525,-1860.0,6.0,0.0,0.0,1.0],[25.75084319835525,33.575866027615874,0.0,6.0,0.0,1.0,1.0],[33.575866027615874,43.84620849102045,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>[[-4.659987055350011,24.261434604896554,-1860.0,6.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,6.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[-4.659987055350011,24.261434604896554,-1860.0,5.0,0.0,0.0,1.0],[24.261434604896554,34.40930185410588,0.0,3.0,0.0,1.0,1.0],[34.40930185410588,45.57195582823613,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>[[-4.453921093408683,24.470777928877318,-1860.0,5.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,5.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,5.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.453921093408683,24.470777928877318,-1860.0,4.0,0.0,0.0,1.0],[24.470777928877318,33.95428580503667,0.0,3.0,0.0,1.0,1.0],[33.95428580503667,34.42846119884463,890.0,4.0,8.0,4.0,-1.0],[34.42846119884463,42.489442893580076,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,4.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-4.5062635054054745,24.70727374859897,-1860.0,4.0,0.0,0.0,1.0],[24.70727374859897,34.76439313112509,0.0,3.0,0.0,1.0,1.0],[34.76439313112509,35.243303577912044,890.0,4.0,8.0,4.0,-1.0],[35.243303577912044,42.90587072650338,1860.0,4.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>[[-2.618455385771295,32.04932766359303,-1860.0,2.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.618455385771295,32.04932766359303,-1860.0,1.0,0.0,0.0,1.0],[32.04932766359303,35.6049977199381,0.0,1.0,7.0,5.0,-1.0],[35.6049977199381,41.38296156149882,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>[[10.935025213554844,30.159331739625436,-1860.0,1.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[10.935025213554844,30.159331739625436,-1860.0,0.0,0.0,0.0,1.0],[30.159331739625436,30.490785300419756,-873.8504,0.0,8.0,3.0,-1.0],[30.490785300419756,33.80532090836296,0.0,0.0,7.0,4.0,-1.0],[33.80532090836296,35.462588712334565,1071.35,0.0,7.0,3.0,-1.0],[35.462588712334565,43.74892773219258,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,7.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[10.59862303866299,30.314017397786472,-1860.0,1.0,7.0,0.0,-1.0],[30.314017397786472,34.91427608158195,0.0,0.0,6.0,1.0,-1.0],[34.91427608158195,75.65942442377049,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[10.424821564384656,17.328288023122052,-1860.0,8.0,15.0,0.0,0.0],[17.328288023122052,34.97048008433985,0.0,0.0,7.0,1.0,-1.0],[34.97048008433985,86.36295261049602,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[10.295243394271406,18.528461346656314,-1860.0,9.0,13.0,1.0,0.0],[18.528461346656314,19.276935705964032,-1607.5346,8.0,13.0,2.0,0.0],[19.276935705964032,35.743371610733846,0.0,0.0,5.0,1.0,-1.0],[35.743371610733846,84.39420496573558,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[10.904807859266159,18.341452276730262,-1860.0,9.0,3.0,0.0,1.0],[18.341452276730262,19.994039925055617,-733.6842,9.0,3.0,0.0,1.0],[19.994039925055617,36.51991640830918,0.0,0.0,3.0,1.0,-1.0],[36.51991640830918,92.70789645137128,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>[[10.723096815150768,19.48061075300562,-1860.0,9.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[10.723096815150768,19.48061075300562,-1860.0,7.0,1.0,0.0,1.0],[19.48061075300562,20.2767483837197,-733.6842,9.0,1.0,0.0,1.0],[20.2767483837197,31.422675213716786,0.0,0.0,1.0,1.0,-1.0],[31.422675213716786,34.6072257365731,0.0,0.0,0.0,1.0,-1.0],[34.6072257365731,38.58791389014348,1860.0,0.0,0.0,0.0,-1.0],[38.58791389014348,89.54072225584446,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>[[10.704894523780043,21.105191622045012,-1860.0,8.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,8.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[10.704894523780043,21.105191622045012,-1860.0,6.0,0.0,0.0,1.0],[21.105191622045012,27.17203159603291,-733.6842,8.0,0.0,0.0,1.0],[27.17203159603291,30.638797295454566,0.0,7.0,0.0,1.0,1.0],[30.638797295454566,43.63916866828577,1016.5,9.0,0.0,0.0,1.0],[43.63916866828577,96.50734558446602,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>[[10.693688779388,22.063281640587462,-1860.0,7.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,7.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[10.693688779388,22.063281640587462,-1860.0,6.0,0.0,0.0,1.0],[22.063281640587462,26.123850519587265,-733.6842,7.0,0.0,0.0,1.0],[26.123850519587265,29.37230562278711,0.0,6.0,0.0,1.0,1.0],[29.37230562278711,48.05092246618622,1016.5,8.0,0.0,0.0,1.0],[48.05092246618622,91.09295258358418,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>[[12.598372861454413,27.390008247241827,-1860.0,7.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,7.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.598372861454413,27.390008247241827,-1860.0,6.0,0.0,0.0,1.0],[27.390008247241827,43.73865788416476,-733.6842,7.0,0.0,0.0,1.0],[43.73865788416476,49.18820776313907,0.0,6.0,0.0,1.0,1.0],[49.18820776313907,53.85925051654562,1016.5,8.0,0.0,0.0,1.0],[53.85925051654562,54.63775764211338,1725.15,9.0,9.0,1.0,-1.0],[54.63775764211338,89.67057829266251,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,6.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.37458633449267,26.413039824104207,-1860.0,6.0,0.0,0.0,1.0],[26.413039824104207,42.711106686118626,-733.6842,5.0,0.0,0.0,1.0],[42.711106686118626,46.78562340162223,0.0,6.0,0.0,1.0,1.0],[46.78562340162223,49.23033343092439,1016.5,7.0,0.0,0.0,1.0],[49.23033343092439,53.304850146427995,1725.15,8.0,9.0,1.0,-1.0],[53.304850146427995,94.05001730146405,1860.0,8.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>[[13.639933032358712,28.222331165931784,-1860.0,5.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,5.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,5.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,6.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.639933032358712,28.222331165931784,-1860.0,4.0,0.0,0.0,1.0],[28.222331165931784,41.18446284021896,-733.6842,4.0,0.0,0.0,1.0],[41.18446284021896,45.2351289884337,0.0,4.0,0.0,1.0,1.0],[45.2351289884337,50.095928366291396,1016.5,4.0,0.0,0.0,1.0],[50.095928366291396,93.84312276701061,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>[[13.491941837436226,26.200707349547443,-1860.0,4.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,4.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,4.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,5.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,6.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,6.0,10.0,0.0,-1.0]]</t>
+          <t>[[13.491941837436226,26.200707349547443,-1860.0,3.0,0.0,0.0,1.0],[26.200707349547443,41.152196187325345,-733.6842,3.0,0.0,0.0,1.0],[41.152196187325345,45.63764283865872,0.0,3.0,0.0,1.0,1.0],[45.63764283865872,52.36581281565877,1016.5,4.0,0.0,0.0,1.0],[52.36581281565877,53.11338725754767,1725.15,5.0,9.0,1.0,-1.0],[53.11338725754767,87.50181158443685,1860.0,5.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>[[16.84510233064838,26.604269294066462,-1860.0,3.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,3.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,3.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,4.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[16.84510233064838,26.604269294066462,-1860.0,2.0,0.0,0.0,1.0],[26.604269294066462,40.545936384663726,-733.6842,2.0,0.0,0.0,1.0],[40.545936384663726,44.72843651184291,0.0,2.0,0.0,1.0,1.0],[44.72843651184291,52.3963534116714,1016.5,3.0,0.0,0.0,1.0],[52.3963534116714,85.85635442910484,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,2.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,3.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,4.0,10.0,0.0,-1.0]]</t>
+          <t>[[16.875250434512846,27.82480811334132,-1860.0,2.0,0.0,0.0,1.0],[27.82480811334132,40.33858831771671,-733.6842,2.0,0.0,0.0,1.0],[40.33858831771671,45.031255894357486,0.0,1.0,0.0,1.0,1.0],[45.031255894357486,52.07025725931865,1016.5,2.0,0.0,0.0,1.0],[52.07025725931865,53.634479784865576,1725.15,4.0,9.0,1.0,-1.0],[53.634479784865576,94.30426544908562,1860.0,3.0,10.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,2.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,3.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[19.36322207426412,41.50920932146643,-1860.0,2.0,0.0,0.0,1.0],[41.50920932146643,46.091137717439324,-733.6842,2.0,0.0,0.0,1.0],[46.091137717439324,50.67306611341222,0.0,1.0,9.0,2.0,-1.0],[50.67306611341222,53.727685044060806,46.5,2.0,9.0,1.0,-1.0],[53.727685044060806,94.96504060781683,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,1.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[19.40057575206109,41.57412990346195,-1860.0,1.0,0.0,0.0,1.0],[41.57412990346195,46.58106148603635,-733.6842,0.0,0.0,0.0,1.0],[46.58106148603635,51.58799306861073,0.0,1.0,9.0,2.0,-1.0],[51.58799306861073,53.01854494934628,46.5,2.0,9.0,1.0,-1.0],[53.01854494934628,90.2128938484703,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>[[18.29585114683094,48.156297245432384,-733.6842,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[18.29585114683094,48.156297245432384,-733.6843,0.0,0.0,0.0,1.0],[48.156297245432384,53.38187531268764,0.0,0.0,9.0,2.0,-1.0],[53.38187531268764,54.874897617617705,46.5,1.0,9.0,1.0,-1.0],[54.874897617617705,92.20045524086952,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>[[18.349246050748278,50.16642770056577,-0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[18.349246050748278,50.16642770056577,0.0,0.0,0.0,1.0,1.0],[50.16642770056577,50.88954546533435,890.0,0.0,8.0,2.0,-1.0],[50.88954546533435,89.93790476283763,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7923,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[19.853463846891557,41.59585373794009,-1860.0,1.0,8.0,0.0,-1.0],[41.59585373794009,43.04534639734332,-1074.7922,0.0,8.0,1.0,-1.0],[43.04534639734332,48.11857070525465,0.0,0.0,7.0,2.0,-1.0],[48.11857070525465,51.01755602406112,890.0001,0.0,7.0,2.0,-1.0],[51.01755602406112,91.6033504873517,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7923,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
+          <t>[[19.172314516033506,40.32332084343475,-1860.0,1.0,7.0,0.0,-1.0],[40.32332084343475,44.69939111806949,-1074.7922,0.0,7.0,1.0,-1.0],[44.69939111806949,49.80480643847669,0.0,0.0,7.0,1.0,-1.0],[49.80480643847669,91.37747404750672,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7923,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[18.862835997170503,41.85503298893214,-1860.0,1.0,6.0,0.0,-1.0],[41.85503298893214,44.01055145690979,-1074.7922,0.0,6.0,1.0,-1.0],[44.01055145690979,48.321588392865095,0.0,0.0,5.0,2.0,-1.0],[48.321588392865095,51.91411917282785,890.0001,0.0,5.0,2.0,-1.0],[51.91411917282785,89.99494544043306,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7923,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[17.99694564525315,39.653137753570505,-1860.0,1.0,6.0,0.0,-1.0],[39.653137753570505,42.15192915068404,-1074.7922,0.0,6.0,0.0,-1.0],[42.15192915068404,46.31658147920661,0.0,0.0,5.0,1.0,-1.0],[46.31658147920661,48.815372876320154,890.0001,0.0,5.0,1.0,-1.0],[48.815372876320154,100.45706175,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7923,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[19.300369879741282,39.656269192465615,-1860.0,1.0,5.0,0.0,-1.0],[39.656269192465615,40.41019138923318,-1074.7922,0.0,5.0,0.0,-1.0],[40.41019138923318,44.93372456983859,0.0,0.0,4.0,1.0,-1.0],[44.93372456983859,47.949413356908856,890.0001,0.0,4.0,1.0,-1.0],[47.949413356908856,93.93866735973049,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4765,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7923,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[17.737711314380388,38.626436171860085,-1860.0,10.0,4.0,0.0,1.0],[38.626436171860085,41.13308315475765,-1808.4764,9.0,4.0,1.0,1.0],[41.13308315475765,41.96863214905684,-1074.7922,0.0,4.0,0.0,-1.0],[41.96863214905684,46.14637712055278,0.0,0.0,3.0,1.0,-1.0],[46.14637712055278,48.65302410345034,890.0001,0.0,3.0,1.0,-1.0],[48.65302410345034,100.45706175,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4765,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.85,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[18.924053915325917,41.16032877932794,-1860.0,10.0,3.0,0.0,1.0],[41.16032877932794,41.98389451503172,-1808.4764,9.0,3.0,1.0,1.0],[41.98389451503172,46.10172319355061,0.0,9.0,2.0,2.0,1.0],[46.10172319355061,46.92528892925439,227.8501,9.0,2.0,2.0,1.0],[46.92528892925439,51.04311760777328,890.0001,0.0,2.0,1.0,-1.0],[51.04311760777328,100.45706175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>[[19.64682174260916,33.52332760246415,-1860.0,9.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[19.64682174260916,33.52332760246415,-1860.0,8.0,2.0,0.0,1.0],[33.52332760246415,40.869713057681494,-733.6842,9.0,2.0,0.0,1.0],[40.869713057681494,44.951038310580024,0.0,9.0,1.0,1.0,1.0],[44.951038310580024,49.848628614058256,1197.85,9.0,1.0,1.0,1.0],[49.848628614058256,100.45706175,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>[[19.184450484062637,32.95838988285303,-1860.0,9.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[19.184450484062637,32.95838988285303,-1860.0,8.0,1.0,0.0,1.0],[32.95838988285303,39.440243717577914,-733.6842,9.0,1.0,0.0,1.0],[39.440243717577914,43.491402364280965,0.0,9.0,0.0,1.0,1.0],[43.491402364280965,48.35279274032463,1197.85,9.0,0.0,1.0,1.0],[48.35279274032463,99.39739168878312,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>[[19.314279809579716,45.89321687238527,-1860.0,9.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,8.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[19.314279809579716,45.89321687238527,-1860.0,8.0,0.0,0.0,1.0],[45.89321687238527,50.72575088380445,0.0,7.0,8.0,2.0,-1.0],[50.72575088380445,99.05109099799635,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8504,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
+          <t>[[17.7712642036819,43.66277656667039,-1860.0,8.0,0.0,0.0,1.0],[43.66277656667039,47.83882694779757,-873.8505,7.0,8.0,2.0,-1.0],[47.83882694779757,52.85008740515018,0.0,7.0,8.0,2.0,-1.0],[52.85008740515018,54.52050755760105,890.0,8.0,8.0,1.0,-1.0],[54.52050755760105,100.45706175,1860.0,8.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>[[13.316516355357539,44.9441072206282,-1860.0,7.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.316516355357539,44.9441072206282,-1860.0,6.0,0.0,0.0,1.0],[44.9441072206282,50.07290573932073,0.0,7.0,0.0,1.0,1.0],[50.07290573932073,56.056504011128695,890.0,7.0,8.0,1.0,-1.0],[56.056504011128695,97.94169191378442,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>[[15.387718341693397,47.453515135232266,-1860.0,6.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,6.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.387718341693397,47.453515135232266,-1860.0,5.0,0.0,0.0,1.0],[47.453515135232266,52.51653568158051,0.0,5.0,8.0,2.0,-1.0],[52.51653568158051,56.735719470204046,890.0,5.0,8.0,1.0,-1.0],[56.735719470204046,98.9275573564394,1860.0,6.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>[[13.557467447436517,43.40177256144821,-1860.0,5.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8504,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,4.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,5.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.557467447436517,43.40177256144821,-1860.0,4.0,0.0,0.0,1.0],[43.40177256144821,46.912867280743704,-873.8505,4.0,8.0,2.0,-1.0],[46.912867280743704,51.30173567986307,0.0,3.0,8.0,2.0,-1.0],[51.30173567986307,53.935056719334696,890.0,4.0,8.0,1.0,-1.0],[53.935056719334696,100.45706175,1860.0,5.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>[[14.205980775788843,43.31364776090793,-1860.0,4.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8504,3.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,3.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,4.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.205980775788843,43.31364776090793,-1860.0,3.0,0.0,0.0,1.0],[43.31364776090793,45.88197131841844,-873.8505,2.0,8.0,2.0,-1.0],[45.88197131841844,51.01861843343946,0.0,2.0,8.0,2.0,-1.0],[51.01861843343946,53.58694199094996,890.0,3.0,8.0,1.0,-1.0],[53.58694199094996,98.9606581736356,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>[[12.882699270253498,44.57615845506954,-1860.0,3.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8504,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,3.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[12.882699270253498,44.57615845506954,-1860.0,2.0,0.0,0.0,1.0],[44.57615845506954,47.21728005380421,-873.8505,2.0,8.0,2.0,-1.0],[47.21728005380421,52.49952325127355,0.0,2.0,8.0,2.0,-1.0],[52.49952325127355,55.14064485000822,890.0,2.0,8.0,1.0,-1.0],[55.14064485000822,100.03971202849762,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8504,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.562888205077785,43.40533164474804,-1860.0,2.0,0.0,0.0,1.0],[43.40533164474804,45.16076949414041,-873.8505,1.0,8.0,2.0,-1.0],[45.16076949414041,50.42708304231751,0.0,1.0,8.0,2.0,-1.0],[50.42708304231751,53.06023981640606,890.0,2.0,8.0,1.0,-1.0],[53.06023981640606,100.45706175,1860.0,2.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8504,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,1.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[14.45151079436823,46.03344240870201,-1860.0,1.0,0.0,0.0,1.0],[46.03344240870201,47.6956493357722,-873.8505,0.0,8.0,2.0,-1.0],[47.6956493357722,52.6822701169828,0.0,0.0,8.0,2.0,-1.0],[52.6822701169828,56.837787434658296,890.0,0.0,8.0,1.0,-1.0],[56.837787434658296,96.73075368434307,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>[[13.26656992515346,50.256475547815626,-0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[13.26656992515346,50.256475547815626,0.0,0.0,0.0,1.0,1.0],[50.256475547815626,55.54074777962451,890.0,0.0,8.0,1.0,-1.0],[55.54074777962451,100.45706175,1860.0,0.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>[[14.224997611241855,40.648856611974345,-0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[14.224997611241855,40.648856611974345,0.0,0.0,0.0,1.0,1.0],[40.648856611974345,63.663185419063936,890.0,0.0,8.0,0.0,-1.0],[63.663185419063936,98.61086990390369,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>[[13.0631040652436,35.13228529876794,-986.1496,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,-0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[13.0631040652436,35.13228529876794,-986.1497,0.0,0.0,0.0,1.0],[35.13228529876794,43.959957792177676,0.0,0.0,8.0,1.0,-1.0],[43.959957792177676,100.45706175,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,-0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[14.093150567174522,35.902219047686,-1860.0,1.0,7.0,0.0,-1.0],[35.902219047686,42.00875822222922,0.0,0.0,6.0,1.0,-1.0],[42.00875822222922,100.45706175,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,-0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.075358982535585,35.70465964650596,-1860.0,1.0,6.0,0.0,-1.0],[35.70465964650596,42.359829081573764,0.0,0.0,6.0,1.0,-1.0],[42.359829081573764,96.4330807414997,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,-0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[13.597342608971536,34.783539008924585,-1860.0,1.0,5.0,1.0,-1.0],[34.783539008924585,41.56312185690956,0.0,0.0,5.0,1.0,-1.0],[41.56312185690956,97.4946803527856,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,-0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[13.838907630315594,36.11296720663019,-1860.0,1.0,2.0,0.0,-1.0],[36.11296720663019,42.37754646246867,0.0,0.0,2.0,1.0,-1.0],[42.37754646246867,82.74927944453887,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,39.93460205941696,-0.0,0.0,1.0,1.0,-1.0],[39.93460205941696,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[13.812296661655028,35.755033195775056,-1860.0,1.0,1.0,0.0,-1.0],[35.755033195775056,40.97949427532744,0.0,0.0,1.0,1.0,-1.0],[40.97949427532744,42.54683259919316,0.0,0.0,0.0,1.0,-1.0],[42.54683259919316,47.2488475707903,1860.0,0.0,0.0,0.0,-1.0],[47.2488475707903,65.53446134922366,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.690500721491528,35.55788734116837,-1860.0,1.0,0.0,0.0,-1.0],[35.55788734116837,62.89212061576441,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.361370108220429,33.697687838089095,-1860.0,1.0,0.0,0.0,-1.0],[33.697687838089095,64.98433049942551,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[14.156169684915382,34.07776706863876,-1860.0,1.0,0.0,0.0,-1.0],[34.07776706863876,64.72637842821318,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[13.359833766607641,29.07844754588593,-1860.0,1.0,0.0,0.0,-1.0],[29.07844754588593,61.989295146249844,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>[[14.32771698013276,29.117100575966113,-1860.0,8.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6842,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[14.32771698013276,29.117100575966113,-1860.0,7.0,0.0,0.0,1.0],[29.117100575966113,35.79617703860053,-733.6843,8.0,0.0,0.0,1.0],[35.79617703860053,39.61279216010591,0.0,8.0,8.0,3.0,-1.0],[39.61279216010591,40.089869050294084,227.85,8.0,8.0,1.0,-1.0],[40.089869050294084,61.55832910876185,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>[[12.357863091369897,33.57936852334953,-1860.0,8.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5346,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.357863091369897,33.57936852334953,-1860.0,7.0,8.0,2.0,-1.0],[33.57936852334953,36.23205670234698,-1607.5347,7.0,8.0,1.0,-1.0],[36.23205670234698,39.94582015294341,0.0,7.0,8.0,1.0,-1.0],[39.94582015294341,43.12904596774036,227.85,8.0,8.0,0.0,-1.0],[43.12904596774036,64.88108903551948,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5346,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,7.0,8.0,0.0,-1.0]]</t>
+          <t>[[11.21110265021379,35.24802977673849,-1860.0,7.0,8.0,1.0,-1.0],[35.24802977673849,35.77057167079338,-1607.5347,6.0,8.0,1.0,-1.0],[35.77057167079338,39.42836492917757,0.0,6.0,8.0,1.0,-1.0],[39.42836492917757,43.60870008161665,227.85,7.0,8.0,0.0,-1.0],[43.60870008161665,62.94275016164738,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5346,5.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,6.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,6.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.484482162591622,35.29868984702014,-1860.0,6.0,8.0,1.0,-1.0],[35.29868984702014,36.94037603178107,-1607.5347,4.0,8.0,1.0,-1.0],[36.94037603178107,41.31820585781023,0.0,5.0,8.0,1.0,-1.0],[41.31820585781023,45.14880695558573,227.85,5.0,8.0,0.0,-1.0],[45.14880695558573,62.66012625970232,1860.0,5.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>[[8.176251301373576,36.24799841734511,-1860.0,5.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,5.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,5.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,5.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.176251301373576,36.24799841734511,-1860.0,4.0,0.0,0.0,1.0],[36.24799841734511,40.178043013581124,0.0,4.0,8.0,1.0,-1.0],[40.178043013581124,41.86234784053942,227.85,4.0,8.0,0.0,-1.0],[41.86234784053942,63.75831059099721,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>[[8.200410679129284,36.11397131683742,-1860.0,4.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5346,3.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,3.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,4.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.200410679129284,36.11397131683742,-1860.0,3.0,8.0,1.0,-1.0],[36.11397131683742,36.68363581964779,-1607.5347,2.0,8.0,1.0,-1.0],[36.68363581964779,40.67128733932038,0.0,2.0,8.0,1.0,-1.0],[40.67128733932038,41.81061634494112,227.85,3.0,8.0,0.0,-1.0],[41.81061634494112,64.59719645735592,1860.0,3.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>[[8.911479795307043,35.554552601145645,-1860.0,3.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6842,3.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,3.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,3.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,3.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.911479795307043,35.554552601145645,-1860.0,2.0,0.0,0.0,1.0],[35.554552601145645,37.72949731998961,-733.6843,2.0,0.0,0.0,1.0],[37.72949731998961,42.07938675767755,0.0,2.0,8.0,1.0,-1.0],[42.07938675767755,42.623122937388544,227.85,2.0,8.0,0.0,-1.0],[42.623122937388544,62.74136158669524,1860.0,2.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5346,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.590642544444625,36.4489796238833,-1860.0,2.0,8.0,3.0,-1.0],[36.4489796238833,37.56331310706084,-1607.5347,1.0,8.0,1.0,-1.0],[37.56331310706084,42.020647039771035,0.0,1.0,8.0,1.0,-1.0],[42.020647039771035,43.692147264537354,227.85,2.0,8.0,0.0,-1.0],[43.692147264537354,63.75014996173319,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6842,1.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,1.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[7.726651746095345,35.40296443649466,-1860.0,1.0,0.0,0.0,1.0],[35.40296443649466,37.03098283004757,-733.6843,0.0,0.0,0.0,1.0],[37.03098283004757,41.3723652128553,0.0,1.0,8.0,3.0,-1.0],[41.3723652128553,44.08572920211014,227.85,0.0,8.0,0.0,-1.0],[44.08572920211014,61.451258733341085,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>[[8.359104983231369,36.184511379983604,-733.6842,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.359104983231369,36.184511379983604,-733.6844,0.0,0.0,0.0,1.0],[36.184511379983604,40.08006827552892,0.0,0.0,8.0,1.0,-1.0],[40.08006827552892,43.41911704313919,227.85,0.0,8.0,0.0,-1.0],[43.41911704313919,63.45340964880081,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>[[8.39296009039569,35.209335418135765,-733.6842,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.39296009039569,35.209335418135765,-733.6844,0.0,0.0,0.0,1.0],[35.209335418135765,39.04024617924149,0.0,0.0,8.0,2.0,-1.0],[39.04024617924149,42.323883974474974,227.85,0.0,8.0,0.0,-1.0],[42.323883974474974,62.572983711748094,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>[[8.381231291361221,34.28626217253296,-1860.0,1.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.381231291361221,34.28626217253296,-1860.0,0.0,2.0,0.0,-1.0],[34.28626217253296,36.67749579233343,-1808.4765,0.0,2.0,1.0,-1.0],[36.67749579233343,40.66288515866755,0.0,0.0,1.0,2.0,-1.0],[40.66288515866755,47.83658601806895,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,44.482917673305835,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.15703010922491,34.94278558576943,-1860.0,1.0,1.0,1.0,-1.0],[34.94278558576943,36.043570057408246,-1808.4765,0.0,1.0,1.0,-1.0],[36.043570057408246,39.71285162953763,0.0,0.0,0.0,2.0,-1.0],[39.71285162953763,42.2813487300282,227.85,0.0,0.0,0.0,-1.0],[42.2813487300282,44.482917673305835,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.214199054710384,35.800383175827015,-1860.0,1.0,0.0,0.0,-1.0],[35.800383175827015,44.148833633533364,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.231776226073956,33.37978573773485,-1860.0,1.0,0.0,0.0,-1.0],[33.37978573773485,45.39077535524453,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.484932719365416,27.172711165237473,-1860.0,1.0,0.0,0.0,-1.0],[27.172711165237473,46.241872844698754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>[[8.444957811119819,24.641902689125708,-1860.0,8.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6842,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,8.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.444957811119819,24.641902689125708,-1860.0,7.0,0.0,0.0,1.0],[24.641902689125708,30.81216740455652,-733.6843,8.0,0.0,0.0,1.0],[30.81216740455652,33.89729976227193,0.0,7.0,0.0,1.0,1.0],[33.89729976227193,36.21114903055849,1016.5,9.0,0.0,0.0,1.0],[36.21114903055849,46.62347073784799,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>[[8.456687325990359,25.67480672719658,-1860.0,7.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6842,7.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,7.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,8.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[8.456687325990359,25.67480672719658,-1860.0,6.0,0.0,0.0,1.0],[25.67480672719658,30.07092231899391,-733.6843,6.0,0.0,0.0,1.0],[30.07092231899391,33.36800901284191,0.0,6.0,0.0,1.0,1.0],[33.36800901284191,35.56606680874057,1016.5,7.0,0.0,0.0,1.0],[35.56606680874057,44.72464095831835,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6842,6.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
+          <t>[[8.16146712689788,25.243628411246725,-1860.0,6.0,0.0,0.0,1.0],[25.243628411246725,27.471736404857445,-733.6843,5.0,0.0,0.0,1.0],[27.471736404857445,30.442547063005065,0.0,6.0,0.0,1.0,1.0],[30.442547063005065,36.01281704703187,1016.5,7.0,0.0,0.0,1.0],[36.01281704703187,44.92524902147474,1860.0,7.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>[[8.595806879666561,24.820478435008496,-1860.0,5.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6842,5.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,5.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,6.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,6.0,9.0,3.0,-1.0]]</t>
+          <t>[[8.595806879666561,24.820478435008496,-1860.0,4.0,0.0,0.0,1.0],[24.820478435008496,27.642160444633184,-733.6843,4.0,0.0,0.0,1.0],[27.642160444633184,30.46384245425787,0.0,4.0,0.0,1.0,1.0],[30.46384245425787,36.459916724710325,1016.5,4.0,0.0,0.0,1.0],[36.459916724710325,43.514121748772034,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>[[12.76980788055936,25.119448349497155,-1860.0,4.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6842,4.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,4.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,5.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.76980788055936,25.119448349497155,-1860.0,3.0,0.0,0.0,1.0],[25.119448349497155,29.579040741058023,-733.6843,3.0,0.0,0.0,1.0],[29.579040741058023,32.66645085829247,0.0,3.0,0.0,1.0,1.0],[32.66645085829247,36.78299768127174,1016.5,4.0,0.0,0.0,1.0],[36.78299768127174,46.73131917013829,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>[[15.99501225267529,24.866380518087936,-1860.0,3.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6842,3.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,3.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,4.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,4.0,9.0,4.0,-1.0]]</t>
+          <t>[[15.99501225267529,24.866380518087936,-1860.0,2.0,0.0,0.0,1.0],[24.866380518087936,27.925473023402642,-733.6843,2.0,0.0,0.0,1.0],[27.925473023402642,30.984565528717347,0.0,2.0,0.0,1.0,1.0],[30.984565528717347,34.65547653509499,1016.5,3.0,0.0,0.0,1.0],[34.65547653509499,46.28002805529087,1860.0,3.0,9.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6842,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,2.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,3.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.45241967339454,25.600846042245905,-1860.0,2.0,0.0,0.0,1.0],[25.600846042245905,28.500396433346296,-733.6843,2.0,0.0,0.0,1.0],[28.500396433346296,31.399946824446687,0.0,1.0,0.0,1.0,1.0],[31.399946824446687,36.039227450207306,1016.5,2.0,0.0,0.0,1.0],[36.039227450207306,44.1579685452884,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6842,1.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.99518482713048,25.395510763969092,-1860.0,1.0,0.0,0.0,1.0],[25.395510763969092,28.33311261923116,-733.6843,0.0,0.0,0.0,1.0],[28.33311261923116,31.564474660019435,0.0,1.0,0.0,1.0,1.0],[31.564474660019435,36.26463762843874,1016.5,2.0,0.0,0.0,1.0],[36.26463762843874,45.07744319422494,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>[[15.336249492833469,28.71106901098448,-733.6842,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.336249492833469,25.975310473180862,-733.6844,0.0,0.0,0.0,1.0],[25.975310473180862,28.71106901098448,-733.6843,0.0,0.0,0.0,1.0],[28.71106901098448,31.750800719655167,0.0,0.0,0.0,1.0,1.0],[31.750800719655167,36.00642511179412,1016.5,1.0,0.0,0.0,1.0],[36.00642511179412,45.42959340867324,1860.0,0.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>[[16.06438042500798,36.96599093567612,-0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.06438042500798,36.96599093567612,0.0,0.0,0.0,1.0,1.0],[36.96599093567612,37.25629108165762,890.0,0.0,8.0,3.0,-1.0],[37.25629108165762,44.804094877176674,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>[[15.719847462416912,35.42905634531299,-0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.719847462416912,35.42905634531299,0.0,0.0,0.0,1.0,1.0],[35.42905634531299,36.555296852907055,890.0,0.0,8.0,2.0,-1.0],[36.555296852907055,43.59430002536994,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7923,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[15.467816108780807,31.68783998259861,-1860.0,1.0,8.0,2.0,-1.0],[31.68783998259861,32.27765903255562,-1074.7921,0.0,8.0,1.0,-1.0],[32.27765903255562,35.816573332297686,0.0,0.0,7.0,2.0,-1.0],[35.816573332297686,36.7013019072332,890.0001,0.0,7.0,0.0,-1.0],[36.7013019072332,44.66385908165285,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[15.052156947622725,31.152124706297208,-1860.0,1.0,7.0,1.0,-1.0],[31.152124706297208,34.431747768249416,0.0,0.0,6.0,1.0,-1.0],[34.431747768249416,35.326190421509104,890.0001,0.0,6.0,0.0,-1.0],[35.326190421509104,44.568764505192604,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7923,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.640541201465409,30.235122709197704,-1860.0,1.0,7.0,1.0,-1.0],[30.235122709197704,30.515787738192554,-1074.7921,0.0,7.0,0.0,-1.0],[30.515787738192554,33.603103057135925,0.0,0.0,6.0,1.0,-1.0],[33.603103057135925,35.28709323110503,890.0001,0.0,6.0,1.0,-1.0],[35.28709323110503,43.426379071955736,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7923,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[14.901878560461185,30.476758797770316,-1860.0,1.0,7.0,0.0,-1.0],[30.476758797770316,30.776275725410876,-1074.7921,0.0,7.0,0.0,-1.0],[30.776275725410876,34.07096192945704,0.0,0.0,6.0,1.0,-1.0],[34.07096192945704,34.370478857097595,890.0001,0.0,6.0,0.0,-1.0],[34.370478857097595,44.554054396876644,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7923,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[15.912450500068951,30.96146709076174,-1860.0,1.0,6.0,0.0,-1.0],[30.96146709076174,31.2081722807731,-1074.7921,0.0,6.0,1.0,-1.0],[31.2081722807731,34.41533975092074,0.0,0.0,5.0,2.0,-1.0],[34.41533975092074,35.40216051096617,890.0001,0.0,5.0,0.0,-1.0],[35.40216051096617,40.33626431119331,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7923,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[16.135123603165802,20.210664734416042,-1860.0,9.0,13.0,1.0,0.0],[20.210664734416042,30.17309861080552,-1074.7921,0.0,6.0,0.0,-1.0],[30.17309861080552,33.56938288684739,0.0,0.0,5.0,1.0,-1.0],[33.56938288684739,34.022220790319636,890.0001,0.0,5.0,1.0,-1.0],[34.022220790319636,38.55059982504213,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4765,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7923,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[15.675729073966822,20.3956468169795,-1860.0,9.0,5.0,0.0,1.0],[20.3956468169795,21.74419474355455,-1808.4763,9.0,5.0,0.0,1.0],[21.74419474355455,30.284998278529876,-1074.7921,0.0,5.0,0.0,-1.0],[30.284998278529876,33.656368094967505,0.0,0.0,4.0,1.0,-1.0],[33.656368094967505,34.78015803378005,890.0001,0.0,4.0,1.0,-1.0],[34.78015803378005,37.92676986245517,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4765,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7923,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[15.870474893686131,21.02302767466669,-1860.0,9.0,4.0,0.0,1.0],[21.02302767466669,21.435231897145133,-1808.4763,9.0,4.0,0.0,1.0],[21.435231897145133,29.26711212423558,-1074.7921,0.0,4.0,0.0,-1.0],[29.26711212423558,32.56474590406314,0.0,0.0,3.0,1.0,-1.0],[32.56474590406314,35.03797123893381,890.0001,0.0,3.0,1.0,-1.0],[35.03797123893381,36.27458390636914,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[15.724542238620721,19.698849272077297,-1860.0,9.0,3.0,0.0,1.0],[19.698849272077297,20.535545489647102,-733.6842,9.0,3.0,0.0,1.0],[20.535545489647102,33.922684970763996,0.0,0.0,3.0,1.0,-1.0],[33.922684970763996,36.43277362347341,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>[[15.360268596773755,20.37500219047014,-1860.0,9.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[15.360268596773755,20.37500219047014,-1860.0,8.0,2.0,0.0,1.0],[20.37500219047014,20.976770221713707,-733.6842,9.0,2.0,0.0,1.0],[20.976770221713707,32.61095215908933,0.0,0.0,2.0,1.0,-1.0],[32.61095215908933,35.21861362781145,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>[[15.952667004090516,18.318021832612608,-1860.0,9.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7424,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.952667004090516,18.318021832612608,-1860.0,8.0,1.0,0.0,1.0],[18.318021832612608,20.28915085638102,-532.7423,8.0,1.0,1.0,1.0],[20.28915085638102,22.45739278252627,0.0,8.0,1.0,1.0,1.0],[22.45739278252627,24.42852180629468,1197.85,9.0,1.0,0.0,1.0],[24.42852180629468,35.466844339397774,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7424,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.976639529397236,18.698189764717316,-1860.0,8.0,0.0,1.0,1.0],[18.698189764717316,19.670171991617345,-532.7423,8.0,0.0,1.0,1.0],[19.670171991617345,21.80853289079741,0.0,8.0,0.0,1.0,1.0],[21.80853289079741,23.55810089921746,1197.85,9.0,0.0,0.0,1.0],[23.55810089921746,35.22188762201781,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>[[15.832286293910919,21.978467773638812,-1860.0,9.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5347,8.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.832286293910919,21.978467773638812,-1860.0,8.0,8.0,3.0,-1.0],[21.978467773638812,22.13212231063201,-1607.5346,7.0,8.0,4.0,-1.0],[22.13212231063201,31.044085456237454,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>[[12.091956485902598,21.76498431541698,-1860.0,8.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5347,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,7.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[12.091956485902598,21.76498431541698,-1860.0,7.0,8.0,3.0,-1.0],[21.76498431541698,21.958444872007266,-1607.5346,7.0,8.0,1.0,-1.0],[21.958444872007266,24.473432107681006,0.0,6.0,7.0,2.0,-1.0],[24.473432107681006,31.244551588341075,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5347,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,6.0,7.0,4.0,-1.0]]</t>
+          <t>[[10.945183828414104,22.071508761142717,-1860.0,7.0,8.0,3.0,-1.0],[22.071508761142717,22.29403525979729,-1607.5346,6.0,8.0,4.0,-1.0],[22.29403525979729,24.741826744997585,0.0,6.0,7.0,5.0,-1.0],[24.741826744997585,25.18687974230673,409.2,6.0,7.0,4.0,-1.0],[25.18687974230673,32.97530719521676,1860.0,4.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>[[9.65376696164116,21.75944995118528,-1860.0,6.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.65376696164116,21.75944995118528,-1860.0,5.0,8.0,3.0,-1.0],[21.75944995118528,24.370479615596757,0.0,5.0,7.0,5.0,-1.0],[24.370479615596757,24.845212281853392,409.2,5.0,7.0,4.0,-1.0],[24.845212281853392,33.153033941344454,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5347,4.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,4.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,5.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[9.850265458890377,22.098639673055978,-1860.0,5.0,8.0,4.0,-1.0],[22.098639673055978,22.544035099025635,-1607.5346,3.0,8.0,4.0,-1.0],[22.544035099025635,24.993709941858754,0.0,3.0,8.0,4.0,-1.0],[24.993709941858754,25.439105367828414,227.85,4.0,8.0,3.0,-1.0],[25.439105367828414,31.897339044388456,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>[[7.630236145808632,21.91668362163247,-1860.0,4.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5347,3.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.630236145808632,21.91668362163247,-1860.0,3.0,8.0,3.0,-1.0],[21.91668362163247,22.147110193823174,-1607.5346,2.0,8.0,4.0,-1.0],[22.147110193823174,24.68180248792095,0.0,3.0,7.0,5.0,-1.0],[24.68180248792095,30.442466792688627,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,3.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5347,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,2.0,7.0,5.0,-1.0]]</t>
+          <t>[[-0.6336587098386811,21.454726636478632,-1860.0,2.0,8.0,3.0,-1.0],[21.454726636478632,22.114081422935865,-1607.5346,2.0,8.0,4.0,-1.0],[22.114081422935865,24.421823175536183,0.0,2.0,7.0,5.0,-1.0],[24.421823175536183,25.410855355222033,409.2,2.0,7.0,5.0,-1.0],[25.410855355222033,32.00440321979436,1860.0,1.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5347,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,1.0,7.0,5.0,-1.0]]</t>
+          <t>[[-2.539888137032523,22.05875559180121,-1860.0,2.0,8.0,3.0,-1.0],[22.05875559180121,22.40521536262985,-1607.5346,1.0,8.0,4.0,-1.0],[22.40521536262985,24.83043375843036,0.0,1.0,7.0,5.0,-1.0],[24.83043375843036,31.759629175003248,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>[[-8.332828864608409,22.198992470804722,-733.6842,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-8.332828864608409,22.198992470804722,-733.6843,0.0,0.0,0.0,1.0],[22.198992470804722,24.64153817763777,0.0,0.0,8.0,2.0,-1.0],[24.64153817763777,31.969175298136925,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>[[-9.702933227245694,20.81253118026722,-733.6842,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[-9.702933227245694,20.81253118026722,-733.6843,0.0,0.0,0.0,1.0],[20.81253118026722,23.28675802411962,0.0,0.0,8.0,2.0,-1.0],[23.28675802411962,23.699129164761686,227.85,0.0,8.0,1.0,-1.0],[23.699129164761686,31.121809696318884,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4765,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-8.60600868042424,20.667100587490488,-1860.0,1.0,7.0,0.0,-1.0],[20.667100587490488,21.792989405487205,-1808.4764,0.0,7.0,1.0,-1.0],[21.792989405487205,24.044767041480647,0.0,0.0,6.0,2.0,-1.0],[24.044767041480647,24.7953595868118,227.85,0.0,6.0,1.0,-1.0],[24.7953595868118,28.548322313467526,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4765,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[-8.495658764577326,21.080942629242358,-1860.0,1.0,6.0,0.0,-1.0],[21.080942629242358,21.811229083410744,-1808.4764,0.0,6.0,1.0,-1.0],[21.811229083410744,24.3672316730001,0.0,0.0,5.0,2.0,-1.0],[24.3672316730001,25.097518127168485,227.85,0.0,5.0,2.0,-1.0],[25.097518127168485,27.653520716757843,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4765,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-8.695105961896813,20.759385942072143,-1860.0,1.0,6.0,0.0,-1.0],[20.759385942072143,21.52443767983757,-1808.4764,0.0,6.0,0.0,-1.0],[21.52443767983757,23.81959289313385,0.0,0.0,5.0,1.0,-1.0],[23.81959289313385,24.202118762016568,227.85,0.0,5.0,1.0,-1.0],[24.202118762016568,29.174955057491847,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4765,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-8.786559521560193,20.538598603604882,-1860.0,1.0,4.0,0.0,-1.0],[20.538598603604882,21.35318632930391,-1808.4764,0.0,4.0,0.0,-1.0],[21.35318632930391,23.796949506401,0.0,0.0,3.0,1.0,-1.0],[23.796949506401,31.53553290054178,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4765,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-8.551771677351692,20.026235174745132,-1860.0,2.0,3.0,1.0,-1.0],[20.026235174745132,21.28702959469058,-1808.4764,0.0,3.0,0.0,-1.0],[21.28702959469058,23.80861843458148,0.0,0.0,2.0,1.0,-1.0],[23.80861843458148,33.054444180848094,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4765,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[-8.500875855240508,19.82590059591878,-1860.0,2.0,2.0,1.0,-1.0],[19.82590059591878,21.174794712640654,-1808.4764,0.0,2.0,0.0,-1.0],[21.174794712640654,23.872582946084393,0.0,0.0,1.0,1.0,-1.0],[23.872582946084393,24.322214318325017,227.85,0.0,1.0,1.0,-1.0],[24.322214318325017,36.01262999658123,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4765,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.24631650423712,19.229036167347445,-1860.0,2.0,2.0,0.0,-1.0],[19.229036167347445,20.543283213728273,-1808.4764,0.0,2.0,0.0,-1.0],[20.543283213728273,22.733694957696315,0.0,0.0,1.0,1.0,-1.0],[22.733694957696315,24.924106701664364,227.85,0.0,1.0,0.0,-1.0],[24.924106701664364,34.123836026330146,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9419,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-9.123393332121417,18.442901135502527,-1860.0,1.0,2.0,0.0,-1.0],[18.442901135502527,20.221371746316972,-200.9418,1.0,2.0,0.0,-1.0],[20.221371746316972,22.444460009835034,0.0,1.0,1.0,1.0,-1.0],[22.444460009835034,34.89375428553617,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-9.027359949009863,19.00989194162133,-1860.0,1.0,0.0,0.0,-1.0],[19.00989194162133,34.34276406931026,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,-0.0,9.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.813884177572477,16.992815391043088,-1860.0,9.0,0.0,0.0,1.0],[16.992815391043088,26.072950424444862,0.0,8.0,0.0,1.0,1.0],[26.072950424444862,38.49839836488939,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>[[-8.73173788014999,17.539251582855375,-1860.0,8.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,-0.0,8.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,8.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[-8.73173788014999,17.539251582855375,-1860.0,7.0,0.0,0.0,1.0],[17.539251582855375,27.755747485135235,0.0,7.0,0.0,1.0,1.0],[27.755747485135235,28.242247290005704,890.0,7.0,8.0,4.0,-1.0],[28.242247290005704,39.43174280202651,1860.0,7.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>[[-8.971465657761424,16.835160399350027,-1860.0,7.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,-0.0,7.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
+          <t>[[-8.971465657761424,16.835160399350027,-1860.0,6.0,0.0,0.0,1.0],[16.835160399350027,27.753348346589487,0.0,6.0,0.0,1.0,1.0],[27.753348346589487,28.249629616918558,708.65,8.0,9.0,2.0,-1.0],[28.249629616918558,40.16038010481614,1860.0,8.0,10.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,-0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-10.4561744993561,17.453105873594986,-1860.0,6.0,0.0,0.0,1.0],[17.453105873594986,27.735472326787487,0.0,6.0,0.0,1.0,1.0],[27.735472326787487,38.01783877997999,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,-0.0,5.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[-9.581443882848344,17.434684435901232,-1860.0,5.0,0.0,0.0,1.0],[17.434684435901232,27.258731097264718,0.0,4.0,0.0,1.0,1.0],[27.258731097264718,39.04758709090089,1860.0,5.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,-0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.963746012354907,17.642961813739145,-1860.0,4.0,0.0,0.0,1.0],[17.642961813739145,28.270715698734197,0.0,4.0,0.0,1.0,1.0],[28.270715698734197,39.488900355117856,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,-0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
+          <t>[[-18.869506492868076,16.90228595607352,-1860.0,3.0,0.0,0.0,1.0],[16.90228595607352,27.209412593904148,0.0,3.0,0.0,1.0,1.0],[27.209412593904148,27.815714160835363,890.0,3.0,8.0,4.0,-1.0],[27.815714160835363,41.154348633322066,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,-0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-19.730185648214132,17.107605273967906,-1860.0,2.0,0.0,0.0,1.0],[17.107605273967906,27.208289881662985,0.0,2.0,0.0,1.0,1.0],[27.208289881662985,28.3966057178624,890.0,2.0,8.0,4.0,-1.0],[28.3966057178624,39.09144824365719,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>[[-18.322836839503953,17.345431669463654,-1860.0,1.0,0.0,0.0,1.0],[17.345431669463654,28.227276299318174,-0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.322836839503953,-0.18642912307974768,-1860.0,1.0,0.0,0.0,1.0],[-0.18642912307974768,17.345431669463654,-1860.0,0.0,0.0,0.0,1.0],[17.345431669463654,19.159072441106073,0.0,0.0,0.0,1.0,1.0],[19.159072441106073,22.786353984390917,0.0,1.0,0.0,1.0,1.0],[22.786353984390917,25.20454167991414,0.0,0.0,0.0,1.0,1.0],[25.20454167991414,28.227276299318174,0.0,1.0,0.0,1.0,1.0],[28.227276299318174,41.52730862469593,1860.0,2.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>[[-18.36657183730695,27.688618808674747,-0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[-18.36657183730695,27.688618808674747,0.0,0.0,0.0,1.0,1.0],[27.688618808674747,28.279069970802716,1678.65,1.0,0.0,0.0,1.0],[28.279069970802716,40.08809321336213,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>[[-18.547634592004425,28.32207412992179,-0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-18.547634592004425,28.32207412992179,0.0,0.0,0.0,1.0,1.0],[28.32207412992179,28.915361582098075,890.0,0.0,8.0,3.0,-1.0],[28.915361582098075,40.18782317344742,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>[[-19.59274793037786,26.421433390683582,-0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.59274793037786,26.421433390683582,0.0,0.0,0.0,1.0,1.0],[26.421433390683582,27.616606931490374,890.0,0.0,8.0,2.0,-1.0],[27.616606931490374,39.568342339558285,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7923,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-19.0848640230873,22.318948420012546,-1860.0,1.0,8.0,0.0,-1.0],[22.318948420012546,24.719169431206737,-1074.7922,0.0,8.0,1.0,-1.0],[24.719169431206737,27.719445695199482,0.0,0.0,8.0,1.0,-1.0],[27.719445695199482,28.31950094799803,708.65,1.0,8.0,0.0,-1.0],[28.31950094799803,40.320606003969,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7923,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.083173204444062,12.989496696720064,-1860.0,1.0,8.0,0.0,-1.0],[12.989496696720064,23.745420893276876,-1074.7922,0.0,8.0,0.0,-1.0],[23.745420893276876,26.733177614542658,0.0,0.0,7.0,1.0,-1.0],[26.733177614542658,27.330728958795813,890.0,0.0,7.0,1.0,-1.0],[27.330728958795813,41.074409876618404,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7923,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-19.997741224992556,12.385340527165038,-1860.0,1.0,7.0,0.0,-1.0],[12.385340527165038,22.58001441210354,-1074.7922,0.0,7.0,0.0,-1.0],[22.58001441210354,25.578447907673688,0.0,0.0,6.0,1.0,-1.0],[25.578447907673688,27.977194704129804,890.0,0.0,6.0,1.0,-1.0],[27.977194704129804,39.37124198729637,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7923,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[-18.84860564699721,13.070559642789203,-1860.0,1.0,6.0,0.0,-1.0],[13.070559642789203,22.35613499981798,-1074.7922,0.0,6.0,0.0,-1.0],[22.35613499981798,25.257877298889465,0.0,0.0,5.0,1.0,-1.0],[25.257877298889465,27.579271138146662,890.0,0.0,5.0,1.0,-1.0],[27.579271138146662,38.60589187461833,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7923,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-18.72920294444079,12.41922387052568,-1860.0,1.0,5.0,0.0,-1.0],[12.41922387052568,22.410228697967757,-1074.7922,0.0,5.0,0.0,-1.0],[22.410228697967757,24.76105336324824,0.0,0.0,4.0,1.0,-1.0],[24.76105336324824,27.699584194848857,890.0,0.0,4.0,1.0,-1.0],[27.699584194848857,39.4537075212513,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7923,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-18.202335393321956,13.1065339757218,-1860.0,1.0,4.0,0.0,-1.0],[13.1065339757218,21.967534740545506,-1074.7922,0.0,4.0,0.0,-1.0],[21.967534740545506,24.330468277831823,0.0,0.0,3.0,1.0,-1.0],[24.330468277831823,27.284135199439728,890.0,0.0,3.0,1.0,-1.0],[27.284135199439728,40.280269654514484,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7923,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.161635208595573,13.240998055117121,-1860.0,1.0,3.0,0.0,-1.0],[13.240998055117121,24.49854582890092,-1074.7922,0.0,3.0,0.0,-1.0],[24.49854582890092,27.461058400949288,0.0,0.0,2.0,1.0,-1.0],[27.461058400949288,30.423570972997656,890.0,0.0,2.0,1.0,-1.0],[30.423570972997656,40.496113717962096,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4765,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7923,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.717597789029234,5.099322627965442,-1860.0,10.0,3.0,0.0,1.0],[5.099322627965442,5.680223125940923,-1808.4764,9.0,3.0,1.0,1.0],[5.680223125940923,13.231929599622163,-1074.7922,0.0,3.0,0.0,-1.0],[13.231929599622163,14.974631093548602,0.0,0.0,2.0,1.0,-1.0],[14.974631093548602,31.239845036862043,890.0,0.0,2.0,0.0,-1.0],[31.239845036862043,38.79155151054328,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6843,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-18.858695035645415,4.193525130370194,-1860.0,10.0,2.0,0.0,1.0],[4.193525130370194,4.78460769872957,-733.6842,9.0,2.0,1.0,1.0],[4.78460769872957,14.833011360838935,0.0,0.0,2.0,1.0,-1.0],[14.833011360838935,39.658479231932674,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6843,9.0,1.0,1.0,1.0],[5.714050911665797,13.371181047233907,0.0,0.0,1.0,1.0,-1.0],[13.371181047233907,14.549201068090536,0.0,0.0,0.0,1.0,-1.0],[14.549201068090536,16.31623109937549,1860.0,0.0,0.0,0.0,-1.0],[16.31623109937549,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.846349505466844,5.12504090123748,-1860.0,10.0,1.0,0.0,1.0],[5.12504090123748,5.714050911665797,-733.6842,9.0,1.0,1.0,1.0],[5.714050911665797,14.549201068090536,0.0,0.0,1.0,1.0,-1.0],[14.549201068090536,40.46564152693644,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6843,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-18.44467554567356,4.854090473381191,-1860.0,10.0,0.0,0.0,1.0],[4.854090473381191,5.383607882905164,-733.6842,9.0,0.0,1.0,1.0],[5.383607882905164,33.97754799719963,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6843,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-19.196582680214775,1.30248995448569,-1860.0,9.0,0.0,0.0,1.0],[1.30248995448569,26.233794510202465,-733.6842,9.0,0.0,0.0,1.0],[26.233794510202465,35.652287342362136,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>-733.6843</v>
+        <v>-733.6842</v>
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>[[-18.44566975749752,26.326646903304486,-1860.0,9.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-18.44566975749752,26.326646903304486,-1860.0,8.0,0.0,0.0,1.0],[26.326646903304486,29.09037015397127,0.0,8.0,7.0,1.0,-1.0],[29.09037015397127,36.27605060570493,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>[[-18.87824952192215,26.336957040724037,-1860.0,8.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.87824952192215,26.336957040724037,-1860.0,6.0,0.0,0.0,1.0],[26.336957040724037,27.99117191496719,-873.8504,7.0,8.0,0.0,-1.0],[27.99117191496719,30.748196705372443,0.0,7.0,7.0,1.0,-1.0],[30.748196705372443,35.71084132810191,1860.0,7.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>[[-18.795445222113045,25.140693754248474,-1860.0,7.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-18.795445222113045,25.140693754248474,-1860.0,6.0,0.0,0.0,1.0],[25.140693754248474,26.239097228657513,-1074.7922,7.0,9.0,1.0,-1.0],[26.239097228657513,28.985105914680112,0.0,7.0,8.0,2.0,-1.0],[28.985105914680112,29.53430765188463,890.0,7.0,8.0,1.0,-1.0],[29.53430765188463,35.57552676113434,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>[[-18.371446659018705,25.32383887525282,-1860.0,6.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[-18.371446659018705,25.32383887525282,-1860.0,5.0,0.0,0.0,1.0],[25.32383887525282,25.87002994443122,-873.8504,5.0,8.0,0.0,-1.0],[25.87002994443122,28.60098529032319,0.0,5.0,7.0,1.0,-1.0],[28.60098529032319,30.239558497858372,1071.35,5.0,7.0,1.0,-1.0],[30.239558497858372,35.70146918964231,1860.0,5.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>[[-18.460136581089603,25.77642098180738,-1860.0,5.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
+          <t>[[-18.460136581089603,25.77642098180738,-1860.0,4.0,0.0,0.0,1.0],[25.77642098180738,26.32255132209006,-873.8504,4.0,8.0,2.0,-1.0],[26.32255132209006,29.053203023503453,0.0,4.0,7.0,3.0,-1.0],[29.053203023503453,31.237724384634166,1071.35,4.0,7.0,1.0,-1.0],[31.237724384634166,35.6067671068956,1860.0,4.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9085,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
+          <t>[[-11.457705885176512,26.050139092890394,-1860.0,4.0,7.0,0.0,-1.0],[26.050139092890394,27.474487636361292,-672.9086,3.0,7.0,1.0,-1.0],[27.474487636361292,30.79796757112671,0.0,3.0,6.0,2.0,-1.0],[30.79796757112671,31.27275041895034,1252.7,3.0,6.0,1.0,-1.0],[31.27275041895034,35.545796049363034,1860.0,3.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9085,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
+          <t>[[-8.751260776202853,25.749859251972516,-1860.0,3.0,7.0,2.0,-1.0],[25.749859251972516,26.623305328635183,-672.9086,2.0,7.0,3.0,-1.0],[26.623305328635183,29.68036659695452,0.0,2.0,6.0,4.0,-1.0],[29.68036659695452,30.553812673617188,1252.7,2.0,6.0,4.0,-1.0],[30.553812673617188,34.48432001859919,1860.0,2.0,7.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,1.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
+          <t>[[-8.720600197365597,27.85785470548778,-1860.0,2.0,6.0,1.0,-1.0],[27.85785470548778,30.906059280725565,0.0,1.0,5.0,3.0,-1.0],[30.906059280725565,31.3415170771881,1434.05,0.0,5.0,3.0,-1.0],[31.3415170771881,34.389721652425884,1860.0,1.0,5.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9085,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[-9.0369809601662,25.38427064912653,-1860.0,1.0,7.0,2.0,-1.0],[25.38427064912653,28.473357332011776,-672.9086,0.0,7.0,0.0,-1.0],[28.473357332011776,31.121145917341988,0.0,0.0,6.0,1.0,-1.0],[31.121145917341988,31.56244401489702,1252.7,0.0,6.0,1.0,-1.0],[31.56244401489702,34.65153069778226,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9085,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-8.731740297598687,24.82649491496002,-1860.0,1.0,7.0,0.0,-1.0],[24.82649491496002,25.72138118729492,-672.9086,0.0,7.0,1.0,-1.0],[25.72138118729492,28.406040004299616,0.0,0.0,6.0,2.0,-1.0],[28.406040004299616,30.195812548969418,1252.7,0.0,6.0,0.0,-1.0],[30.195812548969418,35.56513018297881,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9085,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-8.808865035697247,24.339139950345356,-1860.0,1.0,6.0,1.0,-1.0],[24.339139950345356,26.15546899067646,-672.9086,0.0,6.0,1.0,-1.0],[26.15546899067646,28.879962551173108,0.0,0.0,5.0,2.0,-1.0],[28.879962551173108,31.150373851586984,1252.7,0.0,5.0,0.0,-1.0],[31.150373851586984,36.145278712497515,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-8.966725062329564,0.5538491698966137,-1860.0,8.0,0.0,0.0,1.0],[0.5538491698966137,23.675243733874474,-733.6842,8.0,0.0,0.0,1.0],[23.675243733874474,26.39540780022481,0.0,8.0,0.0,1.0,1.0],[26.39540780022481,27.755489833399977,1016.5,9.0,0.0,0.0,1.0],[27.755489833399977,35.91598203245099,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,1.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-8.189371790192736,0.8107482806395137,-1860.0,1.0,0.0,0.0,1.0],[0.8107482806395137,24.382491323295405,-733.6842,0.0,0.0,0.0,1.0],[24.382491323295405,26.953954200676044,0.0,1.0,0.0,1.0,1.0],[26.953954200676044,34.239765686587866,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,1.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8285544780504653,25.031884576340058,-1860.0,1.0,8.0,3.0,-1.0],[25.031884576340058,27.511652704843257,0.0,0.0,8.0,4.0,-1.0],[27.511652704843257,27.865905294629428,227.85,0.0,8.0,3.0,-1.0],[27.865905294629428,34.24245191078052,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>[[-0.8045334098895883,22.896049447989117,-733.6842,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
+          <t>[[-0.8045334098895883,22.896049447989117,-733.6843,0.0,0.0,0.0,1.0],[22.896049447989117,25.409747629885345,0.0,0.0,8.0,2.0,-1.0],[25.409747629885345,27.205246331239795,227.85,0.0,8.0,2.0,-1.0],[27.205246331239795,34.74634087692848,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>[[-0.8086767806605984,23.28119775225262,-986.1495,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-0.8086767806605984,23.28119775225262,-986.1497,0.0,0.0,0.0,1.0],[23.28119775225262,26.42335530002391,0.0,0.0,8.0,2.0,-1.0],[26.42335530002391,33.755056244823585,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>[[-0.8226825328544912,22.666785807354938,-986.1495,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[-0.8226825328544912,22.666785807354938,-986.1497,0.0,0.0,0.0,1.0],[22.666785807354938,26.076547340611146,0.0,0.0,8.0,3.0,-1.0],[26.076547340611146,36.68469433296379,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>[[-0.792115077659882,12.814010090091632,-1860.0,9.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-0.792115077659882,12.814010090091632,-1860.0,8.0,0.0,0.0,1.0],[12.814010090091632,17.91630702799845,-733.6842,9.0,0.0,0.0,1.0],[17.91630702799845,41.30183466007137,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,9.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-0.7901573278879391,18.16278630648099,-1860.0,8.0,0.0,0.0,1.0],[18.16278630648099,28.93150428055424,0.0,9.0,0.0,1.0,1.0],[28.93150428055424,41.85396584944215,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,8.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,8.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,8.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[-0.7626232794666812,18.13348796244254,-1860.0,5.0,0.0,0.0,1.0],[18.13348796244254,29.11959914959907,0.0,7.0,0.0,1.0,1.0],[29.11959914959907,29.559043597085328,890.0,7.0,8.0,0.0,-1.0],[29.559043597085328,42.74237702167316,1860.0,6.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,7.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7843419030361622,17.71378017751417,-1860.0,4.0,0.0,0.0,1.0],[17.71378017751417,29.759068974151592,0.0,7.0,0.0,1.0,1.0],[29.759068974151592,30.189257859745787,890.0,7.0,8.0,1.0,-1.0],[30.189257859745787,41.80435777078901,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,6.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,6.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,6.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,6.0,8.0,1.0,-1.0]]</t>
+          <t>[[-0.7838041493776018,17.488555091540736,-1860.0,4.0,0.0,0.0,1.0],[17.488555091540736,29.23507174641681,0.0,4.0,0.0,1.0,1.0],[29.23507174641681,30.540240263625265,890.0,4.0,8.0,1.0,-1.0],[30.540240263625265,42.28675691850134,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>[[0.4373098028181701,26.72693793185583,-1860.0,6.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,5.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,5.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,5.0,7.0,1.0,-1.0]]</t>
+          <t>[[0.4373098028181701,26.72693793185583,-1860.0,3.0,0.0,0.0,1.0],[26.72693793185583,28.06369868417978,-873.8504,4.0,8.0,0.0,-1.0],[28.06369868417978,31.182807106268996,0.0,3.0,7.0,1.0,-1.0],[31.182807106268996,44.55041462950848,1860.0,4.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,5.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,4.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,4.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,4.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,4.0,7.0,1.0,-1.0]]</t>
+          <t>[[-0.9883996611836087,25.258160411523082,-1860.0,3.0,0.0,0.0,1.0],[25.258160411523082,27.007931083036862,-873.8504,3.0,8.0,0.0,-1.0],[27.007931083036862,29.63258709030753,0.0,3.0,7.0,1.0,-1.0],[29.63258709030753,31.382357761821307,1071.35,3.0,7.0,1.0,-1.0],[31.382357761821307,42.31842445878244,1860.0,3.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>[[-3.238786972373251,27.35248498107974,-1860.0,4.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,3.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,3.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,3.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,3.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.238786972373251,27.35248498107974,-1860.0,2.0,0.0,0.0,1.0],[27.35248498107974,27.80907112963874,-873.8504,2.0,8.0,1.0,-1.0],[27.80907112963874,31.00517416955174,0.0,2.0,7.0,2.0,-1.0],[31.00517416955174,31.918346466669735,1071.35,2.0,7.0,1.0,-1.0],[31.918346466669735,41.96324173496774,1860.0,2.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,3.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,2.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.9947433807787847,25.510747135571663,-1860.0,2.0,0.0,0.0,1.0],[25.510747135571663,26.460930152783344,-873.8504,2.0,8.0,0.0,-1.0],[26.460930152783344,29.31147920441839,0.0,1.0,7.0,1.0,-1.0],[29.31147920441839,30.73675373023591,1071.35,2.0,7.0,1.0,-1.0],[30.73675373023591,44.03931597119946,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>[[-2.940369776150578,25.958161273224494,-1860.0,2.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,1.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,1.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
+          <t>[[-2.940369776150578,25.958161273224494,-1860.0,1.0,0.0,0.0,1.0],[25.958161273224494,26.890371952236592,-873.8504,0.0,8.0,1.0,-1.0],[26.890371952236592,29.687003989272892,0.0,1.0,7.0,2.0,-1.0],[29.687003989272892,32.01753068680314,1071.35,0.0,7.0,1.0,-1.0],[32.01753068680314,43.20405883494833,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>[[-3.317736787693387,26.322060943358295,-1860.0,1.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-3.317736787693387,-0.12575857050320582,-1860.0,1.0,0.0,0.0,1.0],[-0.12575857050320582,26.322060943358295,-1860.0,0.0,0.0,0.0,1.0],[26.322060943358295,26.77805783152832,-873.8504,0.0,8.0,1.0,-1.0],[26.77805783152832,29.514039160548474,0.0,0.0,7.0,2.0,-1.0],[29.514039160548474,30.882029825058556,1071.35,0.0,7.0,1.0,-1.0],[30.882029825058556,41.825955141139175,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8836,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-3.1675207668873657,23.958319871765298,-1860.0,2.0,7.0,0.0,-1.0],[23.958319871765298,24.41041721574284,-401.8837,2.0,7.0,0.0,-1.0],[24.41041721574284,27.123001279608104,0.0,2.0,6.0,1.0,-1.0],[27.123001279608104,28.931390655518285,1497.3,2.0,6.0,1.0,-1.0],[28.931390655518285,41.590116286889526,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,2.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
+          <t>[[-3.2429692379502564,22.87532269503339,-1860.0,1.0,5.0,1.0,-1.0],[22.87532269503339,25.207313046192645,-200.9418,1.0,5.0,2.0,-1.0],[25.207313046192645,28.005701467583748,0.0,1.0,5.0,2.0,-1.0],[28.005701467583748,28.4720995378156,1497.3,2.0,5.0,1.0,-1.0],[28.4720995378156,42.930439715002976,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8836,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-3.132943569688188,24.27451152586689,-1860.0,2.0,5.0,0.0,-1.0],[24.27451152586689,24.7470538551006,-401.8837,2.0,5.0,0.0,-1.0],[24.7470538551006,27.10976550126914,0.0,2.0,4.0,1.0,-1.0],[27.10976550126914,28.054850159736556,1497.3,2.0,4.0,1.0,-1.0],[28.054850159736556,43.64874702444893,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>[[-2.949744650801829,23.86187624182115,-1860.0,2.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-2.949744650801829,23.86187624182115,-1860.0,1.0,2.0,2.0,-1.0],[23.86187624182115,24.650453326898294,-200.9418,1.0,2.0,2.0,-1.0],[24.650453326898294,27.410473124668307,0.0,1.0,2.0,2.0,-1.0],[27.410473124668307,27.80476166720688,1497.3,2.0,2.0,1.0,-1.0],[27.80476166720688,36.08482106051692,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8836,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.0940505631117587,22.816301005505593,-1860.0,2.0,2.0,0.0,-1.0],[22.816301005505593,24.749909331521813,-401.8837,1.0,2.0,0.0,-1.0],[24.749909331521813,27.45696098794452,0.0,1.0,1.0,1.0,-1.0],[27.45696098794452,30.164012644367226,1497.3,1.0,1.0,1.0,-1.0],[30.164012644367226,35.1913942920094,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>[[-3.133647285768385,22.892994648448287,-1860.0,2.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-3.133647285768385,7.277009487918283,-1860.0,1.0,1.0,0.0,-1.0],[7.277009487918283,20.0901255170711,-1860.0,2.0,1.0,0.0,-1.0],[20.0901255170711,22.892994648448287,-1860.0,1.0,1.0,0.0,-1.0],[22.892994648448287,36.106520553512134,0.0,1.0,1.0,1.0,-1.0],[36.106520553512134,36.50693042942316,181.3501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7423,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-6.519053499862936,10.160326180227317,-1860.0,9.0,0.0,0.0,1.0],[10.160326180227317,11.468512821803023,-532.7424,8.0,0.0,1.0,1.0],[11.468512821803023,12.449652802984803,0.0,8.0,0.0,1.0,1.0],[12.449652802984803,18.663539350469406,1197.85,9.0,0.0,0.0,1.0],[18.663539350469406,25.858565879135792,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,8.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,8.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,9.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-23.157544165598864,16.90843076475364,-1860.0,8.0,9.0,2.0,-1.0],[16.90843076475364,17.403072430560456,-1808.4764,7.0,9.0,2.0,-1.0],[17.403072430560456,18.886997427980923,0.0,7.0,9.0,2.0,-1.0],[18.886997427980923,19.38163909378774,46.5,8.0,9.0,1.0,-1.0],[19.38163909378774,25.811980749276415,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-23.95174992965749,17.10621284315048,-1860.0,7.0,9.0,3.0,-1.0],[17.10621284315048,19.239094026153488,0.0,7.0,8.0,4.0,-1.0],[19.239094026153488,28.837059349667033,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,6.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,6.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-27.589920189762932,15.94679725448454,-1860.0,6.0,0.0,0.0,1.0],[15.94679725448454,17.092500345122634,-733.6842,5.0,0.0,0.0,1.0],[17.092500345122634,19.383906526398814,0.0,5.0,8.0,3.0,-1.0],[19.383906526398814,29.1223827968226,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,5.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,5.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.266459330222244,16.8154451342167,-1860.0,5.0,0.0,0.0,1.0],[16.8154451342167,18.506016551633156,0.0,4.0,8.0,3.0,-1.0],[18.506016551633156,19.633064163244132,227.85,4.0,8.0,3.0,-1.0],[19.633064163244132,27.522397444520944,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.458330178919848,-1860.0,4.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,4.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,4.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,4.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.458330178919848,-1860.0,3.0,0.0,0.0,1.0],[16.458330178919848,17.582684322976174,-733.6842,3.0,0.0,0.0,1.0],[17.582684322976174,19.26921553906067,0.0,3.0,8.0,4.0,-1.0],[19.26921553906067,19.831392611088834,227.85,3.0,8.0,3.0,-1.0],[19.831392611088834,27.139694547454976,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,3.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.659021744360256,-1860.0,3.0,0.0,0.0,1.0],[16.659021744360256,18.39651625696386,0.0,2.0,9.0,2.0,-1.0],[18.39651625696386,28.821483332585455,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.856873397231563,-1860.0,2.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.856873397231563,-1860.0,1.0,8.0,3.0,-1.0],[16.856873397231563,18.558349984002742,0.0,1.0,8.0,4.0,-1.0],[18.558349984002742,19.1255088462598,227.85,2.0,8.0,3.0,-1.0],[19.1255088462598,27.632891780115717,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>[[-28.352162380837775,16.97681646261686,-733.6842,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[-28.352162380837775,16.97681646261686,-733.6843,0.0,0.0,0.0,1.0],[16.97681646261686,18.720238725826647,0.0,0.0,9.0,2.0,-1.0],[18.720238725826647,19.30137948022991,46.5,1.0,9.0,1.0,-1.0],[19.30137948022991,29.180772305085412,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,16.3082887319805,-733.6842,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-28.51583558333333,16.3082887319805,-733.6843,0.0,0.0,0.0,1.0],[16.3082887319805,17.989193393804772,0.0,0.0,8.0,2.0,-1.0],[17.989193393804772,18.549494947746194,227.85,0.0,8.0,2.0,-1.0],[18.549494947746194,26.954018256867542,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>[[-28.292333007671303,-7.798825774169366,-1860.0,1.0,2.0,0.0,-1.0],[-7.798825774169366,-7.196075561419306,-200.9418,0.0,2.0,0.0,-1.0],[-7.196075561419306,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-28.292333007671303,-6.59332534866925,-1860.0,1.0,2.0,0.0,-1.0],[-6.59332534866925,18.119433374083087,0.0,0.0,2.0,1.0,-1.0],[18.119433374083087,31.379938054584343,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="E414" s="4" t="inlineStr">
         <is>
-          <t>[0.3434343434,0,0.0101010101,0.4242424242,0,0,0.2222222222,0]</t>
+          <t>[0.3636363636,0,0,0.4141414141,0,0,0.2222222222,0]</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>[[-28.251498498182293,-8.062514982872095,-1860.0,1.0,1.0,0.0,-1.0],[-8.062514982872095,-6.874927717265614,-200.9418,0.0,1.0,0.0,-1.0],[-6.874927717265614,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-28.251498498182293,-6.281134084462369,-1860.0,1.0,1.0,0.0,-1.0],[-6.281134084462369,18.064404860470518,0.0,0.0,1.0,1.0,-1.0],[18.064404860470518,30.534071149338583,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="E415" s="4" t="inlineStr">
         <is>
-          <t>[0.3434343434,0,0.0202020202,0.4242424242,0,0,0.2121212121,0]</t>
+          <t>[0.3737373737,0,0,0.4141414141,0,0,0.2121212121,0]</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.08576385353344,-1860.0,1.0,0.0,0.0,-1.0],[-8.08576385353344,-7.466670770812229,-200.9418,0.0,0.0,0.0,-1.0],[-7.466670770812229,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-6.847577688091018,-1860.0,1.0,0.0,0.0,-1.0],[-6.847577688091018,32.77437960606635,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="E416" s="4" t="inlineStr">
         <is>
-          <t>[0.3333333333,0,0.0101010101,0.6565656566,0,0,0,0]</t>
+          <t>[0.3535353535,0,0,0.6464646465,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-28.51583558333333,-8.161336289602811,-1860.0,8.0,0.0,0.0,1.0],[-8.161336289602811,14.587809979860712,-733.6842,8.0,0.0,0.0,1.0],[14.587809979860712,16.38379521166046,0.0,8.0,0.0,1.0,1.0],[16.38379521166046,22.370412650992964,1016.5,9.0,0.0,0.0,1.0],[22.370412650992964,30.751677066058473,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,3.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
+          <t>[[-11.908724046901925,20.73534036402382,-1860.0,4.0,9.0,0.0,-1.0],[20.73534036402382,21.176476369576875,-1808.4764,3.0,9.0,1.0,-1.0],[21.176476369576875,23.382156397342122,0.0,1.0,8.0,2.0,-1.0],[23.382156397342122,23.823292402895177,227.85,3.0,8.0,1.0,-1.0],[23.823292402895177,25.146700419554328,590.55,1.0,6.0,0.0,-1.0],[25.146700419554328,31.763740502850084,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,1.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,2.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,2.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.035674578375192,19.366164276537077,-1860.0,1.0,3.0,1.0,-1.0],[19.366164276537077,19.924816670587283,-1808.4764,1.0,3.0,1.0,-1.0],[19.924816670587283,22.15942624678813,0.0,0.0,3.0,1.0,-1.0],[22.15942624678813,22.718078640838343,46.5,1.0,3.0,0.0,-1.0],[22.718078640838343,42.27091243259575,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,46.49825979899363,409.2,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.446742943472662,20.89588487044766,-1860.0,2.0,2.0,0.0,-1.0],[20.89588487044766,21.49128893855338,-1808.4764,1.0,2.0,1.0,-1.0],[21.49128893855338,23.872905210976263,0.0,1.0,1.0,2.0,-1.0],[23.872905210976263,24.468309279081986,227.85,1.0,1.0,2.0,-1.0],[24.468309279081986,26.254521483399145,409.2,0.0,0.0,0.0,-1.0],[26.254521483399145,46.49825979899363,409.2001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>[[-13.362752798384967,18.067167782712055,-1860.0,1.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.362752798384967,18.067167782712055,-1860.0,0.0,2.0,0.0,-1.0],[18.067167782712055,19.8804324316215,-1808.4764,0.0,2.0,1.0,-1.0],[19.8804324316215,22.298118630167423,0.0,0.0,2.0,1.0,-1.0],[22.298118630167423,22.902540179803907,46.5,1.0,2.0,0.0,-1.0],[22.902540179803907,46.47498061562668,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,50.37025249962831,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.510026571708218,20.517998799094805,-1860.0,1.0,1.0,0.0,-1.0],[20.517998799094805,21.153153133148713,-1808.4764,0.0,1.0,1.0,-1.0],[21.153153133148713,23.058616135310423,0.0,0.0,0.0,2.0,-1.0],[23.058616135310423,24.96407913747214,227.85,0.0,0.0,0.0,-1.0],[24.96407913747214,50.37025249962831,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,-0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.468146016474295,6.028954467555527,-1860.0,1.0,1.0,0.0,-1.0],[6.028954467555527,21.12348387454636,0.0,0.0,1.0,1.0,-1.0],[21.12348387454636,23.010300050420213,0.0,0.0,0.0,1.0,-1.0],[23.010300050420213,25.52605495158535,1860.0,0.0,0.0,0.0,-1.0],[25.52605495158535,48.79678778736288,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.037180856471332,6.060877343205567,-1860.0,1.0,0.0,0.0,-1.0],[6.060877343205567,49.98641120246244,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,-0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-12.888065504034058,18.190362976117605,-1860.0,9.0,0.0,0.0,1.0],[18.190362976117605,32.143943110063255,0.0,9.0,0.0,1.0,1.0],[32.143943110063255,49.90304509872135,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>[[-12.761608216582523,18.15128723523793,-1860.0,8.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,-0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.65,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[-12.761608216582523,18.15128723523793,-1860.0,7.0,0.0,0.0,1.0],[18.15128723523793,32.31969765065564,0.0,8.0,0.0,1.0,1.0],[32.31969765065564,33.60773496114816,1678.6499,9.0,0.0,2.0,1.0],[33.60773496114816,50.99623865279717,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,-0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.73523555927291,17.54656383104959,-1860.0,7.0,0.0,0.0,1.0],[17.54656383104959,34.298197536334385,0.0,7.0,0.0,1.0,1.0],[34.298197536334385,51.04983124161917,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,-0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.630442718895095,18.12591559759094,-1860.0,6.0,0.0,0.0,1.0],[18.12591559759094,32.27384042317452,0.0,6.0,0.0,1.0,1.0],[32.27384042317452,48.267146747747255,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -10706,7 +10706,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,-0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.65,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[-12.931053183247252,17.377753250520712,-1860.0,5.0,0.0,0.0,1.0],[17.377753250520712,32.5321564674047,0.0,5.0,0.0,1.0,1.0],[32.5321564674047,34.42645686951519,1678.6499,6.0,0.0,0.0,1.0],[34.42645686951519,49.58086008639918,1860.0,5.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,-0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.789751678456406,17.524917111374926,-1860.0,4.0,0.0,0.0,1.0],[17.524917111374926,33.64974093575329,0.0,4.0,0.0,1.0,1.0],[33.64974093575329,51.064550666081935,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,-0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
+          <t>[[-12.387430091420587,17.799611991275615,-1860.0,3.0,0.0,0.0,1.0],[17.799611991275615,33.52202974267989,0.0,3.0,0.0,1.0,1.0],[33.52202974267989,49.87334420414034,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8504,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-11.166545990068537,28.404275155559752,-1860.0,3.0,0.0,0.0,1.0],[28.404275155559752,30.91670824417107,-873.8505,2.0,8.0,3.0,-1.0],[30.91670824417107,34.05724960493522,0.0,2.0,8.0,3.0,-1.0],[34.05724960493522,51.01617295306163,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8504,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,2.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,890.0,3.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.640204688437672,30.186354010912417,-1860.0,2.0,8.0,2.0,-1.0],[30.186354010912417,30.768301067825497,-873.8505,2.0,8.0,2.0,-1.0],[30.768301067825497,34.25998340930396,0.0,1.0,8.0,2.0,-1.0],[34.25998340930396,34.84193046621704,889.9999,2.0,8.0,1.0,-1.0],[34.84193046621704,49.97255394595708,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,890.0,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,2.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.4856277310705694,30.797224793110733,-1860.0,1.0,8.0,2.0,-1.0],[30.797224793110733,34.22553994452995,0.0,1.0,8.0,2.0,-1.0],[34.22553994452995,35.368311661669686,889.9999,2.0,8.0,1.0,-1.0],[35.368311661669686,49.08157226734657,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8504,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,890.0,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.9743499847910035,30.436236141724955,-1860.0,1.0,0.0,0.0,1.0],[30.436236141724955,31.018214719399438,-873.8505,0.0,8.0,2.0,-1.0],[31.018214719399438,33.928107607771864,0.0,0.0,8.0,2.0,-1.0],[33.928107607771864,34.51008618544635,889.9999,1.0,8.0,1.0,-1.0],[34.51008618544635,49.64152920498293,1860.0,1.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,-0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,890.0,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.847153200307435,30.646372336029042,-1860.0,1.0,0.0,0.0,1.0],[30.646372336029042,34.66808395922837,0.0,1.0,0.0,1.0,1.0],[34.66808395922837,37.54073511865647,889.9999,1.0,8.0,0.0,-1.0],[37.54073511865647,49.03133975636885,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8504,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.35,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-7.981039677926239,29.75385873808272,-1860.0,1.0,0.0,0.0,1.0],[29.75385873808272,34.89952670390212,-873.8505,0.0,8.0,0.0,-1.0],[34.89952670390212,38.90171289953943,0.0,0.0,7.0,1.0,-1.0],[38.90171289953943,40.61693555481257,1071.3499,0.0,7.0,1.0,-1.0],[40.61693555481257,48.6213079460872,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C455" t="n">
-        <v>-873.8504</v>
+        <v>-873.8505</v>
       </c>
       <c r="D455" s="4" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>[[-7.391476067821784,8.815961861520975,-986.1496,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,-0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-7.391476067821784,8.815961861520975,-986.1497,0.0,0.0,0.0,1.0],[8.815961861520975,33.40655734052378,0.0,0.0,8.0,1.0,-1.0],[33.40655734052378,47.93736375993453,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,-0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-7.50252825896867,8.725470877811897,-1860.0,1.0,7.0,0.0,-1.0],[8.725470877811897,33.36798808551572,0.0,0.0,7.0,1.0,-1.0],[33.36798808551572,52.00013524256007,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,-0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-7.88717335140371,9.044753456036549,-1860.0,1.0,6.0,0.0,-1.0],[9.044753456036549,32.874872666508026,0.0,0.0,6.0,1.0,-1.0],[32.874872666508026,54.19655827587724,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,-0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-7.871601879230988,9.1470993319877,-1860.0,1.0,5.0,0.0,-1.0],[9.1470993319877,34.35999001527465,0.0,0.0,5.0,1.0,-1.0],[34.35999001527465,54.5303025619042,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,-0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-8.06501593357726,9.678007584631597,-1860.0,1.0,4.0,0.0,-1.0],[9.678007584631597,34.151143471816226,0.0,0.0,4.0,1.0,-1.0],[34.151143471816226,52.5059953872047,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,-0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-7.452173238962049,9.01199110040751,-1860.0,1.0,3.0,0.0,-1.0],[9.01199110040751,34.88424934798826,0.0,0.0,3.0,1.0,-1.0],[34.88424934798826,50.76040781809462,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,-0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-8.132259430011528,9.377048097731977,-1860.0,1.0,2.0,0.0,-1.0],[9.377048097731977,33.52781710151612,0.0,0.0,2.0,1.0,-1.0],[33.52781710151612,51.640893854354225,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,30.317950836778262,-0.0,0.0,1.0,1.0,-1.0],[30.317950836778262,33.54922388266518,0.0,0.0,0.0,1.0,-1.0],[33.54922388266518,36.7804969285521,1860.0,0.0,0.0,0.0,-1.0],[36.7804969285521,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-7.811071104687318,8.991548733924635,-1860.0,1.0,1.0,0.0,-1.0],[8.991548733924635,33.54922388266518,0.0,0.0,1.0,1.0,-1.0],[33.54922388266518,56.16813520387358,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.509250764453817,9.287177164359285,-1860.0,1.0,0.0,0.0,-1.0],[9.287177164359285,54.07765164119422,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -11120,7 +11120,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6843,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.998756354782032,3.2823498029561913,-1860.0,9.0,0.0,0.0,1.0],[3.2823498029561913,9.219774096502626,-733.6842,9.0,0.0,0.0,1.0],[9.219774096502626,50.781744151327665,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6843,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-7.5259422466292625,8.88714186218196,-1860.0,9.0,0.0,0.0,1.0],[8.88714186218196,29.555469999203503,-733.6842,9.0,0.0,0.0,1.0],[29.555469999203503,52.65536615234522,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6843,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-7.83124313551667,9.15363989450027,-1860.0,8.0,0.0,0.0,1.0],[9.15363989450027,29.778140716663696,-733.6842,8.0,0.0,0.0,1.0],[29.778140716663696,32.81115554345243,0.0,8.0,8.0,2.0,-1.0],[32.81115554345243,35.23756740488342,227.85,8.0,8.0,1.0,-1.0],[35.23756740488342,52.22245043490036,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6843,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.948929564089551,8.896219842097295,-1860.0,7.0,0.0,0.0,1.0],[8.896219842097295,29.22657257370211,-733.6842,7.0,0.0,0.0,1.0],[29.22657257370211,32.13090867821708,0.0,7.0,8.0,1.0,-1.0],[32.13090867821708,35.616112003635045,227.85,7.0,8.0,1.0,-1.0],[35.616112003635045,49.556925305306926,1860.0,7.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6843,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
+          <t>[[-7.779917561568604,9.173138445962588,-1860.0,6.0,0.0,0.0,1.0],[9.173138445962588,30.364458455376578,-733.6842,6.0,0.0,0.0,1.0],[30.364458455376578,33.39178988529286,0.0,6.0,8.0,2.0,-1.0],[33.39178988529286,34.602722457259375,227.85,6.0,8.0,2.0,-1.0],[34.602722457259375,52.161244750773825,1860.0,6.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6843,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
+          <t>[[-7.778354666204955,9.193166131691363,-1860.0,5.0,0.0,0.0,1.0],[9.193166131691363,29.80144138627975,-733.6842,5.0,0.0,0.0,1.0],[29.80144138627975,33.438195842971815,0.0,5.0,8.0,3.0,-1.0],[33.438195842971815,34.65044732853584,227.85,5.0,8.0,1.0,-1.0],[34.65044732853584,52.22809386921417,1860.0,5.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6843,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
+          <t>[[-7.795372522931508,8.664729823290738,-1860.0,4.0,0.0,0.0,1.0],[8.664729823290738,32.08872162368394,-733.6842,4.0,0.0,0.0,1.0],[32.08872162368394,35.254125921034365,0.0,4.0,8.0,2.0,-1.0],[35.254125921034365,54.87963256460705,1860.0,4.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6843,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
+          <t>[[-8.127396585498271,8.772950009571108,-1860.0,3.0,0.0,0.0,1.0],[8.772950009571108,31.70913467430812,-733.6842,3.0,0.0,0.0,1.0],[31.70913467430812,35.330637516108695,0.0,3.0,8.0,2.0,-1.0],[35.330637516108695,51.627400304211314,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6843,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,2.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[-2.2953996911123196,9.064560437938052,-1860.0,2.0,0.0,0.0,1.0],[9.064560437938052,30.161629249031595,-733.6842,2.0,0.0,0.0,1.0],[30.161629249031595,33.407332143045984,0.0,1.0,8.0,2.0,-1.0],[33.407332143045984,34.48923310771745,227.85,2.0,8.0,2.0,-1.0],[34.48923310771745,51.25869806012514,1860.0,1.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5347,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,2.0,8.0,0.0,-1.0]]</t>
+          <t>[[1.1803474957605447,30.770960056018414,-1860.0,2.0,8.0,1.0,-1.0],[30.770960056018414,32.77710328044268,-1607.5346,1.0,8.0,1.0,-1.0],[32.77710328044268,36.28785392318514,0.0,1.0,8.0,1.0,-1.0],[36.28785392318514,37.79246134150333,227.85,2.0,8.0,0.0,-1.0],[37.79246134150333,50.83239230026104,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5347,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[8.84718636594401,30.1015725931777,-1860.0,1.0,8.0,0.0,-1.0],[30.1015725931777,30.553793576735863,-1607.5346,0.0,8.0,1.0,-1.0],[30.553793576735863,33.71934046164301,0.0,0.0,7.0,2.0,-1.0],[33.71934046164301,37.337108330108315,409.2,0.0,7.0,1.0,-1.0],[37.337108330108315,53.617063738202205,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4765,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[8.629600166848725,24.505992982956336,-1860.0,1.0,8.0,0.0,-1.0],[24.505992982956336,26.9485149546652,-1808.4764,0.0,8.0,0.0,-1.0],[26.9485149546652,29.79812392165887,0.0,0.0,7.0,1.0,-1.0],[29.79812392165887,33.86899387450698,227.85,0.0,7.0,0.0,-1.0],[33.86899387450698,48.931212700044966,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4765,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[8.578850941358132,25.691822073148877,-1860.0,1.0,7.0,0.0,-1.0],[25.691822073148877,29.11441629950702,-1808.4764,0.0,7.0,0.0,-1.0],[29.11441629950702,32.53701052586517,0.0,0.0,6.0,1.0,-1.0],[32.53701052586517,33.392659082454706,227.85,0.0,6.0,0.0,-1.0],[33.392659082454706,50.93345449254022,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4765,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.58402710487467,24.645981237977466,-1860.0,1.0,6.0,1.0,-1.0],[24.645981237977466,27.684729317213126,-1808.4764,0.0,6.0,0.0,-1.0],[27.684729317213126,30.723477396448793,0.0,0.0,5.0,1.0,-1.0],[30.723477396448793,33.328118607222216,227.85,0.0,5.0,0.0,-1.0],[33.328118607222216,51.5606070826362,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4765,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[8.712982875655083,24.97042591158625,-1860.0,1.0,6.0,0.0,-1.0],[24.97042591158625,25.692978935405414,-1808.4764,0.0,6.0,1.0,-1.0],[25.692978935405414,28.221914518772483,0.0,0.0,5.0,2.0,-1.0],[28.221914518772483,32.19595614977788,227.85,0.0,5.0,0.0,-1.0],[32.19595614977788,44.479357554703654,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4765,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[8.82649513126567,14.423283006946393,-1860.0,8.0,13.0,2.0,0.0],[14.423283006946393,24.497501183171693,-1808.4764,0.0,6.0,0.0,-1.0],[24.497501183171693,27.48245471686808,0.0,0.0,5.0,1.0,-1.0],[27.48245471686808,45.765295110758444,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4765,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[8.660443620862267,15.446325744617937,-1860.0,9.0,13.0,1.0,0.0],[15.446325744617937,24.171031332303798,-1808.4764,0.0,5.0,0.0,-1.0],[24.171031332303798,26.756129284210722,0.0,0.0,4.0,1.0,-1.0],[26.756129284210722,28.04867826016418,227.85,0.0,4.0,0.0,-1.0],[28.04867826016418,40.651030775710424,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4765,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[8.548162273718686,15.656809220158557,-1860.0,10.0,4.0,0.0,1.0],[15.656809220158557,24.310814198433185,-1808.4764,0.0,4.0,0.0,-1.0],[24.310814198433185,27.09245865573574,0.0,0.0,3.0,1.0,-1.0],[27.09245865573574,39.14625130404683,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>[[8.632676841069298,15.006814361456225,-1860.0,10.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4765,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[8.632676841069298,15.006814361456225,-1860.0,9.0,3.0,0.0,1.0],[15.006814361456225,24.416255462979787,-1808.4764,0.0,3.0,0.0,-1.0],[24.416255462979787,27.148028686002757,0.0,0.0,2.0,1.0,-1.0],[27.148028686002757,28.058619760343745,227.85,0.0,2.0,1.0,-1.0],[28.058619760343745,38.68218229432196,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4765,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[8.616079852194712,15.022587019903547,-1860.0,10.0,2.0,0.0,1.0],[15.022587019903547,24.952673129852236,-1808.4764,0.0,2.0,0.0,-1.0],[24.952673129852236,27.51527599693577,0.0,0.0,1.0,1.0,-1.0],[27.51527599693577,40.32829033235344,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4765,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,40.50480958264197,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.08920529025552,15.947533603561325,-1860.0,10.0,1.0,0.0,1.0],[15.947533603561325,24.788152956030356,-1808.4764,0.0,1.0,0.0,-1.0],[24.788152956030356,27.407595727132293,0.0,0.0,0.0,1.0,-1.0],[27.407595727132293,30.35446884462197,227.85,0.0,0.0,0.0,-1.0],[30.35446884462197,40.50480958264197,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -11649,11 +11649,11 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>[[8.842562569053646,15.41074883013695,-1860.0,9.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2189,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,9.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.85,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.842562569053646,15.41074883013695,-1860.0,8.0,0.0,1.0,1.0],[15.41074883013695,16.306410593011947,-481.2188,9.0,0.0,1.0,1.0],[16.306410593011947,18.097734118761938,0.0,8.0,0.0,1.0,1.0],[18.097734118761938,38.39940074392852,227.8501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C488" t="n">
-        <v>227.85</v>
+        <v>227.8501</v>
       </c>
       <c r="D488" s="4" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6843,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[8.919905311090957,15.155385387502504,-1860.0,9.0,0.0,0.0,1.0],[15.155385387502504,18.273125425708276,-733.6842,9.0,0.0,0.0,1.0],[18.273125425708276,36.97956565494292,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>[[8.550657227158867,15.978622018906291,-1860.0,8.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,8.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.5,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[8.550657227158867,15.978622018906291,-1860.0,7.0,0.0,0.0,1.0],[15.978622018906291,17.464214977255775,-733.6843,8.0,0.0,0.0,1.0],[17.464214977255775,19.544045118945057,0.0,7.0,0.0,1.0,1.0],[19.544045118945057,30.83455160240114,1016.4999,9.0,0.0,0.0,1.0],[30.83455160240114,37.96539780247866,1678.65,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>[[6.6348014116466745,15.477132553586404,-1860.0,7.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,7.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.5,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.6348014116466745,15.477132553586404,-1860.0,6.0,0.0,0.0,1.0],[15.477132553586404,18.424576267566312,-733.6843,7.0,0.0,0.0,1.0],[18.424576267566312,20.38953874355292,0.0,6.0,0.0,1.0,1.0],[20.38953874355292,29.23186988549265,1016.4999,8.0,0.0,0.0,1.0],[29.23186988549265,39.056682265425685,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>[[5.014245738012112,15.464234063745074,-1860.0,6.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,6.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,6.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.5,7.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.014245738012112,15.464234063745074,-1860.0,5.0,0.0,0.0,1.0],[15.464234063745074,17.48681244937081,-733.6843,5.0,0.0,0.0,1.0],[17.48681244937081,19.509390834996545,0.0,5.0,0.0,1.0,1.0],[19.509390834996545,29.285186365520925,1016.4999,6.0,0.0,0.0,1.0],[29.285186365520925,38.38678910083674,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>[[4.80593404755855,15.80707791294227,-1860.0,5.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,5.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,5.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.5,6.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[4.80593404755855,15.80707791294227,-1860.0,3.0,0.0,0.0,1.0],[15.80707791294227,17.226580347185333,-733.6843,4.0,0.0,0.0,1.0],[17.226580347185333,19.355833998549926,0.0,4.0,0.0,1.0,1.0],[19.355833998549926,29.292351038251347,1016.4999,4.0,0.0,0.0,1.0],[29.292351038251347,39.93861929507431,1860.0,6.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,4.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,4.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.5,5.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.136988153927689,15.74779109715457,-1860.0,4.0,0.0,0.0,1.0],[15.74779109715457,18.82834679034947,-733.6843,3.0,0.0,0.0,1.0],[18.82834679034947,20.88205058581274,0.0,3.0,0.0,1.0,1.0],[20.88205058581274,30.123717665397443,1016.4999,4.0,0.0,0.0,1.0],[30.123717665397443,39.0231007790716,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,3.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,3.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.5,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,4.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.36313052343956,14.794150075647046,-1860.0,3.0,0.0,0.0,1.0],[14.794150075647046,18.162371344292577,-733.6843,2.0,0.0,0.0,1.0],[18.162371344292577,19.846481978615344,0.0,2.0,0.0,1.0,1.0],[19.846481978615344,30.287967911416487,1016.4999,4.0,0.0,0.0,1.0],[30.287967911416487,38.70852108303031,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>[[3.5918526248606204,18.159338784552713,-1860.0,3.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,3.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,3.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.5918526248606204,18.159338784552713,-1860.0,2.0,0.0,0.0,1.0],[18.159338784552713,29.88438862040245,0.0,2.0,0.0,1.0,1.0],[29.88438862040245,30.239693160882744,890.0,2.0,8.0,3.0,-1.0],[30.239693160882744,38.76700213240982,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>[[3.3390809357406224,17.87989495737115,-1860.0,2.0,0.0,0.0,1.0],[17.87989495737115,29.938130975308656,0.0,2.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[3.3390809357406224,17.87989495737115,-1860.0,1.0,0.0,0.0,1.0],[17.87989495737115,27.100898971088064,0.0,2.0,0.0,1.0,1.0],[27.100898971088064,29.938130975308656,0.0,0.0,0.0,1.0,1.0],[29.938130975308656,30.647438976363805,890.0,2.0,8.0,1.0,-1.0],[30.647438976363805,38.44982698797043,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>[[3.7020015909171002,17.18838567738531,-1860.0,1.0,0.0,0.0,1.0],[17.18838567738531,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,21.09233896557347,0.0,0.0,0.0,1.0,1.0],[21.09233896557347,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[3.7020015909171002,18.96290989928902,-1860.0,0.0,0.0,0.0,1.0],[18.96290989928902,26.77081647566535,0.0,1.0,0.0,1.0,1.0],[26.77081647566535,28.545340697569063,0.0,0.0,0.0,1.0,1.0],[28.545340697569063,29.61005523071129,0.0,1.0,0.0,1.0,1.0],[29.61005523071129,30.319864919472774,890.0,1.0,8.0,3.0,-1.0],[30.319864919472774,38.83758118461059,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>[[3.5676443893777567,24.40867347535547,-1860.0,1.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[3.5676443893777567,24.40867347535547,-1860.0,0.0,3.0,0.0,-1.0],[24.40867347535547,26.49277638395324,-1074.7922,0.0,3.0,0.0,-1.0],[26.49277638395324,29.271580262083603,0.0,0.0,2.0,1.0,-1.0],[29.271580262083603,37.95534238124098,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[3.8386374432748696,18.05559317772364,-1860.0,8.0,0.0,0.0,1.0],[18.05559317772364,19.909978708303917,-733.6842,8.0,0.0,0.0,1.0],[19.909978708303917,22.073428493980902,0.0,8.0,0.0,1.0,1.0],[22.073428493980902,30.418163381592137,1016.5,9.0,0.0,0.0,1.0],[30.418163381592137,34.4359986978494,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>[[3.852624596638034,17.856215668709932,-1860.0,7.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,7.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,7.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,8.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.852624596638034,17.856215668709932,-1860.0,6.0,0.0,0.0,1.0],[17.856215668709932,20.65693388312431,-733.6842,6.0,0.0,0.0,1.0],[20.65693388312431,22.835270272113274,0.0,6.0,0.0,1.0,1.0],[22.835270272113274,29.681470351792864,1016.5,7.0,0.0,0.0,1.0],[29.681470351792864,34.66052495519621,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>[[3.7308772600832674,17.193471352098303,-1860.0,6.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,6.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,6.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[3.7308772600832674,17.193471352098303,-1860.0,5.0,0.0,0.0,1.0],[17.193471352098303,20.63739077098587,-733.6842,5.0,0.0,0.0,1.0],[20.63739077098587,22.8289758557325,0.0,5.0,0.0,1.0,1.0],[22.8289758557325,29.716814693507636,1016.5,7.0,0.0,0.0,1.0],[29.716814693507636,34.72615203007137,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>[[3.7331082354585186,17.71248440328762,-1860.0,5.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,5.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,5.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,6.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
+          <t>[[3.7331082354585186,17.71248440328762,-1860.0,4.0,0.0,0.0,1.0],[17.71248440328762,20.197706833123902,-733.6842,4.0,0.0,0.0,1.0],[20.197706833123902,22.37227645923065,0.0,4.0,0.0,1.0,1.0],[22.37227645923065,30.75990215992811,1016.5,5.0,0.0,0.0,1.0],[30.75990215992811,34.487735804682536,1860.0,6.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>[[2.7878386935804578,16.8274046597201,-1860.0,4.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,4.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,4.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,5.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[2.7878386935804578,16.8274046597201,-1860.0,3.0,0.0,0.0,1.0],[16.8274046597201,20.337296151255007,-733.6842,3.0,0.0,0.0,1.0],[20.337296151255007,22.443231046175953,0.0,3.0,0.0,1.0,1.0],[22.443231046175953,30.164992327552756,1016.5,4.0,0.0,0.0,1.0],[30.164992327552756,37.53576445977606,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,3.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,3.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,4.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,5.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,5.0,9.0,1.0,-1.0]]</t>
+          <t>[[3.0552479507692314,18.04728954197882,-1860.0,3.0,0.0,0.0,1.0],[18.04728954197882,20.32868717542376,-733.6842,2.0,0.0,0.0,1.0],[20.32868717542376,22.6100848088687,0.0,2.0,0.0,1.0,1.0],[22.6100848088687,30.10610560447349,1016.5,3.0,0.0,0.0,1.0],[30.10610560447349,30.432019552108486,1725.15,4.0,9.0,1.0,-1.0],[30.432019552108486,35.320728766633344,1860.0,4.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,3.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
+          <t>[[2.828559302774794,17.378212630666162,-1860.0,2.0,0.0,0.0,1.0],[17.378212630666162,19.96481766673574,-733.6842,2.0,0.0,0.0,1.0],[19.96481766673574,22.228097073296617,0.0,2.0,0.0,1.0,1.0],[22.228097073296617,30.63456344052274,1016.5,2.0,0.0,0.0,1.0],[30.63456344052274,34.837796624135805,1860.0,3.0,9.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>[[2.760839825309646,18.24087360009212,-1860.0,1.0,0.0,0.0,1.0],[18.24087360009212,20.260008440281137,-1860.0,0.0,0.0,0.0,1.0],[20.260008440281137,22.279143280470155,0.0,0.0,0.0,1.0,1.0],[22.279143280470155,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,1.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[2.760839825309646,20.260008440281137,-1860.0,1.0,0.0,0.0,1.0],[20.260008440281137,26.990457907577863,0.0,0.0,0.0,1.0,1.0],[26.990457907577863,30.01916016786139,0.0,1.0,0.0,1.0,1.0],[30.01916016786139,30.355682641226228,890.0,0.0,8.0,1.0,-1.0],[30.355682641226228,36.07656468842845,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7922,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[2.7173527521838956,25.235552994200457,-1860.0,1.0,8.0,0.0,-1.0],[25.235552994200457,26.229003004877658,-1074.7923,0.0,8.0,1.0,-1.0],[26.229003004877658,29.209353036909263,0.0,0.0,7.0,2.0,-1.0],[29.209353036909263,30.202803047586464,890.0,0.0,7.0,0.0,-1.0],[30.202803047586464,35.501203104531534,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7922,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[3.033755273987173,25.887433501254144,-1860.0,1.0,7.0,0.0,-1.0],[25.887433501254144,26.590623600554668,-1074.7923,0.0,7.0,0.0,-1.0],[26.590623600554668,29.403383997756755,0.0,0.0,6.0,1.0,-1.0],[29.403383997756755,30.45816914670754,890.0,0.0,6.0,0.0,-1.0],[30.45816914670754,37.84166518936303,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7922,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[2.8988015939037197,25.708916748372157,-1860.0,1.0,6.0,0.0,-1.0],[25.708916748372157,27.070714668041912,-1074.7923,0.0,6.0,1.0,-1.0],[27.070714668041912,30.134759987298867,0.0,0.0,5.0,2.0,-1.0],[30.134759987298867,32.1774568668035,890.0,0.0,5.0,0.0,-1.0],[32.1774568668035,36.60330010573021,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,4.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[2.8543732486296145,26.25298389498913,-1860.0,1.0,4.0,0.0,-1.0],[26.25298389498913,29.480378466900785,0.0,0.0,3.0,2.0,-1.0],[29.480378466900785,42.79338107603637,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,3.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[2.7500164488974335,25.80571477074939,-1860.0,1.0,3.0,1.0,-1.0],[25.80571477074939,29.71346024902938,0.0,0.0,2.0,2.0,-1.0],[29.71346024902938,41.43669668386936,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,2.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[2.8374702402250533,25.5441163892489,-1860.0,1.0,2.0,1.0,-1.0],[25.5441163892489,29.193398806056305,0.0,0.0,1.0,2.0,-1.0],[29.193398806056305,42.9795768251065,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,28.769179416787427,0.0,0.0,1.0,2.0,-1.0],[28.769179416787427,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[2.9255890984794393,25.650125412853704,-1860.0,1.0,1.0,1.0,-1.0],[25.650125412853704,26.095704556272807,0.0,0.0,1.0,2.0,-1.0],[26.095704556272807,28.769179416787427,0.0,0.0,0.0,2.0,-1.0],[28.769179416787427,30.55149599046384,1860.0,0.0,0.0,0.0,-1.0],[30.55149599046384,47.037924296970665,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>[[2.901672760188005,21.739943251045954,-1860.0,9.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[2.901672760188005,21.739943251045954,-1860.0,8.0,0.0,0.0,1.0],[21.739943251045954,36.296788630345276,0.0,9.0,0.0,1.0,1.0],[36.296788630345276,45.28778136461839,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,8.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,8.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,8.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
+          <t>[[-1.4814532064442627,21.341401455558504,-1860.0,7.0,0.0,0.0,1.0],[21.341401455558504,36.081161758101956,0.0,7.0,0.0,1.0,1.0],[36.081161758101956,36.55663789689368,890.0,7.0,8.0,4.0,-1.0],[36.55663789689368,45.59068453393645,1860.0,8.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -12845,7 +12845,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,7.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,7.0,8.0,4.0,-1.0]]</t>
+          <t>[[-3.0126129553512984,20.656689076322607,-1860.0,6.0,0.0,0.0,1.0],[20.656689076322607,35.764754202922965,0.0,7.0,0.0,1.0,1.0],[35.764754202922965,36.268356373809645,890.0,7.0,8.0,4.0,-1.0],[36.268356373809645,46.8440019624299,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>[[-6.945689090104867,20.737775993827807,-1860.0,6.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,6.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,6.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[-6.945689090104867,20.737775993827807,-1860.0,5.0,0.0,0.0,1.0],[20.737775993827807,36.70900584994281,0.0,4.0,0.0,1.0,1.0],[36.70900584994281,37.24138017847997,890.0,4.0,8.0,4.0,-1.0],[37.24138017847997,45.75936943507464,1860.0,6.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>[[-11.39848926879086,21.134509917775084,-1860.0,5.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,5.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[-11.39848926879086,21.134509917775084,-1860.0,4.0,0.0,0.0,1.0],[21.134509917775084,36.544877953516846,0.0,4.0,0.0,1.0,1.0],[36.544877953516846,45.106193528928934,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>[[-14.292704665772625,21.431522159172808,-1860.0,4.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,4.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,4.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,4.0,8.0,4.0,-1.0]]</t>
+          <t>[[-14.292704665772625,21.431522159172808,-1860.0,3.0,0.0,0.0,1.0],[21.431522159172808,36.31661666956674,0.0,3.0,0.0,1.0,1.0],[36.31661666956674,36.9120204499825,890.0,3.0,8.0,4.0,-1.0],[36.9120204499825,44.65226959538734,1860.0,3.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,3.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,4.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[-14.821895666685798,21.07748771183696,-1860.0,3.0,0.0,0.0,1.0],[21.07748771183696,36.633887175863485,0.0,2.0,0.0,1.0,1.0],[36.633887175863485,37.830533288480915,1678.65,3.0,0.0,0.0,1.0],[37.830533288480915,44.412086907876756,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,2.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,2.0,8.0,4.0,-1.0]]</t>
+          <t>[[-15.800245108512707,22.319923039660644,-1860.0,2.0,0.0,0.0,1.0],[22.319923039660644,36.9326541631271,0.0,2.0,0.0,1.0,1.0],[36.9326541631271,37.567990298929985,890.0,1.0,8.0,4.0,-1.0],[37.567990298929985,47.09803233597332,1860.0,1.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>[[-14.74384651414167,18.903274861010285,-1860.0,1.0,0.0,0.0,1.0],[18.903274861010285,20.772559381852066,-1860.0,0.0,0.0,0.0,1.0],[20.772559381852066,23.264938742974433,0.0,0.0,0.0,1.0,1.0],[23.264938742974433,36.97302522914745,0.0,1.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,1.0,8.0,2.0,-1.0]]</t>
+          <t>[[-14.74384651414167,20.772559381852066,-1860.0,1.0,0.0,0.0,1.0],[20.772559381852066,30.742076826341535,0.0,1.0,0.0,1.0,1.0],[30.742076826341535,36.97302522914745,0.0,0.0,0.0,1.0,1.0],[36.97302522914745,46.94254267363692,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7922,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-14.12082405334311,28.901135585017197,-1860.0,1.0,8.0,0.0,-1.0],[28.901135585017197,33.08382610541334,-1074.7923,0.0,8.0,0.0,-1.0],[33.08382610541334,36.66898940861003,0.0,0.0,7.0,1.0,-1.0],[36.66898940861003,37.26651662580947,890.0,0.0,7.0,0.0,-1.0],[37.26651662580947,45.0343704494023,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[-14.23646373709396,26.961725408764313,-1860.0,1.0,7.0,0.0,-1.0],[26.961725408764313,36.51492868896334,0.0,0.0,7.0,1.0,-1.0],[36.51492868896334,44.873981559137476,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-14.952068224539028,27.02830181960754,-1860.0,1.0,6.0,0.0,-1.0],[27.02830181960754,35.29716258587884,0.0,0.0,6.0,1.0,-1.0],[35.29716258587884,48.018486841680826,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-14.795484139741667,26.930122698168134,-1860.0,1.0,5.0,0.0,-1.0],[26.930122698168134,36.7479125423822,0.0,0.0,5.0,1.0,-1.0],[36.7479125423822,45.9520905213329,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-14.081071884181647,26.556187147484586,-1860.0,1.0,4.0,0.0,-1.0],[26.556187147484586,36.86713346895214,0.0,0.0,4.0,1.0,-1.0],[36.86713346895214,45.96502728201175,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-14.299893828677986,26.90369554479748,-1860.0,1.0,3.0,0.0,-1.0],[26.90369554479748,35.57813541289757,0.0,0.0,3.0,1.0,-1.0],[35.57813541289757,39.373202855191366,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[-14.694086409330586,26.662162776441107,-1860.0,1.0,2.0,0.0,-1.0],[26.662162776441107,37.40404568183636,0.0,0.0,2.0,1.0,-1.0],[37.40404568183636,38.478233972375875,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -13259,7 +13259,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,37.53024845044009,0.0,0.0,1.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-14.880460656356275,26.7239166758429,-1860.0,1.0,1.0,0.0,-1.0],[26.7239166758429,33.748032329331075,0.0,0.0,1.0,1.0,-1.0],[33.748032329331075,37.53024845044009,0.0,0.0,0.0,1.0,-1.0],[37.53024845044009,38.61088162789981,1860.0,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-14.530285299219964,-0.49534455146290846,-1860.0,8.0,0.0,0.0,1.0],[-0.49534455146290846,24.455661222327414,-733.6842,8.0,0.0,0.0,1.0],[24.455661222327414,27.054724323763907,0.0,9.0,9.0,2.0,-1.0],[27.054724323763907,28.0943495643385,46.5,9.0,9.0,2.0,-1.0],[28.0943495643385,36.93116410922258,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -13558,11 +13558,11 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>[[-17.621245709939604,24.49811383490921,-733.6842,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-17.621245709939604,24.49811383490921,-733.6843,0.0,0.0,0.0,1.0],[24.49811383490921,27.306071137899128,0.0,0.0,9.0,3.0,-1.0],[27.306071137899128,27.86766259849711,1725.15,2.0,9.0,1.0,-1.0],[27.86766259849711,37.97630888926083,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C571" t="n">
-        <v>-733.6842</v>
+        <v>-733.6843</v>
       </c>
       <c r="D571" s="4" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[-19.143167850157166,22.295058623737592,-1860.0,1.0,8.0,1.0,-1.0],[22.295058623737592,23.95258768269338,-1074.7922,0.0,8.0,2.0,-1.0],[23.95258768269338,26.16262642796777,0.0,0.0,7.0,3.0,-1.0],[26.16262642796777,26.715136114286363,890.0001,0.0,7.0,3.0,-1.0],[26.715136114286363,35.555291095383915,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[-17.62081740897492,22.808883169583492,-1860.0,1.0,6.0,1.0,-1.0],[22.808883169583492,23.355230474699145,-1074.7922,0.0,6.0,2.0,-1.0],[23.355230474699145,26.086967000277422,0.0,0.0,5.0,3.0,-1.0],[26.086967000277422,26.633314305393075,890.0001,0.0,5.0,3.0,-1.0],[26.633314305393075,36.46756579747485,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>[[-17.212868878855527,22.451366393779875,-1860.0,1.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
+          <t>[[-17.212868878855527,22.451366393779875,-1860.0,0.0,4.0,1.0,-1.0],[22.451366393779875,24.08140345977859,-1074.7922,0.0,4.0,2.0,-1.0],[24.08140345977859,26.79813190310978,0.0,0.0,3.0,3.0,-1.0],[26.79813190310978,36.57835429910207,1860.0,0.0,3.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -13719,7 +13719,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[-17.920124183740267,23.327523859970636,-1860.0,1.0,3.0,1.0,-1.0],[23.327523859970636,23.824483474955105,-1074.7922,0.0,3.0,2.0,-1.0],[23.824483474955105,26.30928154987745,0.0,0.0,2.0,3.0,-1.0],[26.30928154987745,28.297120009815327,890.0001,0.0,2.0,3.0,-1.0],[28.297120009815327,31.27887769972213,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C578" t="n">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
+          <t>[[-18.453038871129028,22.97451571834117,-1860.0,1.0,3.0,0.0,-1.0],[22.97451571834117,23.473642882069722,-1074.7922,0.0,3.0,1.0,-1.0],[23.473642882069722,25.96927870071251,0.0,0.0,2.0,2.0,-1.0],[25.96927870071251,28.464914519355293,890.0001,0.0,2.0,2.0,-1.0],[28.464914519355293,30.960550337998075,1860.0,0.0,3.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-18.33661349057718,20.188767897113728,-1860.0,1.0,3.0,0.0,-1.0],[20.188767897113728,23.69107529599472,-1074.7922,0.0,3.0,0.0,-1.0],[23.69107529599472,26.192723438052575,0.0,0.0,2.0,1.0,-1.0],[26.192723438052575,29.194701208521998,890.0001,0.0,2.0,1.0,-1.0],[29.194701208521998,31.196019722168277,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C580" t="n">
@@ -13788,11 +13788,11 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>[[-17.325188007870292,-4.345116533696082,-1860.0,10.0,3.0,0.0,1.0],[-4.345116533696082,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.325188007870292,-3.864373145763704,-1860.0,1.0,3.0,0.0,-1.0],[-3.864373145763704,21.13428302671996,-1074.7922,0.0,3.0,0.0,-1.0],[21.13428302671996,23.53799996638185,0.0,0.0,2.0,1.0,-1.0],[23.53799996638185,29.787664009502766,890.0001,0.0,2.0,0.0,-1.0],[29.787664009502766,30.268407397435148,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C581" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D581" s="4" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="E581" s="4" t="inlineStr">
         <is>
-          <t>[0.2727272727,0,0.5353535354,0.0505050505,0,0.1313131313,0.0101010101,0]</t>
+          <t>[0.2828282828,0,0.5252525253,0.0505050505,0,0.1313131313,0.0101010101,0]</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>[[-17.656335934047352,-4.702199129227216,-1860.0,10.0,2.0,0.0,1.0],[-4.702199129227216,-4.203963098272595,-934.626,9.0,2.0,0.0,1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-17.656335934047352,-4.203963098272595,-1860.0,1.0,2.0,0.0,-1.0],[-4.203963098272595,24.19549066614078,0.0,0.0,2.0,1.0,-1.0],[24.19549066614078,31.669031130460088,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="E582" s="4" t="inlineStr">
         <is>
-          <t>[0.2626262626,0.0101010101,0,0.5757575758,0,0,0.1515151515,0]</t>
+          <t>[0.2727272727,0,0,0.5757575758,0,0,0.1515151515,0]</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>[[-18.4914812858837,-4.953106608294783,-1860.0,10.0,1.0,0.0,1.0],[-4.953106608294783,-4.4695932269523215,-934.626,9.0,1.0,0.0,1.0],[-4.4695932269523215,24.057696272252898,0.0,0.0,1.0,1.0,-1.0],[24.057696272252898,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-18.4914812858837,-4.4695932269523215,-1860.0,10.0,1.0,0.0,1.0],[-4.4695932269523215,21.640129365540595,0.0,0.0,1.0,1.0,-1.0],[21.640129365540595,24.057696272252898,0.0,0.0,0.0,1.0,-1.0],[24.057696272252898,26.95877656030767,1860.0,0.0,0.0,0.0,-1.0],[26.95877656030767,29.37634346701997,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C583" t="n">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="E583" s="4" t="inlineStr">
         <is>
-          <t>[0.2828282828,0.0101010101,0,0.595959596,0,0,0.1111111111,0]</t>
+          <t>[0.2929292929,0,0,0.595959596,0,0,0.1111111111,0]</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.733144258573962,-733.6842,9.0,1.0,0.0,1.0],[-4.733144258573962,-4.291158468990343,181.35,9.0,0.0,0.0,1.0],[-4.291158468990343,-3.849172679406724,1016.5,9.0,0.0,0.0,1.0],[-3.849172679406724,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-17.992717946082532,-10.47895952316101,-1860.0,9.0,1.0,0.0,1.0],[-10.47895952316101,-4.291158468990343,-733.6842,9.0,1.0,0.0,1.0],[-4.291158468990343,-0.31328636273777377,1860.0,0.0,0.0,0.0,-1.0],[-0.31328636273777377,25.763875222695745,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C584" t="n">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="E584" s="4" t="inlineStr">
         <is>
-          <t>[0.1717171717,0.1313131313,0,0,0.0202020202,0,0.6767676768,0]</t>
+          <t>[0.1717171717,0.1414141414,0,0,0,0,0.6868686869,0]</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-17.541201200501405,-3.9120485460436196,-1860.0,8.0,0.0,0.0,1.0],[-3.9120485460436196,15.872205307201554,-733.6842,8.0,0.0,0.0,1.0],[15.872205307201554,17.630805649712237,0.0,8.0,8.0,3.0,-1.0],[17.630805649712237,18.949755906595243,227.85,8.0,8.0,1.0,-1.0],[18.949755906595243,25.984157276637976,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4764,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5346,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.60846950085199,15.801729690813085,-1860.0,2.0,9.0,0.0,-1.0],[15.801729690813085,16.21267832853829,-1808.4765,1.0,9.0,1.0,-1.0],[16.21267832853829,17.445524241713905,-1607.5347,0.0,8.0,1.0,-1.0],[17.445524241713905,19.500267430339925,0.0,0.0,8.0,1.0,-1.0],[19.500267430339925,19.911216068065123,227.85,1.0,8.0,0.0,-1.0],[19.911216068065123,26.075445633943183,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>[[-13.089258523851058,14.852002584084783,-733.6842,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-13.089258523851058,14.852002584084783,-733.6844,0.0,0.0,0.0,1.0],[14.852002584084783,16.44864607596683,0.0,0.0,9.0,1.0,-1.0],[16.44864607596683,18.44445044081939,46.5,1.0,9.0,0.0,-1.0],[18.44445044081939,20.440254805671948,227.85,0.0,8.0,0.0,-1.0],[20.440254805671948,26.42766790022963,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>[[-13.582656085878643,13.324792810262409,-785.2077,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,0.0,9.0,0.0,-1.0]]</t>
+          <t>[[-13.582656085878643,13.324792810262409,-785.2079,0.0,0.0,0.0,1.0],[13.324792810262409,14.931207669733517,0.0,0.0,8.0,1.0,-1.0],[14.931207669733517,16.537622529204626,181.35,0.0,8.0,1.0,-1.0],[16.537622529204626,26.17611168603127,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,8.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[-14.065811190081442,12.98551863422074,-1860.0,1.0,7.0,0.0,-1.0],[12.98551863422074,14.703063384970084,0.0,0.0,7.0,1.0,-1.0],[14.703063384970084,16.420608135719426,181.35,0.0,7.0,1.0,-1.0],[16.420608135719426,28.443421390964843,1860.0,1.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[-13.638813213151954,13.116121458189317,-1860.0,1.0,7.0,0.0,-1.0],[13.116121458189317,14.549421529868313,0.0,0.0,6.0,1.0,-1.0],[14.549421529868313,15.98272160154731,181.35,0.0,6.0,1.0,-1.0],[15.98272160154731,33.66008915225493,1860.0,1.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[-13.943712320387379,13.713081043081251,-1860.0,1.0,6.0,0.0,-1.0],[13.713081043081251,15.19469497326707,0.0,0.0,5.0,1.0,-1.0],[15.19469497326707,16.67630890345289,181.35,0.0,5.0,1.0,-1.0],[16.67630890345289,34.949547375744665,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[-13.458419018136013,13.489774983372822,-1860.0,1.0,5.0,0.0,-1.0],[13.489774983372822,14.933428233453654,0.0,0.0,4.0,1.0,-1.0],[14.933428233453654,16.377081483534486,181.35,0.0,4.0,1.0,-1.0],[16.377081483534486,34.18213823453139,1860.0,1.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -14271,7 +14271,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[-13.1795604552901,13.627744745986098,-1860.0,1.0,4.0,0.0,-1.0],[13.627744745986098,15.014329497776243,0.0,0.0,3.0,1.0,-1.0],[15.014329497776243,16.863109166829773,181.35,0.0,3.0,1.0,-1.0],[16.863109166829773,32.577736353784786,1860.0,1.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C602" t="n">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,3.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[-13.491455190456973,13.044121775419748,-1860.0,1.0,2.0,0.0,-1.0],[13.044121775419748,14.93952013012523,0.0,0.0,2.0,1.0,-1.0],[14.93952013012523,16.361068896154343,181.35,0.0,2.0,1.0,-1.0],[16.361068896154343,33.41965408850366,1860.0,1.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C603" t="n">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>[[-13.798500505043743,13.636940747544651,-1860.0,1.0,2.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[-13.798500505043743,13.155617216797486,-1860.0,1.0,2.0,0.0,-1.0],[13.155617216797486,13.636940747544651,-1860.0,1.0,1.0,0.0,-1.0],[13.636940747544651,15.080911339786143,0.0,0.0,1.0,1.0,-1.0],[15.080911339786143,17.0062054627748,181.35,0.0,1.0,1.0,-1.0],[17.0062054627748,33.852529038925574,1860.0,1.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>[[-13.09164031997929,11.850995537604339,-1860.0,1.0,1.0,0.0,-1.0],[11.850995537604339,16.167990205263045,-1860.0,0.0,1.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.09164031997929,16.167990205263045,-1860.0,1.0,0.0,0.0,-1.0],[16.167990205263045,18.086654502000243,0.0,0.0,0.0,1.0,-1.0],[18.086654502000243,34.39530102426646,181.35,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,14.491377236458941,0.0,0.0,1.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[-13.674291219793194,12.104456180844352,-1860.0,1.0,1.0,0.0,-1.0],[12.104456180844352,13.059224603090186,0.0,0.0,1.0,1.0,-1.0],[13.059224603090186,14.491377236458941,0.0,0.0,0.0,1.0,-1.0],[14.491377236458941,33.58674568137564,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>[[-13.252081670763886,-3.6843685574201412,-1860.0,10.0,0.0,0.0,1.0],[-3.6843685574201412,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[-13.252081670763886,-3.2059829017529538,-1860.0,10.0,0.0,0.0,1.0],[-3.2059829017529538,34.108098240287646,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="E608" s="4" t="inlineStr">
         <is>
-          <t>[0.202020202,0,0,0.797979798,0,0,0,0]</t>
+          <t>[0.2121212121,0,0,0.7878787879,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>[[-13.04004209056855,7.333007074773429,-1860.0,8.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[-13.04004209056855,7.333007074773429,-1860.0,9.0,0.0,0.0,1.0],[7.333007074773429,24.227730772861896,0.0,9.0,0.0,1.0,1.0],[24.227730772861896,36.15341808915964,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C610" t="n">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>[[-13.79743690539747,6.295463740289181,-1860.0,7.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.79743690539747,6.295463740289181,-1860.0,8.0,0.0,0.0,1.0],[6.295463740289181,25.43155959332409,0.0,8.0,0.0,1.0,1.0],[25.43155959332409,30.693985952908683,1678.65,9.0,0.0,0.0,1.0],[30.693985952908683,33.56440033086392,1860.0,9.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,6.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.477651010691503,6.5141244327980665,-1860.0,7.0,0.0,0.0,1.0],[6.5141244327980665,25.5539105694548,0.0,7.0,0.0,1.0,1.0],[25.5539105694548,29.36186779678615,1678.65,8.0,0.0,0.0,1.0],[29.36186779678615,33.645819677533915,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>[[-13.63629985442631,6.973972321648217,-1860.0,5.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
+          <t>[[-13.63629985442631,6.973972321648217,-1860.0,6.0,0.0,0.0,1.0],[6.973972321648217,23.270466600404824,0.0,6.0,0.0,1.0,1.0],[23.270466600404824,29.98078777401048,1678.65,7.0,0.0,0.0,1.0],[29.98078777401048,33.81525701607086,1860.0,7.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>[[-12.677717925832917,6.72792425719083,-1860.0,4.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
+          <t>[[-12.677717925832917,6.72792425719083,-1860.0,5.0,0.0,0.0,1.0],[6.72792425719083,24.28541004183137,0.0,5.0,0.0,1.0,1.0],[24.28541004183137,29.829879236981007,1678.65,6.0,0.0,0.0,1.0],[29.829879236981007,33.064152934151636,1860.0,6.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.872993494586886,6.501520124567865,-1860.0,2.0,0.0,0.0,1.0],[6.501520124567865,23.75940285707852,0.0,2.0,0.0,1.0,1.0],[23.75940285707852,30.819445793105608,1678.65,3.0,0.0,0.0,1.0],[30.819445793105608,33.95724265356209,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>[[-4.881552307742827,6.067825225044898,-1860.0,1.0,0.0,0.0,1.0],[6.067825225044898,6.849923620244021,-1860.0,0.0,0.0,0.0,1.0],[6.849923620244021,7.632022015443144,0.0,0.0,0.0,1.0,1.0],[7.632022015443144,24.05608831462473,0.0,1.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,2.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[-4.881552307742827,6.849923620244021,-1860.0,1.0,0.0,0.0,1.0],[6.849923620244021,19.36349794342999,0.0,1.0,0.0,1.0,1.0],[19.36349794342999,24.05608831462473,0.0,0.0,0.0,1.0,1.0],[24.05608831462473,29.921826278618152,1678.65,1.0,0.0,0.0,1.0],[29.921826278618152,33.83231825461377,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C618" t="n">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,1.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[4.830693769807795,23.767145310053905,0.0,0.0,0.0,1.0,1.0],[23.767145310053905,29.778717227592352,1678.65,0.0,0.0,0.0,1.0],[29.778717227592352,34.58797476162311,1860.0,0.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7922,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[4.967796904095384,24.25360834401886,-1860.0,1.0,8.0,1.0,-1.0],[24.25360834401886,27.760119514914038,-1074.7923,0.0,8.0,0.0,-1.0],[27.760119514914038,30.828316789447317,0.0,0.0,7.0,1.0,-1.0],[30.828316789447317,31.266630685809215,890.0,0.0,7.0,1.0,-1.0],[31.266630685809215,48.36087264392321,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7922,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[4.591093059070173,24.979428511129314,-1860.0,1.0,8.0,0.0,-1.0],[24.979428511129314,26.921174744658757,-1074.7923,0.0,8.0,0.0,-1.0],[26.921174744658757,29.83379409495292,0.0,0.0,7.0,1.0,-1.0],[29.83379409495292,52.64931233892387,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7922,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
+          <t>[[4.863091593793426,24.239072919225187,-1860.0,1.0,7.0,0.0,-1.0],[24.239072919225187,24.74896716463129,-1074.7923,0.0,7.0,1.0,-1.0],[24.74896716463129,27.808332637067878,0.0,0.0,6.0,2.0,-1.0],[27.808332637067878,30.357803864098372,890.0,0.0,6.0,0.0,-1.0],[30.357803864098372,55.34262188899722,1860.0,0.0,6.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7922,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.0936561679229095,24.37261782561748,-1860.0,1.0,6.0,0.0,-1.0],[24.37261782561748,24.893670843393007,-1074.7923,0.0,6.0,1.0,-1.0],[24.893670843393007,27.49893593227065,0.0,0.0,5.0,2.0,-1.0],[27.49893593227065,31.146307056699357,890.0,0.0,5.0,0.0,-1.0],[31.146307056699357,56.67790492770027,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7922,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[5.037254937043609,24.0029293191894,-1860.0,1.0,5.0,0.0,-1.0],[24.0029293191894,24.52975360758234,-1074.7923,0.0,5.0,0.0,-1.0],[24.52975360758234,27.16387504954703,0.0,0.0,4.0,1.0,-1.0],[27.16387504954703,30.324820779904663,890.0,0.0,4.0,0.0,-1.0],[30.324820779904663,57.192859487944524,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>[[5.0102696048923185,24.62393903975309,-1860.0,1.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,3.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[5.0102696048923185,24.62393903975309,-1860.0,0.0,3.0,0.0,-1.0],[24.62393903975309,27.720834213678472,0.0,0.0,2.0,1.0,-1.0],[27.720834213678472,56.10903997466116,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,2.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[4.857921714079791,24.36676019334334,-1860.0,1.0,2.0,0.0,-1.0],[24.36676019334334,27.960493597418203,0.0,0.0,1.0,2.0,-1.0],[27.960493597418203,55.6835798574243,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C629" t="n">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,28.179347067774426,0.0,0.0,1.0,1.0,-1.0],[28.179347067774426,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.008691202990625,25.15708760715045,-1860.0,1.0,1.0,0.0,-1.0],[25.15708760715045,25.660797517254448,0.0,0.0,1.0,1.0,-1.0],[25.660797517254448,28.179347067774426,0.0,0.0,0.0,1.0,-1.0],[28.179347067774426,30.697896618294404,1860.0,0.0,0.0,0.0,-1.0],[30.697896618294404,54.8759723032862,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>[[5.100775592433641,16.0172212623511,-1860.0,8.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6842,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,8.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.100775592433641,16.0172212623511,-1860.0,7.0,0.0,0.0,1.0],[16.0172212623511,21.97164617321517,-733.6843,8.0,0.0,0.0,1.0],[21.97164617321517,24.452656552741864,0.0,7.0,0.0,1.0,1.0],[24.452656552741864,33.384293919037965,1016.5,9.0,0.0,0.0,1.0],[33.384293919037965,54.224781107062206,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -15030,7 +15030,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>[[4.992893814078394,16.03823118937139,-1860.0,7.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6842,7.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,7.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,8.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
+          <t>[[4.992893814078394,16.03823118937139,-1860.0,6.0,0.0,0.0,1.0],[16.03823118937139,22.349852546681674,-733.6843,6.0,0.0,0.0,1.0],[22.349852546681674,24.979694778894295,0.0,6.0,0.0,1.0,1.0],[24.979694778894295,34.44712681485972,1016.5,7.0,0.0,0.0,1.0],[34.44712681485972,57.06377001188824,1860.0,8.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>[[5.024863077657301,15.319835764701056,-1860.0,6.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6842,6.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,6.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,7.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,7.0,1.0,0.0,1.0]]</t>
+          <t>[[5.024863077657301,15.319835764701056,-1860.0,5.0,0.0,0.0,1.0],[15.319835764701056,20.98207074257512,-733.6843,5.0,0.0,0.0,1.0],[20.98207074257512,23.55581391433606,0.0,5.0,0.0,1.0,1.0],[23.55581391433606,33.850786601379816,1016.5,6.0,0.0,0.0,1.0],[33.850786601379816,55.984977878523885,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>[[5.075011052085991,15.038088377698118,-1860.0,5.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6842,5.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,5.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,6.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
+          <t>[[5.075011052085991,15.038088377698118,-1860.0,3.0,0.0,0.0,1.0],[15.038088377698118,21.8549307583801,-733.6843,4.0,0.0,0.0,1.0],[21.8549307583801,24.476793212488555,0.0,4.0,0.0,1.0,1.0],[24.476793212488555,32.342380574813916,1016.5,4.0,0.0,0.0,1.0],[32.342380574813916,56.98788764343339,1860.0,6.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>[[5.049031821720391,16.308173777922356,-1860.0,4.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6842,4.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,4.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,5.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,5.0,1.0,0.0,1.0]]</t>
+          <t>[[5.049031821720391,16.308173777922356,-1860.0,3.0,0.0,0.0,1.0],[16.308173777922356,21.425965576195974,-733.6843,3.0,0.0,0.0,1.0],[21.425965576195974,23.47308229550542,0.0,3.0,0.0,1.0,1.0],[23.47308229550542,33.1968867122253,1016.5,4.0,0.0,0.0,1.0],[33.1968867122253,55.71517062462923,1860.0,4.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6842,3.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,3.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,4.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,4.0,1.0,0.0,1.0]]</t>
+          <t>[[5.062513955862454,15.982296530286714,-1860.0,3.0,0.0,0.0,1.0],[15.982296530286714,21.442187817498844,-733.6843,2.0,0.0,0.0,1.0],[21.442187817498844,23.92395658441345,0.0,2.0,0.0,1.0,1.0],[23.92395658441345,32.85832414530603,1016.5,3.0,0.0,0.0,1.0],[32.85832414530603,54.20153554077163,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>[[5.149124104043402,15.561247222066516,-1860.0,2.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6842,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,3.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
+          <t>[[5.149124104043402,15.561247222066516,-1860.0,1.0,0.0,0.0,1.0],[15.561247222066516,20.76730878107807,-733.6843,2.0,0.0,0.0,1.0],[20.76730878107807,22.849733404682695,0.0,2.0,0.0,1.0,1.0],[22.849733404682695,34.82367499040927,1016.5,2.0,0.0,0.0,1.0],[34.82367499040927,56.68913353825781,1860.0,3.0,1.0,0.0,1.0]]</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>[[12.453519927190623,21.744944337543433,-1860.0,2.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6842,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,3.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
+          <t>[[12.453519927190623,21.744944337543433,-1860.0,1.0,0.0,0.0,1.0],[21.744944337543433,30.1514711850055,-733.6843,2.0,0.0,0.0,1.0],[30.1514711850055,33.248612655123104,0.0,2.0,0.0,1.0,1.0],[33.248612655123104,38.557998032467566,1016.5,2.0,0.0,0.0,1.0],[38.557998032467566,56.25594929028244,1860.0,3.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6842,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
+          <t>[[14.359218967168415,21.612356946148715,-1860.0,1.0,0.0,0.0,1.0],[21.612356946148715,29.718805275597287,-733.6843,1.0,0.0,0.0,1.0],[29.718805275597287,33.13204667747037,0.0,1.0,0.0,1.0,1.0],[33.13204667747037,38.25190878027999,1016.5,2.0,0.0,0.0,1.0],[38.25190878027999,56.59808131534781,1860.0,2.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -15214,11 +15214,11 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>[[15.468694675348974,30.718274688690588,-733.6842,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,1.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
+          <t>[[15.468694675348974,27.909141528338186,-733.6844,0.0,0.0,0.0,1.0],[27.909141528338186,30.718274688690588,-733.6843,0.0,0.0,0.0,1.0],[30.718274688690588,34.33001732342939,0.0,0.0,0.0,1.0,1.0],[34.33001732342939,39.94828364413419,1016.5,0.0,0.0,0.0,1.0],[39.94828364413419,55.19786365747581,1860.0,1.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C643" t="n">
-        <v>-733.6842</v>
+        <v>-733.6844</v>
       </c>
       <c r="D643" s="4" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>[[15.433312970188537,39.84677261349068,-0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[15.433312970188537,39.84677261349068,0.0,0.0,0.0,1.0,1.0],[39.84677261349068,40.26056006507207,890.0,0.0,8.0,2.0,-1.0],[40.26056006507207,56.398270676746364,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C644" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>[[15.37756823849231,39.594717827547726,-0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[15.37756823849231,39.594717827547726,0.0,0.0,0.0,1.0,1.0],[39.594717827547726,40.00517799007409,890.0,0.0,8.0,1.0,-1.0],[40.00517799007409,56.01312432860224,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C645" t="n">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7922,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[15.010904772646576,34.85850389486829,-1860.0,1.0,8.0,0.0,-1.0],[34.85850389486829,35.70308258092028,-1074.7921,0.0,8.0,0.0,-1.0],[35.70308258092028,39.50368666815423,0.0,0.0,7.0,1.0,-1.0],[39.50368666815423,40.34826535420621,890.0001,0.0,7.0,1.0,-1.0],[40.34826535420621,56.81754973221998,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7922,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[15.740607208219268,33.310480943479895,-1860.0,1.0,7.0,0.0,-1.0],[33.310480943479895,34.87224749772528,-1074.7921,0.0,7.0,0.0,-1.0],[34.87224749772528,38.776663883338756,0.0,0.0,6.0,1.0,-1.0],[38.776663883338756,54.39432942579264,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C647" t="n">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7922,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.001412810804764,34.90126157782096,-1860.0,1.0,6.0,0.0,-1.0],[34.90126157782096,35.31584176046713,-1074.7921,0.0,6.0,0.0,-1.0],[35.31584176046713,39.461643586928844,0.0,0.0,5.0,1.0,-1.0],[39.461643586928844,56.04485089277568,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7922,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.093806695932079,32.88485232806318,-1860.0,1.0,5.0,0.0,-1.0],[32.88485232806318,35.31090400517196,-1074.7921,0.0,5.0,0.0,-1.0],[35.31090400517196,38.949981520835145,0.0,0.0,4.0,1.0,-1.0],[38.949981520835145,39.75866541320474,890.0001,0.0,4.0,0.0,-1.0],[39.75866541320474,55.12365936822706,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C649" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7922,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[15.081344426556138,27.67290722465218,-1860.0,1.0,5.0,0.0,-1.0],[27.67290722465218,34.14856809224443,-1074.7921,0.0,5.0,0.0,-1.0],[34.14856809224443,38.105916400217474,0.0,0.0,4.0,1.0,-1.0],[38.105916400217474,39.54495214857131,890.0001,0.0,4.0,0.0,-1.0],[39.54495214857131,50.697479198313516,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7922,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[14.77468045156605,30.73523133969364,-1860.0,1.0,4.0,0.0,-1.0],[30.73523133969364,33.39532315438157,-1074.7921,0.0,4.0,0.0,-1.0],[33.39532315438157,36.72043792274149,0.0,0.0,3.0,1.0,-1.0],[36.72043792274149,39.38052973742942,890.0001,0.0,3.0,0.0,-1.0],[39.38052973742942,47.6933166583292,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -15421,11 +15421,11 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7922,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.751388302345143,29.827492769927723,-1860.0,1.0,3.0,0.0,-1.0],[29.827492769927723,34.519527592455255,-1074.7921,0.0,3.0,0.0,-1.0],[34.519527592455255,38.20612638158402,0.0,0.0,2.0,1.0,-1.0],[38.20612638158402,39.88185310391528,890.0001,0.0,2.0,0.0,-1.0],[39.88185310391528,48.930777404504084,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C652" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D652" s="4" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,-0.0,0.0,1.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[15.878218514382214,30.989303834002033,-1860.0,1.0,2.0,0.0,-1.0],[30.989303834002033,36.77652799896281,0.0,0.0,2.0,1.0,-1.0],[36.77652799896281,47.707951421666515,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C653" t="n">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,33.49693462319364,-0.0,0.0,1.0,1.0,-1.0],[33.49693462319364,37.09533876172902,0.0,0.0,0.0,1.0,-1.0],[37.09533876172902,37.42246641068678,1860.0,0.0,0.0,0.0,-1.0],[37.42246641068678,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[15.177786281558943,30.55278578257377,-1860.0,1.0,1.0,0.0,-1.0],[30.55278578257377,37.09533876172902,0.0,0.0,1.0,1.0,-1.0],[37.09533876172902,47.56342352837742,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.774416554386047,29.372975476177313,-1860.0,1.0,0.0,0.0,-1.0],[29.372975476177313,46.3711741284164,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>[[15.134100086077074,23.042745215831857,-1860.0,9.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[15.134100086077074,23.042745215831857,-1860.0,7.0,0.0,1.0,1.0],[23.042745215831857,23.651102533505302,-733.6842,9.0,0.0,1.0,1.0],[23.651102533505302,45.2477873109126,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>[[15.59322238749069,24.223458261848442,-1860.0,8.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,8.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.65,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[15.59322238749069,24.223458261848442,-1860.0,7.0,0.0,0.0,1.0],[24.223458261848442,28.230353489228833,-733.6842,8.0,0.0,0.0,1.0],[28.230353489228833,31.312580587213745,0.0,7.0,0.0,1.0,1.0],[31.312580587213745,35.011253104795635,1016.5,9.0,0.0,0.0,1.0],[35.011253104795635,46.10727065754133,1678.6501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>[[15.757141210793566,23.390326556607754,-1860.0,7.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,7.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,9.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.757141210793566,23.390326556607754,-1860.0,6.0,0.0,0.0,1.0],[23.390326556607754,29.191547419426534,-733.6842,7.0,0.0,0.0,1.0],[29.191547419426534,32.550148971584775,0.0,6.0,0.0,1.0,1.0],[32.550148971584775,34.68744086841275,1016.5,8.0,0.0,0.0,1.0],[34.68744086841275,35.29809569607788,1725.15,8.0,9.0,2.0,-1.0],[35.29809569607788,45.98455518021775,1860.0,9.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -15605,7 +15605,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,6.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,6.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.412417416526957,23.307904819403745,-1860.0,6.0,0.0,0.0,1.0],[23.307904819403745,28.9005417297748,-733.6842,5.0,0.0,0.0,1.0],[28.9005417297748,32.19032814764013,0.0,5.0,0.0,1.0,1.0],[32.19032814764013,34.49317864014586,1016.5,7.0,0.0,0.0,1.0],[34.49317864014586,34.82215728193239,1725.15,8.0,9.0,2.0,-1.0],[34.82215728193239,47.9813029533937,1860.0,8.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,5.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,5.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,6.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.480965077534327,22.737637267054176,-1860.0,5.0,0.0,0.0,1.0],[22.737637267054176,28.612086182379766,-733.6842,4.0,0.0,0.0,1.0],[28.612086182379766,31.722088549316844,0.0,4.0,0.0,1.0,1.0],[31.722088549316844,34.140979279156795,1016.5,4.0,0.0,0.0,1.0],[34.140979279156795,34.832090916253925,1725.15,7.0,9.0,2.0,-1.0],[34.832090916253925,49.69099111384219,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C661" t="n">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>[[15.301263784589397,19.08752914840641,-1860.0,4.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,4.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,4.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,5.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,6.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,6.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.301263784589397,19.08752914840641,-1860.0,3.0,0.0,0.0,1.0],[19.08752914840641,28.381089586866356,-733.6842,3.0,0.0,0.0,1.0],[28.381089586866356,31.478943066353004,0.0,3.0,0.0,1.0,1.0],[31.478943066353004,34.23259060367447,1016.5,4.0,0.0,0.0,1.0],[34.23259060367447,34.57679654583965,1725.15,5.0,9.0,2.0,-1.0],[34.57679654583965,49.37765205894252,1860.0,5.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>[[15.319409572035747,27.97448690278405,-1860.0,4.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,-0.0,4.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,5.0,9.0,2.0,-1.0]]</t>
+          <t>[[15.319409572035747,27.97448690278405,-1860.0,3.0,0.0,0.0,1.0],[27.97448690278405,35.07367662491115,0.0,3.0,0.0,1.0,1.0],[35.07367662491115,45.87679141945238,1860.0,4.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>[[15.875033184735637,27.98434482472492,-1860.0,3.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,-0.0,3.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,3.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[15.875033184735637,27.98434482472492,-1860.0,1.0,0.0,0.0,1.0],[27.98434482472492,34.644466226719025,0.0,2.0,0.0,1.0,1.0],[34.644466226719025,35.249931808718486,890.0,2.0,8.0,4.0,-1.0],[35.249931808718486,45.84557949370911,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>[[7.40668292284102,32.0729403673296,-1860.0,3.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7923,3.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,2.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.40668292284102,32.0729403673296,-1860.0,1.0,0.0,0.0,1.0],[32.0729403673296,32.458350639899734,-1074.7922,2.0,9.0,2.0,-1.0],[32.458350639899734,35.92704309303094,0.0,2.0,7.0,1.0,-1.0],[35.92704309303094,36.31245336560107,1071.35,2.0,7.0,1.0,-1.0],[36.31245336560107,45.56229990728429,1860.0,1.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C665" t="n">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>[[7.342765194682687,31.577713215216676,-1860.0,2.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,2.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.342765194682687,31.577713215216676,-1860.0,1.0,0.0,0.0,1.0],[31.577713215216676,35.09568954077806,0.0,2.0,8.0,3.0,-1.0],[35.09568954077806,35.87746205756948,890.0,2.0,8.0,3.0,-1.0],[35.87746205756948,46.040504775857926,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C666" t="n">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>[[6.9510885856512665,31.628901835611902,-1860.0,1.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7923,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[6.9510885856512665,31.628901835611902,-1860.0,0.0,0.0,0.0,1.0],[31.628901835611902,32.412324478467795,-1074.7922,1.0,9.0,2.0,-1.0],[32.412324478467795,35.937726371319314,0.0,1.0,8.0,3.0,-1.0],[35.937726371319314,36.32943769274726,890.0,1.0,8.0,3.0,-1.0],[36.32943769274726,45.73050940701798,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C667" t="n">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>[[7.168922608885759,34.13795349870542,-0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
+          <t>[[7.168922608885759,34.13795349870542,0.0,0.0,0.0,1.0,1.0],[34.13795349870542,35.382678001312485,890.0,0.0,8.0,3.0,-1.0],[35.382678001312485,48.24483119491879,1860.0,0.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7923,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.937129663466531,29.632533295052465,-1860.0,1.0,8.0,2.0,-1.0],[29.632533295052465,30.037808359902215,-1074.7922,0.0,8.0,2.0,-1.0],[30.037808359902215,33.2800088787002,0.0,0.0,7.0,3.0,-1.0],[33.2800088787002,34.901109138099194,890.0,0.0,7.0,3.0,-1.0],[34.901109138099194,47.05936108359166,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7923,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[7.417254319787326,28.14665665296946,-1860.0,1.0,8.0,0.0,-1.0],[28.14665665296946,29.166135456240713,-1074.7922,0.0,8.0,1.0,-1.0],[29.166135456240713,32.56439813381156,0.0,0.0,7.0,2.0,-1.0],[32.56439813381156,34.26352947259698,890.0,0.0,7.0,2.0,-1.0],[34.26352947259698,41.06005482773866,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7923,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[7.22917318841805,27.595961505092752,-1860.0,1.0,8.0,0.0,-1.0],[27.595961505092752,28.868885774884923,-1074.7922,0.0,8.0,1.0,-1.0],[28.868885774884923,32.05119644936534,0.0,0.0,7.0,2.0,-1.0],[32.05119644936534,32.68765858426143,890.0,0.0,7.0,1.0,-1.0],[32.68765858426143,38.734048865774234,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7923,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[7.07979083730359,27.449390922018026,-1860.0,1.0,7.0,0.0,-1.0],[27.449390922018026,28.139885840143936,-1074.7922,0.0,7.0,0.0,-1.0],[28.139885840143936,30.90186551264759,0.0,0.0,6.0,1.0,-1.0],[30.90186551264759,32.28285534889942,890.0,0.0,6.0,1.0,-1.0],[32.28285534889942,41.25928928453629,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7923,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
+          <t>[[6.855898764790677,27.84861379160557,-1860.0,1.0,5.0,0.0,-1.0],[27.84861379160557,28.23029951936584,-1074.7922,0.0,5.0,0.0,-1.0],[28.23029951936584,31.665471069208277,0.0,0.0,4.0,1.0,-1.0],[31.665471069208277,44.642785813057486,1860.0,0.0,4.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7923,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[6.422290305579039,28.485493283549324,-1860.0,1.0,4.0,0.0,-1.0],[28.485493283549324,29.233398469243234,-1074.7922,0.0,4.0,1.0,-1.0],[29.233398469243234,32.225019212018864,0.0,0.0,3.0,2.0,-1.0],[32.225019212018864,32.59897180486582,890.0,0.0,3.0,2.0,-1.0],[32.59897180486582,43.443596997427484,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7923,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.070425708983416,28.78504312001573,-1860.0,1.0,3.0,0.0,-1.0],[28.78504312001573,29.49699778922991,-1074.7922,0.0,3.0,0.0,-1.0],[29.49699778922991,32.70079380069369,0.0,0.0,2.0,1.0,-1.0],[32.70079380069369,35.548612477550385,890.0,0.0,2.0,1.0,-1.0],[35.548612477550385,42.31218183508504,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4765,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7923,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[7.116012772742423,24.391889204313728,-1860.0,9.0,3.0,2.0,1.0],[24.391889204313728,25.494604721222537,-1808.4764,9.0,3.0,2.0,1.0],[25.494604721222537,29.537894949888162,-1074.7922,0.0,3.0,0.0,-1.0],[29.537894949888162,32.47846966164498,0.0,0.0,2.0,1.0,-1.0],[32.47846966164498,33.94875701752339,890.0,0.0,2.0,1.0,-1.0],[33.94875701752339,43.50562483073305,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C677" t="n">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7923,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[6.815609251831358,24.449312384869366,-1860.0,10.0,2.0,0.0,1.0],[24.449312384869366,29.847384772534063,-1074.7922,0.0,2.0,0.0,-1.0],[29.847384772534063,33.08622820513288,0.0,0.0,1.0,1.0,-1.0],[33.08622820513288,37.764557607775615,890.0,0.0,1.0,0.0,-1.0],[37.764557607775615,42.44288701041835,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -16065,11 +16065,11 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4765,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.826923434851289,23.88813063111298,-1860.0,9.0,1.0,1.0,1.0],[23.88813063111298,24.27588534011893,-1808.4764,9.0,1.0,1.0,1.0],[24.27588534011893,26.990168303160562,0.0,9.0,1.0,1.0,1.0],[26.990168303160562,27.37792301216651,46.5,10.0,1.0,0.0,1.0],[27.37792301216651,45.214639626440096,890.0001,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C680" t="n">
-        <v>890</v>
+        <v>890.0001</v>
       </c>
       <c r="D680" s="4" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,-0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[7.224868158370898,26.004920315026013,-1860.0,9.0,0.0,1.0,1.0],[26.004920315026013,36.68377350214362,0.0,9.0,0.0,1.0,1.0],[36.68377350214362,43.680263521289646,662.15,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,-0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,890.0,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
+          <t>[[7.185375415205917,26.35311924123216,-1860.0,8.0,0.0,1.0,1.0],[26.35311924123216,35.03285229452706,0.0,8.0,0.0,1.0,1.0],[35.03285229452706,35.75616338230164,889.9999,8.0,8.0,4.0,-1.0],[35.75616338230164,42.98927426004739,1860.0,8.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,-0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,890.0,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
+          <t>[[7.121039743720916,26.710328764446032,-1860.0,7.0,0.0,1.0,1.0],[26.710328764446032,36.5049732748086,0.0,7.0,0.0,1.0,1.0],[36.5049732748086,36.8677378863035,889.9999,7.0,8.0,3.0,-1.0],[36.8677378863035,43.03473628171697,1860.0,7.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C684" t="n">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>[[7.019629382299565,26.105943105379367,-1860.0,6.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,-0.0,6.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,890.0,6.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,6.0,8.0,4.0,-1.0]]</t>
+          <t>[[7.019629382299565,26.105943105379367,-1860.0,5.0,0.0,1.0,1.0],[26.105943105379367,36.412552515842464,0.0,4.0,0.0,1.0,1.0],[36.412552515842464,37.55773133922725,889.9999,4.0,8.0,4.0,-1.0],[37.55773133922725,44.81053055399757,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>[[5.855215861552942,24.168189152101355,-1860.0,5.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,-0.0,5.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,890.0,5.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,5.0,9.0,3.0,-1.0]]</t>
+          <t>[[5.855215861552942,24.168189152101355,-1860.0,4.0,0.0,0.0,1.0],[24.168189152101355,36.25475152386331,0.0,4.0,0.0,1.0,1.0],[36.25475152386331,36.621010989674275,889.9999,4.0,8.0,4.0,-1.0],[36.621010989674275,42.114902976838806,1860.0,3.0,9.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>[[5.797994855764833,32.81892929969216,-1860.0,5.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,-0.0,5.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,5.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.797994855764833,32.81892929969216,-1860.0,4.0,0.0,0.0,1.0],[32.81892929969216,37.4510894900797,0.0,4.0,0.0,1.0,1.0],[37.4510894900797,44.013316426462055,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>[[5.420225279167751,33.84564490494072,-1860.0,4.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8504,3.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,3.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,3.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.420225279167751,33.84564490494072,-1860.0,3.0,0.0,0.0,1.0],[33.84564490494072,34.235034214882816,-873.8505,2.0,8.0,3.0,-1.0],[34.235034214882816,37.73953800436168,0.0,2.0,7.0,4.0,-1.0],[37.73953800436168,43.969766963435205,1860.0,2.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>[[5.7508207852407525,33.001741461744125,-1860.0,3.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.35,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.7508207852407525,33.001741461744125,-1860.0,2.0,0.0,0.0,1.0],[33.001741461744125,36.78659155570293,0.0,2.0,7.0,4.0,-1.0],[36.78659155570293,37.92204658389057,1071.3499,2.0,7.0,4.0,-1.0],[37.92204658389057,43.220836715432895,1860.0,2.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C689" t="n">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.35,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.964350820839753,32.520769149082675,-1860.0,2.0,0.0,0.0,1.0],[32.520769149082675,36.03558922193835,0.0,1.0,7.0,4.0,-1.0],[36.03558922193835,37.98826704019151,1071.3499,1.0,7.0,1.0,-1.0],[37.98826704019151,44.62737162225224,1860.0,1.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -16318,7 +16318,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.35,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.752687575372794,32.6346037524853,-1860.0,1.0,0.0,0.0,1.0],[32.6346037524853,36.14094064515214,0.0,0.0,7.0,5.0,-1.0],[36.14094064515214,37.309719609374426,1071.3499,0.0,7.0,5.0,-1.0],[37.309719609374426,44.32239339470812,1860.0,0.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>[[6.19610098460995,37.06424312311912,-0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,890.0,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[6.19610098460995,37.06424312311912,0.0,0.0,0.0,1.0,1.0],[37.06424312311912,37.43172100572042,889.9999,0.0,8.0,2.0,-1.0],[37.43172100572042,42.576411362138614,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>[[5.777144260757365,35.54331894192165,-0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,890.0,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
+          <t>[[5.777144260757365,35.54331894192165,0.0,0.0,0.0,1.0,1.0],[35.54331894192165,36.023418533553325,889.9999,0.0,8.0,0.0,-1.0],[36.023418533553325,53.30700383229388,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,890.0,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
+          <t>[[5.942806062990978,31.221650593240938,-1860.0,1.0,7.0,0.0,-1.0],[31.221650593240938,31.853621706497186,-1074.7923,0.0,7.0,1.0,-1.0],[31.853621706497186,35.01347727277843,0.0,0.0,6.0,2.0,-1.0],[35.01347727277843,36.27741949929093,889.9999,0.0,6.0,2.0,-1.0],[36.27741949929093,68.50794627535963,1860.0,0.0,6.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C695" t="n">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,890.0,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[5.644910302815902,30.8937013071726,-1860.0,1.0,6.0,0.0,-1.0],[30.8937013071726,32.04137362555245,-1074.7923,0.0,6.0,1.0,-1.0],[32.04137362555245,35.48439058069199,0.0,0.0,5.0,2.0,-1.0],[35.48439058069199,37.20589905826177,889.9999,0.0,5.0,2.0,-1.0],[37.20589905826177,62.45469006261847,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,890.0,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[5.656569383363265,31.483819955773455,-1860.0,1.0,4.0,0.0,-1.0],[31.483819955773455,32.71368903065013,-1074.7923,0.0,4.0,1.0,-1.0],[32.71368903065013,36.403296255280154,0.0,0.0,3.0,2.0,-1.0],[36.403296255280154,37.01823079271849,889.9999,0.0,3.0,2.0,-1.0],[37.01823079271849,66.5350885897587,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C698" t="n">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,890.0,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
+          <t>[[5.949061243550825,31.691487132188282,-1860.0,10.0,11.0,2.0,0.0],[31.691487132188282,34.75606164274036,0.0,9.0,11.0,3.0,0.0],[34.75606164274036,35.368976544850774,889.9999,0.0,2.0,1.0,-1.0],[35.368976544850774,66.62763655248197,1860.0,0.0,2.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.3269,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,890.0,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
+          <t>[[5.9211837771289675,31.90178804470698,-1860.0,9.0,1.0,2.0,1.0],[31.90178804470698,32.50598814395298,-1607.5347,8.0,1.0,3.0,1.0],[32.50598814395298,33.110188243198984,-822.327,9.0,10.0,4.0,0.0],[33.110188243198984,36.73538883867498,0.0,9.0,10.0,4.0,0.0],[36.73538883867498,37.94378903716698,889.9999,0.0,1.0,1.0,-1.0],[37.94378903716698,65.736993602483,1860.0,0.0,1.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C700" t="n">
@@ -16548,11 +16548,11 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.85,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,890.0,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.5820891349112465,32.32630314018349,-1860.0,9.0,2.0,0.0,1.0],[32.32630314018349,35.89219834088645,0.0,9.0,1.0,1.0,1.0],[35.89219834088645,36.48651420767028,227.8499,9.0,1.0,1.0,1.0],[36.48651420767028,37.67514594123794,889.9999,0.0,1.0,0.0,-1.0],[37.67514594123794,64.41935994651018,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>227.85</v>
+        <v>227.8499</v>
       </c>
       <c r="D701" s="4" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>[[5.8823909272670205,32.29880920212269,-1860.0,9.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,9.0,0.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
+          <t>[[5.8823909272670205,32.29880920212269,-1860.0,8.0,1.0,1.0,1.0],[32.29880920212269,36.31869893960072,0.0,8.0,1.0,1.0,1.0],[36.31869893960072,62.73511721445639,1860.0,9.0,1.0,1.0,1.0]]</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,-0.0,9.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.980859745441576,32.362751141045614,-1860.0,9.0,0.0,1.0,1.0],[32.362751141045614,38.811657926637714,0.0,8.0,0.0,1.0,1.0],[38.811657926637714,64.02102081577047,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>[[5.551586064375953,34.682302039284565,-1860.0,9.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,-0.0,9.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[5.551586064375953,34.682302039284565,-1860.0,8.0,0.0,0.0,1.0],[34.682302039284565,38.93053145229207,0.0,8.0,0.0,3.0,1.0],[38.93053145229207,65.63368776262496,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>[[5.519737223169096,33.328697471364436,-1860.0,8.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,-0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
+          <t>[[5.519737223169096,33.328697471364436,-1860.0,6.0,0.0,0.0,1.0],[33.328697471364436,39.8371775294527,0.0,8.0,0.0,3.0,1.0],[39.8371775294527,41.0205375400142,890.0,8.0,8.0,2.0,-1.0],[41.0205375400142,64.09605774596352,1860.0,8.0,9.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>[[5.8738382526313515,34.02257256186337,-1860.0,7.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,-0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,7.0,8.0,2.0,-1.0]]</t>
+          <t>[[5.8738382526313515,34.02257256186337,-1860.0,5.0,0.0,0.0,1.0],[34.02257256186337,38.71402828006871,0.0,7.0,0.0,3.0,1.0],[38.71402828006871,63.930602765422385,1860.0,5.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>[[5.790447701973391,33.61829338027952,-1860.0,6.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,-0.0,6.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,6.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.790447701973391,33.61829338027952,-1860.0,4.0,0.0,0.0,1.0],[33.61829338027952,39.53911160970635,0.0,4.0,0.0,3.0,1.0],[39.53911160970635,40.131193432649034,890.0,5.0,8.0,3.0,-1.0],[40.131193432649034,64.40654817329906,1860.0,6.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>[[5.717840236276732,34.20607486027302,-1860.0,5.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7923,5.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,5.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,5.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
+          <t>[[5.717840236276732,34.20607486027302,-1860.0,3.0,0.0,0.0,1.0],[34.20607486027302,34.82538430862077,-1074.7922,4.0,9.0,3.0,-1.0],[34.82538430862077,38.54124099870724,0.0,4.0,8.0,4.0,-1.0],[38.54124099870724,39.77985989540272,890.0,4.0,8.0,4.0,-1.0],[39.77985989540272,67.02947562270352,1860.0,5.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>[[5.59923945864782,33.54709545904373,-1860.0,4.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7923,4.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,4.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,4.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,4.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.59923945864782,33.54709545904373,-1860.0,3.0,0.0,0.0,1.0],[33.54709545904373,34.154657546008856,-1074.7922,3.0,9.0,3.0,-1.0],[34.154657546008856,37.80003006779963,0.0,3.0,8.0,4.0,-1.0],[37.80003006779963,38.407592154764764,890.0,3.0,8.0,1.0,-1.0],[38.407592154764764,65.74788606819554,1860.0,3.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>[[10.505498645660388,34.93527156472982,-1860.0,3.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,3.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,3.0,8.0,4.0,-1.0]]</t>
+          <t>[[10.505498645660388,34.93527156472982,-1860.0,2.0,0.0,0.0,1.0],[34.93527156472982,39.278342305897716,0.0,1.0,0.0,3.0,1.0],[39.278342305897716,64.25099906761314,1860.0,2.0,8.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C710" t="n">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>[[17.0354249272596,34.30955869369576,-1860.0,2.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,-0.0,2.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
+          <t>[[17.0354249272596,34.30955869369576,-1860.0,1.0,0.0,0.0,1.0],[34.30955869369576,39.107929184372466,0.0,1.0,0.0,3.0,1.0],[39.107929184372466,40.06760328250781,890.0,2.0,8.0,2.0,-1.0],[40.06760328250781,64.53929278495903,1860.0,2.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>[[16.245864004337356,34.34927316690133,-1860.0,1.0,0.0,0.0,1.0],[34.34927316690133,38.99117295217414,-0.0,1.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
+          <t>[[16.245864004337356,34.34927316690133,-1860.0,0.0,0.0,0.0,1.0],[34.34927316690133,35.277653123955886,0.0,1.0,0.0,3.0,1.0],[35.277653123955886,38.99117295217414,0.0,0.0,0.0,3.0,1.0],[38.99117295217414,40.383742887755986,890.0,1.0,8.0,3.0,-1.0],[40.383742887755986,62.20067187853821,1860.0,1.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>[[13.377518634125957,38.178981092299246,-0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
+          <t>[[13.377518634125957,38.178981092299246,0.0,0.0,0.0,1.0,1.0],[38.178981092299246,40.163098088953106,1678.65,1.0,0.0,1.0,1.0],[40.163098088953106,62.484414301309066,1860.0,1.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>[[10.100087511346796,29.88787855184674,-1860.0,1.0,0.0,0.0,1.0],[29.88787855184674,39.2321132098606,-0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,1.0,8.0,0.0,-1.0]]</t>
+          <t>[[10.100087511346796,29.88787855184674,-1860.0,0.0,0.0,0.0,1.0],[29.88787855184674,35.384487174207834,0.0,1.0,0.0,1.0,1.0],[35.384487174207834,38.13279148538838,0.0,0.0,0.0,1.0,1.0],[38.13279148538838,39.2321132098606,0.0,1.0,0.0,1.0,1.0],[39.2321132098606,64.51651287272165,1860.0,0.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>[[6.038010189969462,35.23858817463015,-1860.0,1.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
+          <t>[[6.038010189969462,35.23858817463015,-1860.0,0.0,0.0,0.0,1.0],[35.23858817463015,36.40661129401657,-873.8504,0.0,8.0,0.0,-1.0],[36.40661129401657,40.49469221186907,0.0,0.0,7.0,1.0,-1.0],[40.49469221186907,41.6627153312555,1071.35,0.0,7.0,0.0,-1.0],[41.6627153312555,63.855154599597626,1860.0,0.0,7.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>[[5.9133631656834655,37.28989980832542,-0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
+          <t>[[5.9133631656834655,37.28989980832542,0.0,0.0,0.0,1.0,1.0],[37.28989980832542,39.61408770778038,890.0,0.0,8.0,1.0,-1.0],[39.61408770778038,63.43701367719371,1860.0,0.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7923,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
+          <t>[[5.8700633407018366,32.30276536943349,-1860.0,1.0,8.0,2.0,-1.0],[32.30276536943349,33.504251825284925,-1074.7922,0.0,8.0,0.0,-1.0],[33.504251825284925,37.10871119283924,0.0,0.0,7.0,1.0,-1.0],[37.10871119283924,39.51168410454211,890.0,0.0,7.0,1.0,-1.0],[39.51168410454211,65.34364290534803,1860.0,0.0,7.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7923,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
+          <t>[[5.629739286392475,31.895303771490912,-1860.0,1.0,7.0,0.0,-1.0],[31.895303771490912,35.065285692106244,-1074.7922,0.0,7.0,0.0,-1.0],[35.065285692106244,38.68812217280947,0.0,0.0,6.0,1.0,-1.0],[38.68812217280947,39.593831292985286,890.0,0.0,6.0,1.0,-1.0],[39.593831292985286,50.46234073509498,1860.0,0.0,6.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7923,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
+          <t>[[6.003789211278378,32.55206763164108,-1860.0,1.0,6.0,0.0,-1.0],[32.55206763164108,35.411112999987836,-1074.7922,0.0,6.0,0.0,-1.0],[35.411112999987836,39.08702847357652,0.0,0.0,5.0,1.0,-1.0],[39.08702847357652,41.12920373668134,890.0,0.0,5.0,1.0,-1.0],[41.12920373668134,46.43885942075388,1860.0,0.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7923,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
+          <t>[[5.538603565668832,31.641517815382105,-1860.0,1.0,6.0,1.0,-1.0],[31.641517815382105,33.19990075566349,-1074.7922,0.0,6.0,1.0,-1.0],[33.19990075566349,36.70626237129662,0.0,0.0,5.0,2.0,-1.0],[36.70626237129662,37.09585810636697,890.0,0.0,5.0,0.0,-1.0],[37.09585810636697,44.10858133763322,1860.0,0.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7923,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
+          <t>[[6.075732337210046,31.84029389353122,-1860.0,1.0,5.0,1.0,-1.0],[31.84029389353122,32.58709277922169,-1074.7922,0.0,5.0,0.0,-1.0],[32.58709277922169,35.94768776482881,0.0,0.0,4.0,1.0,-1.0],[35.94768776482881,38.56148386474545,890.0,0.0,4.0,0.0,-1.0],[38.56148386474545,43.04227717888826,1860.0,0.0,4.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7923,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
+          <t>[[6.323637585308626,31.845397912843964,-1860.0,1.0,4.0,0.0,-1.0],[31.845397912843964,32.19986680628195,-1074.7922,0.0,4.0,0.0,-1.0],[32.19986680628195,35.744555740661866,0.0,0.0,3.0,1.0,-1.0],[35.744555740661866,37.87136910128981,890.0,0.0,3.0,0.0,-1.0],[37.87136910128981,41.416058035669714,1860.0,0.0,3.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -17054,7 +17054,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7923,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
+          <t>[[5.532599802694209,32.41959273462963,-1860.0,1.0,3.0,0.0,-1.0],[32.41959273462963,32.82089113659882,-1074.7922,0.0,3.0,1.0,-1.0],[32.82089113659882,36.43257675432149,0.0,0.0,2.0,2.0,-1.0],[36.43257675432149,38.840367166136595,890.0,0.0,2.0,0.0,-1.0],[38.840367166136595,45.261141597643565,1860.0,0.0,2.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7923,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.807691584223856,31.43842393144155,-1860.0,1.0,2.0,1.0,-1.0],[31.43842393144155,31.809883820531663,-1074.7922,0.0,2.0,0.0,-1.0],[31.809883820531663,35.15302282234266,0.0,0.0,1.0,1.0,-1.0],[35.15302282234266,40.724921158694336,890.0,0.0,1.0,0.0,-1.0],[40.724921158694336,42.582220604144894,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,33.025434083328,-0.0,0.0,1.0,2.0,-1.0],[33.025434083328,36.51763974573228,0.0,0.0,0.0,2.0,-1.0],[36.51763974573228,37.29368544848879,1860.0,0.0,0.0,0.0,-1.0],[37.29368544848879,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
+          <t>[[5.863834486850254,31.473342677814987,-1860.0,1.0,1.0,0.0,-1.0],[31.473342677814987,36.51763974573228,0.0,0.0,1.0,2.0,-1.0],[36.51763974573228,44.27809677329735,1860.0,0.0,1.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[6.274995285997301,31.837474971500754,-1860.0,1.0,0.0,1.0,-1.0],[31.837474971500754,41.918452875642956,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,-0.0,0.0,0.0,1.0,-1.0]]</t>
+          <t>[[5.722181504183003,31.073599830421916,-1860.0,1.0,0.0,0.0,-1.0],[31.073599830421916,41.576330279863754,0.0,0.0,0.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>[[6.08874873479854,28.614641867900705,-1860.0,9.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7923,9.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,9.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.15,0.0,0.0,0.0,-1.0]]</t>
+          <t>[[6.08874873479854,28.614641867900705,-1860.0,8.0,0.0,0.0,1.0],[28.614641867900705,28.990073420119074,-1074.7922,8.0,9.0,2.0,-1.0],[28.990073420119074,32.368957390084404,0.0,8.0,8.0,3.0,-1.0],[32.368957390084404,43.25647240441712,662.1501,0.0,0.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C730" t="n">
@@ -17238,7 +17238,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>[[6.093610436480207,29.864418878405466,-1860.0,8.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8505,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,7.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
+          <t>[[6.093610436480207,29.864418878405466,-1860.0,7.0,0.0,0.0,1.0],[29.864418878405466,30.25410426269932,-873.8504,7.0,8.0,1.0,-1.0],[30.25410426269932,33.761272721344035,0.0,6.0,8.0,1.0,-1.0],[33.761272721344035,44.672463481572024,1860.0,8.0,8.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -17261,7 +17261,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8505,6.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,6.0,7.0,5.0,-1.0]]</t>
+          <t>[[5.940295990748728,29.46027690807245,-1860.0,7.0,0.0,0.0,1.0],[29.46027690807245,30.218985969921604,-873.8504,5.0,8.0,4.0,-1.0],[30.218985969921604,33.25382221731821,0.0,6.0,7.0,5.0,-1.0],[33.25382221731821,33.63317674824279,1071.35,6.0,7.0,5.0,-1.0],[33.63317674824279,43.49639455228177,1860.0,5.0,7.0,5.0,-1.0]]</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>[[5.792876763597392,29.695944878509668,-1860.0,6.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7923,6.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,6.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,6.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.792876763597392,29.695944878509668,-1860.0,5.0,0.0,0.0,1.0],[29.695944878509668,30.07535865811145,-1074.7922,5.0,9.0,2.0,-1.0],[30.07535865811145,33.11066889492571,0.0,6.0,8.0,3.0,-1.0],[33.11066889492571,33.49008267452749,890.0,4.0,8.0,3.0,-1.0],[33.49008267452749,43.35484094417383,1860.0,5.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>[[5.920771901706709,29.45730616428769,-1860.0,5.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,4.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,4.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,4.0,8.0,3.0,-1.0]]</t>
+          <t>[[5.920771901706709,29.45730616428769,-1860.0,4.0,0.0,0.0,1.0],[29.45730616428769,32.54406475610159,0.0,3.0,7.0,4.0,-1.0],[32.54406475610159,32.92990958007833,1071.35,3.0,7.0,4.0,-1.0],[32.92990958007833,44.119409475403714,1860.0,3.0,8.0,3.0,-1.0]]</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7923,4.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,4.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,4.0,9.0,2.0,-1.0]]</t>
+          <t>[[5.729929070450166,28.72834939554622,-1860.0,4.0,0.0,0.0,1.0],[28.72834939554622,29.09929165885422,-1074.7922,3.0,9.0,2.0,-1.0],[29.09929165885422,32.437772028626235,0.0,3.0,8.0,3.0,-1.0],[32.437772028626235,42.45321313794226,1860.0,3.0,9.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>[[6.028534461864241,29.182923856584985,-1860.0,3.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8505,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
+          <t>[[6.028534461864241,29.182923856584985,-1860.0,2.0,0.0,0.0,1.0],[29.182923856584985,29.55638175004822,-873.8504,2.0,8.0,3.0,-1.0],[29.55638175004822,32.917502791217366,0.0,2.0,7.0,4.0,-1.0],[32.917502791217366,43.000865914724784,1860.0,2.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C736" t="n">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8505,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
+          <t>[[5.904617264301909,28.885789318489433,-1860.0,2.0,0.0,0.0,1.0],[28.885789318489433,30.4438348814852,-873.8504,1.0,8.0,3.0,-1.0],[30.4438348814852,33.559926007476726,0.0,1.0,7.0,4.0,-1.0],[33.559926007476726,44.46624494844708,1860.0,1.0,7.0,4.0,-1.0]]</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8505,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
+          <t>[[5.834823644290232,29.464308432555832,-1860.0,1.0,0.0,0.0,1.0],[29.464308432555832,29.851677035642155,-873.8504,0.0,8.0,4.0,-1.0],[29.851677035642155,32.95062586033272,0.0,0.0,7.0,5.0,-1.0],[32.95062586033272,33.337994463419044,1071.35,0.0,7.0,2.0,-1.0],[33.337994463419044,44.18431534983604,1860.0,0.0,7.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>[[14.603709426006594,31.69296770568061,-0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
+          <t>[[14.603709426006594,31.69296770568061,0.0,0.0,0.0,1.0,1.0],[31.69296770568061,31.973119480757227,890.0,0.0,8.0,2.0,-1.0],[31.973119480757227,42.338735158592286,1860.0,0.0,8.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7923,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
+          <t>[[14.245771520889912,26.922191625735785,-1860.0,1.0,8.0,3.0,-1.0],[26.922191625735785,28.733108783570913,-1074.7922,0.0,8.0,2.0,-1.0],[28.733108783570913,31.75130404662945,0.0,0.0,8.0,2.0,-1.0],[31.75130404662945,32.35494309924116,708.65,1.0,8.0,1.0,-1.0],[32.35494309924116,44.12590462516947,1860.0,1.0,8.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C740" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7923,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
+          <t>[[13.63758398867611,28.437049312171897,-1860.0,1.0,6.0,3.0,-1.0],[28.437049312171897,28.739079216733035,-1074.7922,0.0,6.0,2.0,-1.0],[28.739079216733035,32.061408166905565,0.0,0.0,5.0,3.0,-1.0],[32.061408166905565,43.53854454022883,1860.0,0.0,5.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C742" t="n">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7923,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
+          <t>[[15.114865484076022,27.020927533341908,-1860.0,1.0,5.0,1.0,-1.0],[27.020927533341908,28.34382331659367,-1074.7922,0.0,5.0,2.0,-1.0],[28.34382331659367,31.51877319639791,0.0,0.0,5.0,2.0,-1.0],[31.51877319639791,31.783352353048265,708.65,1.0,5.0,1.0,-1.0],[31.783352353048265,41.30820199246097,1860.0,1.0,5.0,1.0,-1.0]]</t>
         </is>
       </c>
       <c r="C743" t="n">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7923,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
+          <t>[[14.10266160291317,27.256677252821802,-1860.0,1.0,4.0,2.0,-1.0],[27.256677252821802,29.449013194473242,-1074.7922,0.0,4.0,2.0,-1.0],[29.449013194473242,32.46347511424397,0.0,0.0,4.0,2.0,-1.0],[32.46347511424397,33.285601092363265,708.65,1.0,4.0,1.0,-1.0],[33.285601092363265,41.23281888084973,1860.0,1.0,5.0,0.0,-1.0]]</t>
         </is>
       </c>
       <c r="C744" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>[[14.814695644686502,29.37746717540806,-1860.0,1.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7923,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
+          <t>[[14.814695644686502,29.37746717540806,-1860.0,0.0,3.0,1.0,-1.0],[29.37746717540806,29.674666594402378,-1074.7922,0.0,3.0,2.0,-1.0],[29.674666594402378,32.94386020333987,0.0,0.0,2.0,3.0,-1.0],[32.94386020333987,44.23743812512394,1860.0,0.0,3.0,2.0,-1.0]]</t>
         </is>
       </c>
       <c r="C745" t="n">

--- a/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -430,12 +430,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E745"/>
+  <dimension ref="A1:F745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,9 +459,9 @@
           <t>P_ESS_state</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dsfunction_state_share</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dsfunction_state_width</t>
         </is>
       </c>
     </row>
@@ -482,9 +482,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0202020202,0.0707070707,0,0.303030303,0,0]</t>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1166399351,3.9082397727,0,0]</t>
         </is>
       </c>
     </row>
@@ -505,9 +505,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.0707070707,0,0.3535353535,0,0]</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.0734418667,0,0]</t>
         </is>
       </c>
     </row>
@@ -528,9 +528,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0101010101,0.0606060606,0,0.3737373737,0,0]</t>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5951678207,3.5710069242,0,0]</t>
         </is>
       </c>
     </row>
@@ -551,9 +551,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0,0.0707070707,0,0.3434343434,0,0]</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -574,9 +574,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.0707070707,0,0.3131313131,0,0]</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.7833586668,0,0]</t>
         </is>
       </c>
     </row>
@@ -597,9 +597,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0,0.4444444444,0,0,0,0]</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -620,9 +620,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0.0202020202,0,0.6767676768,0,0,0,0]</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[1.2256223835,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -643,9 +643,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0.0606060606,0,0.6767676768,0,0,0,0]</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>[3.7623926693,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -666,9 +666,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0.202020202,0,0.4545454545,0,0,0,0]</t>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>[11.9412188708,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -689,9 +689,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>[0.3333333333,0.1818181818,0,0.0606060606,0,0.4242424242,0,0]</t>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>[10.7369902025,0,3.5789967342,0,2.3859978228]</t>
         </is>
       </c>
     </row>
@@ -712,9 +712,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.2121212121,0,0.0606060606,0,0.0101010101,0.3939393939,0]</t>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>[12.7440141167,0,3.6411468905,0,0.6068578151]</t>
         </is>
       </c>
     </row>
@@ -735,9 +735,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0.1919191919,0,0.0606060606,0,0.0303030303,0.3434343434,0]</t>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>[10.5599650746,0,3.334725813,0,1.6673629065]</t>
         </is>
       </c>
     </row>
@@ -758,9 +758,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.202020202,0,0.0606060606,0,0.0202020202,0.3636363636,0]</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>[11.6727217696,0,3.5018165309,0,1.167272177]</t>
         </is>
       </c>
     </row>
@@ -781,9 +781,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.1818181818,0,0.0606060606,0,0.0404040404,0.3636363636,0]</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>[10.3275527392,0,3.4425175797,0,2.2950117198]</t>
         </is>
       </c>
     </row>
@@ -804,9 +804,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.0202020202,0.0707070707,0,0.0101010101,0.3636363636,0]</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.098258909,3.8439061814,0,0.5491294545]</t>
         </is>
       </c>
     </row>
@@ -827,9 +827,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.0303030303,0.0606060606,0,0.0101010101,0.3636363636,0]</t>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.7007667338,3.4015334676,0,0.5669222446]</t>
         </is>
       </c>
     </row>
@@ -850,9 +850,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0,0.0606060606,0,0.0101010101,0.3737373737,0]</t>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3824580236,0,0.5637430039]</t>
         </is>
       </c>
     </row>
@@ -873,9 +873,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0202020202,0.0505050505,0,0.0202020202,0.3535353535,0]</t>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2069288879,3.0173222197,0,1.2069288879]</t>
         </is>
       </c>
     </row>
@@ -896,9 +896,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.5151515152,0,0.0505050505,0,0.0707070707,0.3636363636,0]</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.9770197677,0,4.1678276748]</t>
         </is>
       </c>
     </row>
@@ -919,9 +919,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.6565656566,0,0.0707070707,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3015725362,0,0.4716532195]</t>
         </is>
       </c>
     </row>
@@ -942,9 +942,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0303030303,0.0707070707,0,0.0303030303,0.2323232323,0]</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.405574432,3.2796736747,0,1.405574432]</t>
         </is>
       </c>
     </row>
@@ -965,9 +965,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0,0.0707070707,0,0.0303030303,0.2626262626,0]</t>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3591804837,0,1.4396487787]</t>
         </is>
       </c>
     </row>
@@ -988,9 +988,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0202020202,0.0707070707,0,0.0101010101,0.2929292929,0]</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9740699758,3.4092449155,0,0.4870349879]</t>
         </is>
       </c>
     </row>
@@ -1011,9 +1011,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0.0202020202,0.0707070707,0,0.0202020202,0.1717171717,0]</t>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8400483022,2.9401690578,0,0.8400483022]</t>
         </is>
       </c>
     </row>
@@ -1034,9 +1034,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0202020202,0.0808080808,0,0.0202020202,0.1313131313,0]</t>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8148473075,3.25938923,0,0.8148473075]</t>
         </is>
       </c>
     </row>
@@ -1057,9 +1057,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.0707070707,0,0.0505050505,0.1212121212,0]</t>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.8760489258,0,2.0543206613]</t>
         </is>
       </c>
     </row>
@@ -1080,9 +1080,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0,0.0101010101,0.0707070707,0,0.0202020202,0.1919191919,0]</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4265744606,2.9860212241,0,0.8531489212]</t>
         </is>
       </c>
     </row>
@@ -1103,9 +1103,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0,0.0101010101,0.0909090909,0,0.0909090909,0,0]</t>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.393551464,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1126,9 +1126,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0,0.0505050505,0.0808080808,0,0.1616161616,0,0]</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.9897087283,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1149,9 +1149,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0,0.303030303,0,0,0,0]</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1172,9 +1172,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.5858585859,0,0,0,0]</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1195,9 +1195,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0,0,0.6868686869,0,0,0,0]</t>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1218,9 +1218,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.404040404,0,0.2727272727,0,0,0,0]</t>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>[16.4293641385,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1241,9 +1241,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.4444444444,0,0.0808080808,0,0.1616161616,0,0]</t>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>[17.8148365858,0,3.2390611974,0,0]</t>
         </is>
       </c>
     </row>
@@ -1264,9 +1264,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.0707070707,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.9479204562,0,0.4211314937]</t>
         </is>
       </c>
     </row>
@@ -1287,9 +1287,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.0808080808,0,0,0.1515151515,0]</t>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1772452978,0,0]</t>
         </is>
       </c>
     </row>
@@ -1310,9 +1310,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0303030303,0.0808080808,0,0.0202020202,0.1212121212,0]</t>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1874214305,3.1664571479,0,0.791614287]</t>
         </is>
       </c>
     </row>
@@ -1333,9 +1333,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0202020202,0.0707070707,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8355653364,2.9244786774,0,0.4177826682]</t>
         </is>
       </c>
     </row>
@@ -1356,9 +1356,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0202020202,0.0707070707,0,0,0.1717171717,0]</t>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8110160899,2.8385563146,0,0]</t>
         </is>
       </c>
     </row>
@@ -1379,9 +1379,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0808080808,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1381501453,0,0.3922687682]</t>
         </is>
       </c>
     </row>
@@ -1402,9 +1402,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0202020202,0.0808080808,0,0,0.1717171717,0]</t>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8205499353,3.2821997411,0,0]</t>
         </is>
       </c>
     </row>
@@ -1425,9 +1425,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0101010101,0.101010101,0,0.0202020202,0.2424242424,0]</t>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3039572802,3.039572802,0,0.6079145604]</t>
         </is>
       </c>
     </row>
@@ -1448,9 +1448,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7575757576,0,0.0303030303,0.2121212121,0]</t>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.8711515717]</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1471,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0202020202,0.101010101,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.591652046,2.9582602299,0,0.295826023]</t>
         </is>
       </c>
     </row>
@@ -1494,9 +1494,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0.0202020202,0.1111111111,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.545859728,3.0022285043,0,0.272929864]</t>
         </is>
       </c>
     </row>
@@ -1517,9 +1517,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.1212121212,0,0,0.202020202,0]</t>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3196478679,0,0]</t>
         </is>
       </c>
     </row>
@@ -1540,9 +1540,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.1414141414,0,0,0.1717171717,0]</t>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.6872706212,0,0]</t>
         </is>
       </c>
     </row>
@@ -1563,9 +1563,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0,0.1212121212,0,0,0.1616161616,0]</t>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.158413158,0,0]</t>
         </is>
       </c>
     </row>
@@ -1586,9 +1586,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.1616161616,0,0,0.1111111111,0]</t>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.0707478798,0,0]</t>
         </is>
       </c>
     </row>
@@ -1609,9 +1609,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>[0.797979798,0,0,0.1313131313,0,0,0.0707070707,0]</t>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0775818934,0,0]</t>
         </is>
       </c>
     </row>
@@ -1632,9 +1632,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0,0.1414141414,0,0,0.1212121212,0]</t>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.649721071,0,0]</t>
         </is>
       </c>
     </row>
@@ -1655,9 +1655,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0,0.1919191919,0,0,0.0707070707,0]</t>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.5361146231,0,0]</t>
         </is>
       </c>
     </row>
@@ -1678,9 +1678,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0.0404040404,0,0.2626262626,0,0,0.0808080808,0]</t>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>[0.8923881553,0,5.8005230093,0,0]</t>
         </is>
       </c>
     </row>
@@ -1701,9 +1701,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0.0303030303,0,0.1919191919,0,0,0.1111111111,0]</t>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>[0.6702129062,0,2.9042559267,0,0]</t>
         </is>
       </c>
     </row>
@@ -1724,9 +1724,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0.0101010101,0,0.3737373737,0,0,0,0]</t>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>[0.2419517546,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1747,9 +1747,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0.0202020202,0,0.4646464646,0,0,0,0]</t>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>[0.5864810618,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -1770,9 +1770,9 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0.0909090909,0,0.0909090909,0.0909090909,0.3131313131,0,0]</t>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>[2.4685368355,0,2.4685368355,2.4685368355,0]</t>
         </is>
       </c>
     </row>
@@ -1793,9 +1793,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.1111111111,0,0.202020202,0,0]</t>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.2652672763,2.9179400393,0,0.2652672763]</t>
         </is>
       </c>
     </row>
@@ -1816,9 +1816,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0101010101,0.0909090909,0,0,0.2929292929,0]</t>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.2856556526,2.5709008731,0,0]</t>
         </is>
       </c>
     </row>
@@ -1839,9 +1839,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0,0.0707070707,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0018565198,0,0.4288366457]</t>
         </is>
       </c>
     </row>
@@ -1862,9 +1862,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0,0.0606060606,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.7076543128,0,0.4512757188]</t>
         </is>
       </c>
     </row>
@@ -1885,9 +1885,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.0707070707,0,0,0.1616161616,0]</t>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0317477263,0,0]</t>
         </is>
       </c>
     </row>
@@ -1908,9 +1908,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0.0101010101,0.0606060606,0,0.0303030303,0.1313131313,0]</t>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4378802282,2.6272813692,0,1.3136406846]</t>
         </is>
       </c>
     </row>
@@ -1931,9 +1931,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.0606060606,0,0.0202020202,0.1919191919,0]</t>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.7393887681,0,0.9131295894]</t>
         </is>
       </c>
     </row>
@@ -1954,9 +1954,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.0606060606,0,0,0.1717171717,0]</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.6138723312,0,0]</t>
         </is>
       </c>
     </row>
@@ -1977,9 +1977,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0.0101010101,0.0707070707,0,0,0.1313131313,0]</t>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4181596701,2.927117691,0,0]</t>
         </is>
       </c>
     </row>
@@ -2000,9 +2000,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7878787879,0,0.0404040404,0.1717171717,0]</t>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.7867872788]</t>
         </is>
       </c>
     </row>
@@ -2023,9 +2023,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0101010101,0.0606060606,0,0,0.1919191919,0]</t>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4536334972,2.7218009833,0,0]</t>
         </is>
       </c>
     </row>
@@ -2046,9 +2046,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0,0.0707070707,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0619856057,0,0.4374265151]</t>
         </is>
       </c>
     </row>
@@ -2069,9 +2069,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.0606060606,0,0.0202020202,0.2323232323,0]</t>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.8491296441,0,0.9497098814]</t>
         </is>
       </c>
     </row>
@@ -2092,9 +2092,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0.0101010101,0.0505050505,0,0,0.2929292929,0]</t>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5126435637,2.5632178186,0,0]</t>
         </is>
       </c>
     </row>
@@ -2115,9 +2115,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0.0101010101,0.0606060606,0,0.0101010101,0.2727272727,0]</t>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5022334762,3.0134008575,0,0.5022334762]</t>
         </is>
       </c>
     </row>
@@ -2138,9 +2138,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0,0.0606060606,0,0.0101010101,0.2828282828,0]</t>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0996624358,0,0.516610406]</t>
         </is>
       </c>
     </row>
@@ -2161,9 +2161,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0202020202,0.0606060606,0,0,0.2525252525,0]</t>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0211355651,3.0634066953,0,0]</t>
         </is>
       </c>
     </row>
@@ -2184,9 +2184,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0202020202,0.0606060606,0,0,0.2424242424,0]</t>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9669739937,2.9009219811,0,0]</t>
         </is>
       </c>
     </row>
@@ -2207,9 +2207,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.0606060606,0,0.0202020202,0.2323232323,0]</t>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4889316466,2.9335898794,0,0.9778632931]</t>
         </is>
       </c>
     </row>
@@ -2230,9 +2230,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0.0101010101,0,0.0606060606,0,0,0.2323232323,0]</t>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>[0.4825755379,0,2.8954532277,0,0]</t>
         </is>
       </c>
     </row>
@@ -2253,9 +2253,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0101010101,0.0606060606,0,0.0202020202,0.2525252525,0]</t>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5172399309,3.1034395856,0,1.0344798619]</t>
         </is>
       </c>
     </row>
@@ -2276,9 +2276,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0.0101010101,0,0.0505050505,0.0303030303,0,0.2424242424,0]</t>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>[0.5013900172,0,2.5069500858,1.5041700515,0]</t>
         </is>
       </c>
     </row>
@@ -2299,9 +2299,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0.0303030303,0.0101010101,0.0606060606,0,0,0.2727272727,0]</t>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>[1.5650294433,0.5216764811,3.1300588866,0,0]</t>
         </is>
       </c>
     </row>
@@ -2322,9 +2322,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0.0101010101,0,0.0606060606,0.0101010101,0.2424242424,0,0]</t>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>[0.5207212996,0,3.1243277978,0.5207212996,0]</t>
         </is>
       </c>
     </row>
@@ -2345,9 +2345,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0202020202,0.0606060606,0,0.2424242424,0,0]</t>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0531066243,3.1593198728,0,0]</t>
         </is>
       </c>
     </row>
@@ -2368,9 +2368,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0.0404040404,0.0101010101,0.0606060606,0,0.0303030303,0.1616161616,0]</t>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>[2.0098893709,0.5024723427,3.0148340563,0,1.5074170282]</t>
         </is>
       </c>
     </row>
@@ -2391,9 +2391,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0.0303030303,0,0.0606060606,0,0.0202020202,0.1818181818,0]</t>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>[1.4609481753,0,2.9218963505,0,0.9739654502]</t>
         </is>
       </c>
     </row>
@@ -2414,9 +2414,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0.0404040404,0.0101010101,0.0707070707,0,0,0.2222222222,0]</t>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>[1.8341585653,0.4585396413,3.2097774893,0,0]</t>
         </is>
       </c>
     </row>
@@ -2437,9 +2437,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.0808080808,0,0.0303030303,0.202020202,0]</t>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3876730854,3.1013846831,0,1.1630192562]</t>
         </is>
       </c>
     </row>
@@ -2460,9 +2460,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0202020202,0.0909090909,0,0.0303030303,0.2323232323,0]</t>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7563766902,3.4036951058,0,1.1345650353]</t>
         </is>
       </c>
     </row>
@@ -2483,9 +2483,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0101010101,0.0909090909,0,0.0303030303,0.2323232323,0]</t>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3725823608,3.3532412471,0,1.1177470824]</t>
         </is>
       </c>
     </row>
@@ -2506,9 +2506,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0303030303,0.0909090909,0,0.0101010101,0.202020202,0]</t>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0511026707,3.1533080122,0,0.3503675569]</t>
         </is>
       </c>
     </row>
@@ -2529,9 +2529,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0101010101,0.101010101,0,0,0.2323232323,0]</t>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3658368761,3.6583687612,0,0]</t>
         </is>
       </c>
     </row>
@@ -2552,9 +2552,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.595959596,0.0101010101,0.0909090909,0,0.0505050505,0.2525252525,0]</t>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3689612532,3.3206512792,0,1.8448062662]</t>
         </is>
       </c>
     </row>
@@ -2575,9 +2575,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.6262626263,0.0202020202,0.0808080808,0,0,0.2727272727,0]</t>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7280915015,2.9123660058,0,0]</t>
         </is>
       </c>
     </row>
@@ -2598,9 +2598,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.0909090909,0,0.0101010101,0.2828282828,0]</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.287491452,0,0.365276828]</t>
         </is>
       </c>
     </row>
@@ -2621,9 +2621,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.0707070707,0,0,0.4545454545,0]</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.323753686,0,0]</t>
         </is>
       </c>
     </row>
@@ -2644,9 +2644,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0101010101,0.0606060606,0,0.0202020202,0.4444444444,0]</t>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4776502611,2.8659015664,0,0.9553005221]</t>
         </is>
       </c>
     </row>
@@ -2667,9 +2667,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0.0202020202,0.0707070707,0,0.0202020202,0.3838383838,0]</t>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8943675559,3.1302864456,0,0.8943675559]</t>
         </is>
       </c>
     </row>
@@ -2690,9 +2690,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0.0202020202,0.0606060606,0,0.0303030303,0.404040404,0]</t>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.932637064,2.797911192,0,1.398955596]</t>
         </is>
       </c>
     </row>
@@ -2713,9 +2713,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0101010101,0.0707070707,0,0.0101010101,0.4141414141,0]</t>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4694624215,3.2862369505,0,0.4694624215]</t>
         </is>
       </c>
     </row>
@@ -2736,9 +2736,9 @@
           <t>CD</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0.0707070707,0.0707070707,0,0,0.3737373737,0]</t>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.2438860936,3.2438860936,0,0]</t>
         </is>
       </c>
     </row>
@@ -2759,9 +2759,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0101010101,0.0909090909,0,0,0.3737373737,0]</t>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4535849218,4.0822642964,0,0]</t>
         </is>
       </c>
     </row>
@@ -2782,9 +2782,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0.0101010101,0,0.0707070707,0.0101010101,0,0.3838383838,0]</t>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>[0.4726820313,0,3.3087742191,0.4726820313,0]</t>
         </is>
       </c>
     </row>
@@ -2805,9 +2805,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0.0404040404,0,0.0707070707,0.0202020202,0,0.4444444444,0]</t>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>[1.9524848609,0,3.4168485066,0.9762424305,0]</t>
         </is>
       </c>
     </row>
@@ -2828,9 +2828,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0.0303030303,0,0.0707070707,0.0303030303,0,0.4343434343,0]</t>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>[1.413526671,0,3.298228899,1.413526671,0]</t>
         </is>
       </c>
     </row>
@@ -2851,9 +2851,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0.0404040404,0,0.0606060606,0.0202020202,0,0.4949494949,0]</t>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>[2.040153656,0,3.060230484,1.020076828,0]</t>
         </is>
       </c>
     </row>
@@ -2874,9 +2874,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0.0505050505,0,0.0707070707,0.1515151515,0.3131313131,0,0]</t>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>[2.43331193,0,3.406636702,7.2999357899,0]</t>
         </is>
       </c>
     </row>
@@ -2897,9 +2897,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0.0404040404,0,0.0707070707,0.1111111111,0.2626262626,0,0]</t>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>[1.8586510094,0,3.2526392665,5.1112902759,0]</t>
         </is>
       </c>
     </row>
@@ -2920,9 +2920,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0.0808080808,0,0.0707070707,0.0606060606,0,0.2626262626,0]</t>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>[3.7991213294,0,3.3242311633,2.8493409971,0]</t>
         </is>
       </c>
     </row>
@@ -2943,9 +2943,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0.0505050505,0,0.0707070707,0.101010101,0.0303030303,0.2727272727,0]</t>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>[2.4439950837,0,3.4215931172,4.8879901674,1.4663970502]</t>
         </is>
       </c>
     </row>
@@ -2966,9 +2966,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0.1111111111,0,0.0707070707,0.0505050505,0,0.3333333333,0]</t>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>[5.5737445868,0,3.5469283734,2.5335202667,0]</t>
         </is>
       </c>
     </row>
@@ -2989,9 +2989,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0.0707070707,0,0.0808080808,0.0808080808,0,0.3333333333,0]</t>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>[3.2253919564,0,3.6861622358,3.6861622358,0]</t>
         </is>
       </c>
     </row>
@@ -3012,9 +3012,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0505050505,0,0.0808080808,0.1111111111,0,0.2929292929,0]</t>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>[2.2041131971,0,3.5265811154,4.8490490336,0]</t>
         </is>
       </c>
     </row>
@@ -3035,9 +3035,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.1919191919,0,0.0808080808,0.0808080808,0,0.3535353535,0]</t>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>[8.5530391438,0,3.6012796395,3.6012796395,0]</t>
         </is>
       </c>
     </row>
@@ -3058,9 +3058,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0,0.1717171717,0,0,0.3737373737,0]</t>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.424612535,0,0]</t>
         </is>
       </c>
     </row>
@@ -3081,9 +3081,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.202020202,0,0.0202020202,0.2929292929,0]</t>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.1979682925,0,0.9197968293]</t>
         </is>
       </c>
     </row>
@@ -3104,9 +3104,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6666666667,0,0,0.3333333333,0]</t>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3127,9 +3127,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6868686869,0,0,0.3131313131,0]</t>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3150,9 +3150,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.0808080808,0,0.0101010101,0.3333333333,0]</t>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.6699708219,0,0.4587463527]</t>
         </is>
       </c>
     </row>
@@ -3173,9 +3173,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0.0303030303,0.0808080808,0,0.0101010101,0.3131313131,0]</t>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.4007739955,3.7353973213,0,0.4669246652]</t>
         </is>
       </c>
     </row>
@@ -3196,9 +3196,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0.0202020202,0.0808080808,0,0.0303030303,0.303030303,0]</t>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9253460396,3.7013841586,0,1.3880190595]</t>
         </is>
       </c>
     </row>
@@ -3219,9 +3219,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0101010101,0.0808080808,0,0.0101010101,0.3434343434,0]</t>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.470987756,3.7679020483,0,0.470987756]</t>
         </is>
       </c>
     </row>
@@ -3242,9 +3242,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.0202020202,0.0808080808,0,0.0202020202,0.3434343434,0]</t>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9001118674,3.6004474697,0,0.9001118674]</t>
         </is>
       </c>
     </row>
@@ -3265,9 +3265,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.0202020202,0.0909090909,0,0,0.3535353535,0]</t>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9467914396,4.2605614783,0,0]</t>
         </is>
       </c>
     </row>
@@ -3288,9 +3288,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0808080808,0.0808080808,0,0.0202020202,0.2929292929,0]</t>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.5929512541,3.5929512541,0,0.8982378135]</t>
         </is>
       </c>
     </row>
@@ -3311,9 +3311,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0505050505,0.0808080808,0,0.0808080808,0.3636363636,0]</t>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.416668505,3.8666696079,0,3.8666696079]</t>
         </is>
       </c>
     </row>
@@ -3334,9 +3334,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0707070707,0.0808080808,0,0.0808080808,0.3434343434,0]</t>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.2714013744,3.7387444279,0,3.7387444279]</t>
         </is>
       </c>
     </row>
@@ -3357,9 +3357,9 @@
           <t>CD</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0,0.4444444444,0.1111111111,0,0.0101010101,0,0]</t>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>[0,19.8570358011,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3380,9 +3380,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0.0101010101,0,0.202020202,0,0,0.4848484848,0]</t>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>[0.4417435374,0,8.834870748,0,0]</t>
         </is>
       </c>
     </row>
@@ -3403,9 +3403,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.0303030303,0,0.0606060606,0.0303030303,0,0.6060606061,0]</t>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>[1.22335544,0,2.44671088,1.22335544,0]</t>
         </is>
       </c>
     </row>
@@ -3426,9 +3426,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.303030303,0,0.3737373737,0,0,0,0]</t>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>[12.4887381776,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3449,9 +3449,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.3737373737,0,0.101010101,0,0.202020202,0,0]</t>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>[14.1644291641,0,3.8282240984,0,0]</t>
         </is>
       </c>
     </row>
@@ -3472,9 +3472,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.3232323232,0,0.101010101,0,0.0202020202,0.202020202,0]</t>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>[12.6641207916,0,3.9575377474,0,0.7915075495]</t>
         </is>
       </c>
     </row>
@@ -3495,9 +3495,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0.3333333333,0,0.101010101,0,0.0303030303,0.1717171717,0]</t>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>[13.205923845,0,4.0017951045,0,1.2005385314]</t>
         </is>
       </c>
     </row>
@@ -3518,9 +3518,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0.2525252525,0,0.0909090909,0,0.0404040404,0.2424242424,0]</t>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>[11.7316690799,0,4.2234008688,0,1.8770670528]</t>
         </is>
       </c>
     </row>
@@ -3541,9 +3541,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0.2626262626,0,0.0808080808,0,0.0303030303,0.2424242424,0]</t>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>[12.0367806246,0,3.7036248076,0,1.3888593028]</t>
         </is>
       </c>
     </row>
@@ -3564,9 +3564,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0.2626262626,0,0.0808080808,0,0.0404040404,0.1919191919,0]</t>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>[12.9337380468,0,3.9796117067,0,1.9898058534]</t>
         </is>
       </c>
     </row>
@@ -3587,9 +3587,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0.3131313131,0,0.0909090909,0,0,0.1818181818,0]</t>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>[15.0263269683,0,4.3624820231,0,0]</t>
         </is>
       </c>
     </row>
@@ -3610,9 +3610,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0.2626262626,0,0.0808080808,0,0,0.1818181818,0]</t>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>[13.5694405962,0,4.1752124911,0,0]</t>
         </is>
       </c>
     </row>
@@ -3633,9 +3633,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7272727273,0,0.0707070707,0,0.0303030303,0.1717171717,0]</t>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.9493033858,0,1.6925585939]</t>
         </is>
       </c>
     </row>
@@ -3656,9 +3656,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7676767677,0,0.0202020202,0.2121212121,0]</t>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.1219570637]</t>
         </is>
       </c>
     </row>
@@ -3679,9 +3679,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0404040404,0.0606060606,0,0.0101010101,0.2323232323,0]</t>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.3048389709,3.4572584563,0,0.5762097427]</t>
         </is>
       </c>
     </row>
@@ -3702,9 +3702,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0.0101010101,0.0707070707,0,0.0404040404,0.1616161616,0]</t>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5426449203,3.798514442,0,2.1705796811]</t>
         </is>
       </c>
     </row>
@@ -3725,9 +3725,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0.0202020202,0.0707070707,0,0,0.2121212121,0]</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1054226526,3.868979284,0,0]</t>
         </is>
       </c>
     </row>
@@ -3748,9 +3748,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0.0303030303,0.0707070707,0,0.0202020202,0.1919191919,0]</t>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.6713592491,3.8998382478,0,1.1142394994]</t>
         </is>
       </c>
     </row>
@@ -3771,9 +3771,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0.0303030303,0.0707070707,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.5573676144,3.633857767,0,0.5191225381]</t>
         </is>
       </c>
     </row>
@@ -3794,9 +3794,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0404040404,0.0707070707,0,0.0101010101,0.1212121212,0]</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.9972610056,3.4952067597,0,0.4993152514]</t>
         </is>
       </c>
     </row>
@@ -3817,9 +3817,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0,0.0808080808,0,0.0101010101,0.0909090909,0]</t>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.7206561126,0,0.4650820141]</t>
         </is>
       </c>
     </row>
@@ -3840,9 +3840,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0202020202,0.0707070707,0,0.0505050505,0.1313131313,0]</t>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0341964639,3.6196876237,0,2.5854911598]</t>
         </is>
       </c>
     </row>
@@ -3863,9 +3863,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>[0.8484848485,0,0,0.0808080808,0,0,0.0707070707,0]</t>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.7545890588,0,0]</t>
         </is>
       </c>
     </row>
@@ -3886,9 +3886,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.1919191919,0,0,0.0808080808,0]</t>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.1503538312,0,0]</t>
         </is>
       </c>
     </row>
@@ -3909,9 +3909,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0,0.2626262626,0,0,0,0]</t>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3932,9 +3932,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.5151515152,0,0,0,0]</t>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3955,9 +3955,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0.0303030303,0,0.5757575758,0,0,0,0]</t>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>[1.3845885548,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -3978,9 +3978,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0.2828282828,0,0.3737373737,0,0,0,0]</t>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>[13.4102642427,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -4001,9 +4001,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0,0.2222222222,0,0.1818181818,0,0]</t>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.9223126093,0,0]</t>
         </is>
       </c>
     </row>
@@ -4024,9 +4024,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0,0.2424242424,0,0,0.1111111111,0]</t>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.9398085089,0,0]</t>
         </is>
       </c>
     </row>
@@ -4047,9 +4047,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0,0.1616161616,0,0,0.2121212121,0]</t>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,7.8250228293,0,0]</t>
         </is>
       </c>
     </row>
@@ -4070,9 +4070,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.202020202,0,0,0.2222222222,0]</t>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.1478672492,0,0]</t>
         </is>
       </c>
     </row>
@@ -4093,9 +4093,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.202020202,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.4835078762,0,0.4741753938]</t>
         </is>
       </c>
     </row>
@@ -4116,9 +4116,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.2121212121,0,0.0101010101,0.1616161616,0]</t>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.0571193825,0,0.4789104468]</t>
         </is>
       </c>
     </row>
@@ -4139,9 +4139,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0,0.2323232323,0,0,0.1616161616,0]</t>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.927015372,0,0]</t>
         </is>
       </c>
     </row>
@@ -4162,9 +4162,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0,0.1919191919,0,0.0202020202,0.1313131313,0]</t>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.7168359002,0,0.9175616737]</t>
         </is>
       </c>
     </row>
@@ -4185,9 +4185,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0,0.0808080808,0,0,0.1313131313,0]</t>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5556700563,0,0]</t>
         </is>
       </c>
     </row>
@@ -4208,9 +4208,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0303030303,0.101010101,0,0.0101010101,0.2222222222,0]</t>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0184700317,3.3949001057,0,0.3394900106]</t>
         </is>
       </c>
     </row>
@@ -4231,9 +4231,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0101010101,0.101010101,0,0.0505050505,0.2525252525,0]</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3314535608,3.3145356079,0,1.657267804]</t>
         </is>
       </c>
     </row>
@@ -4254,9 +4254,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0.0101010101,0.0707070707,0,0,0.4646464646,0]</t>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.489377053,3.425639371,0,0]</t>
         </is>
       </c>
     </row>
@@ -4277,9 +4277,9 @@
           <t>CD</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0101010101,0.0606060606,0,0,0.5252525253,0]</t>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5566929665,3.340157799,0,0]</t>
         </is>
       </c>
     </row>
@@ -4300,9 +4300,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0,0,0.0707070707,0,0,0.6262626263,0]</t>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.6002586838,0,0]</t>
         </is>
       </c>
     </row>
@@ -4323,9 +4323,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>[0.0909090909,0,0,0.2323232323,0,0,0.6767676768,0]</t>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,17.6421920612,0,0]</t>
         </is>
       </c>
     </row>
@@ -4346,9 +4346,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>[0.0909090909,0,0.0202020202,0.202020202,0,0,0.6868686869,0]</t>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.5596021599,15.5960215995,0,0]</t>
         </is>
       </c>
     </row>
@@ -4369,9 +4369,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>[0.1111111111,0,0.0101010101,0.2222222222,0,0,0.6565656566,0]</t>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7484743593,16.4664359048,0,0]</t>
         </is>
       </c>
     </row>
@@ -4392,9 +4392,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>[0.1111111111,0.0404040404,0,0.1717171717,0,0,0.6767676768,0]</t>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>[3.0639434488,0,13.0217596576,0,0]</t>
         </is>
       </c>
     </row>
@@ -4415,9 +4415,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>[0.0909090909,0.0202020202,0,0.202020202,0,0,0.6868686869,0]</t>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>[1.6525876483,0,16.5258764833,0,0]</t>
         </is>
       </c>
     </row>
@@ -4438,9 +4438,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>[0.101010101,0.0303030303,0,0.1616161616,0,0,0.7070707071,0]</t>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>[2.4968042659,0,13.316289418,0,0]</t>
         </is>
       </c>
     </row>
@@ -4461,9 +4461,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>[0.1111111111,0.0101010101,0,0.1818181818,0,0,0.696969697,0]</t>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>[0.7961376307,0,11.14592683,0,0]</t>
         </is>
       </c>
     </row>
@@ -4484,9 +4484,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>[0.0909090909,0.0505050505,0,0.8585858586,0,0,0,0]</t>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>[4.3287257565,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -4507,9 +4507,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>[0.1212121212,0.0808080808,0,0.797979798,0,0,0,0]</t>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>[6.7394547971,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -4530,9 +4530,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>[0.1212121212,0.0707070707,0,0.0404040404,0.1515151515,0.6161616162,0,0]</t>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>[6.066839974,0,3.4667656994,13.0003713728,0]</t>
         </is>
       </c>
     </row>
@@ -4553,9 +4553,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>[0.1414141414,0.0505050505,0,0.0404040404,0.2323232323,0,0.5353535354,0]</t>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>[4.060568879,0,3.2484551032,18.6786168434,0]</t>
         </is>
       </c>
     </row>
@@ -4576,9 +4576,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>[0.1919191919,0.2121212121,0,0.0707070707,0.0606060606,0.0101010101,0.4545454545,0]</t>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>[16.3486496369,0,5.449549879,4.6710427534,0.7785071256]</t>
         </is>
       </c>
     </row>
@@ -4599,9 +4599,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>[0.1616161616,0.202020202,0,0.0505050505,0.0303030303,0.0505050505,0.5050505051,0]</t>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>[16.298066862,0,4.0745167155,2.4447100293,4.0745167155]</t>
         </is>
       </c>
     </row>
@@ -4622,9 +4622,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>[0.1818181818,0.1616161616,0,0.0505050505,0.0606060606,0,0.5454545455,0]</t>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>[12.9621316743,0,4.0506661482,4.8607993779,0]</t>
         </is>
       </c>
     </row>
@@ -4645,9 +4645,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>[0.1717171717,0.202020202,0,0.0606060606,0.0909090909,0.0101010101,0.4646464646,0]</t>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>[14.9514888378,0,4.4854466513,6.728169977,0.7475744419]</t>
         </is>
       </c>
     </row>
@@ -4668,9 +4668,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>[0.1414141414,0.202020202,0,0.0606060606,0.1111111111,0,0.4848484848,0]</t>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>[13.9416670906,0,4.1825001272,7.6679168998,0]</t>
         </is>
       </c>
     </row>
@@ -4691,9 +4691,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>[0.1414141414,0.1616161616,0,0.0606060606,0.0909090909,0.0202020202,0.5252525253,0]</t>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t>[12.5137802044,0,4.6926675766,7.039001365,1.5642225255]</t>
         </is>
       </c>
     </row>
@@ -4714,9 +4714,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.0606060606,0,0.0606060606,0,0.0404040404,0.5454545455,0]</t>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>[4.581928396,0,4.581928396,0,3.0546189306]</t>
         </is>
       </c>
     </row>
@@ -4737,9 +4737,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.0707070707,0,0.0707070707,0,0.0202020202,0.5252525253,0]</t>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.0069315826,0,1.4305518807]</t>
         </is>
       </c>
     </row>
@@ -4760,9 +4760,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.404040404,0,0.0707070707,0,0.0202020202,0.5050505051,0]</t>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.2255780673,0,1.4930223049]</t>
         </is>
       </c>
     </row>
@@ -4783,9 +4783,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.4444444444,0,0.0101010101,0.5454545455,0]</t>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.7231177648]</t>
         </is>
       </c>
     </row>
@@ -4806,9 +4806,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0,0.0202020202,0.0707070707,0,0.0404040404,0.5656565657,0]</t>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.4494926594,5.0732243079,0,2.8989853188]</t>
         </is>
       </c>
     </row>
@@ -4829,9 +4829,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0,0.0606060606,0.0707070707,0,0,0.5757575758,0]</t>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t>[0,4.3760702746,5.1054153204,0,0]</t>
         </is>
       </c>
     </row>
@@ -4852,9 +4852,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0,0.0303030303,0.0606060606,0,0.0505050505,0.5353535354,0]</t>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.155518468,4.311036936,0,3.59253078]</t>
         </is>
       </c>
     </row>
@@ -4875,9 +4875,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0,0.0303030303,0.0505050505,0,0.0303030303,0.6262626263,0]</t>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.4987913971,4.1646523285,0,2.4987913971]</t>
         </is>
       </c>
     </row>
@@ -4898,9 +4898,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0.0101010101,0.0606060606,0,0.0404040404,0.6161616162,0]</t>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7539221968,4.5235331806,0,3.0156887871]</t>
         </is>
       </c>
     </row>
@@ -4921,9 +4921,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.0303030303,0.0101010101,0.0505050505,0,0.0303030303,0.6262626263,0]</t>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>[2.5066469829,0.8355489943,4.1777449715,0,2.5066469829]</t>
         </is>
       </c>
     </row>
@@ -4944,9 +4944,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.0101010101,0,0.0505050505,0.0101010101,0.0505050505,0.6060606061,0]</t>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>[0.8235657357,0,4.1178286785,0.8235657357,4.1178286785]</t>
         </is>
       </c>
     </row>
@@ -4967,9 +4967,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>[0.2424242424,0.0606060606,0,0.1212121212,0,0,0.5757575758,0]</t>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>[4.7935223641,0,9.5870447282,0,0]</t>
         </is>
       </c>
     </row>
@@ -4990,9 +4990,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>[0.1717171717,0.0909090909,0,0.0505050505,0.0606060606,0,0.6262626263,0]</t>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>[7.3463854552,0,4.0813252529,4.8975903035,0]</t>
         </is>
       </c>
     </row>
@@ -5013,9 +5013,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>[0.1717171717,0.0808080808,0,0.0505050505,0.0606060606,0,0.6363636364,0]</t>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>[6.4818538347,0,4.0511586467,4.861390376,0]</t>
         </is>
       </c>
     </row>
@@ -5036,9 +5036,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>[0.1616161616,0.1616161616,0,0.6767676768,0,0,0,0]</t>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>[13.1679247291,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5059,9 +5059,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>[0.3333333333,0,0,0.0606060606,0,0.6060606061,0,0]</t>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.8325340114,0,0]</t>
         </is>
       </c>
     </row>
@@ -5082,9 +5082,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0,0.0505050505,0.0606060606,0,0.0202020202,0.5555555556,0]</t>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t>[0,4.1760503811,5.0112604574,0,1.6704201525]</t>
         </is>
       </c>
     </row>
@@ -5105,9 +5105,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0,0,0.0606060606,0,0.0707070707,0.4949494949,0]</t>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.1287985187,0,5.9835982718]</t>
         </is>
       </c>
     </row>
@@ -5128,9 +5128,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0,0.0606060606,0,0.0505050505,0.5050505051,0]</t>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.0630205463,0,4.2191837886]</t>
         </is>
       </c>
     </row>
@@ -5151,9 +5151,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0,0.0404040404,0.0505050505,0,0.0303030303,0.5353535354,0]</t>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.5110947193,4.3888683991,0,2.6333210395]</t>
         </is>
       </c>
     </row>
@@ -5174,9 +5174,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0,0.0303030303,0.0606060606,0,0.0303030303,0.5353535354,0]</t>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.5683235575,5.136647115,0,2.5683235575]</t>
         </is>
       </c>
     </row>
@@ -5197,9 +5197,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0,0.0303030303,0.0606060606,0,0.0303030303,0.5151515152,0]</t>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.6411215987,5.2822431975,0,2.6411215987]</t>
         </is>
       </c>
     </row>
@@ -5220,9 +5220,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0,0.0202020202,0.0606060606,0,0.0303030303,0.5454545455,0]</t>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.7554378494,5.2663135482,0,2.6331567741]</t>
         </is>
       </c>
     </row>
@@ -5243,9 +5243,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0.0202020202,0.0606060606,0,0.0505050505,0.4848484848,0]</t>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.6622069271,4.9866207812,0,4.1555173177]</t>
         </is>
       </c>
     </row>
@@ -5266,9 +5266,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.4242424242,0,0.0606060606,0.5151515152,0]</t>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,5.2842722318]</t>
         </is>
       </c>
     </row>
@@ -5289,9 +5289,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.3131313131,0,0.2727272727,0.4141414141,0]</t>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,23.0143288071]</t>
         </is>
       </c>
     </row>
@@ -5312,9 +5312,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.2525252525,0,0.101010101,0,0,0.6464646465,0]</t>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.8276724934,0,0]</t>
         </is>
       </c>
     </row>
@@ -5335,9 +5335,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0,0,0.0707070707,0,0,0.6767676768,0]</t>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.1065391745,0,0]</t>
         </is>
       </c>
     </row>
@@ -5358,9 +5358,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0,0,0.0808080808,0,0,0.6565656566,0]</t>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.6551694351,0,0]</t>
         </is>
       </c>
     </row>
@@ -5381,9 +5381,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0,0,0.0808080808,0,0,0.6666666667,0]</t>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.779582848,0,0]</t>
         </is>
       </c>
     </row>
@@ -5404,9 +5404,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0,0,0.0606060606,0,0,0.6767676768,0]</t>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.2655219565,0,0]</t>
         </is>
       </c>
     </row>
@@ -5427,9 +5427,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0,0,0.0808080808,0,0,0.6060606061,0]</t>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.0753279211,0,0]</t>
         </is>
       </c>
     </row>
@@ -5450,9 +5450,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0,0,0.0909090909,0,0,0.5858585859,0]</t>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.2645792558,0,0]</t>
         </is>
       </c>
     </row>
@@ -5473,9 +5473,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.1313131313,0,0,0.4444444444,0]</t>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.2244610796,0,0]</t>
         </is>
       </c>
     </row>
@@ -5496,9 +5496,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0,0.5555555556,0,0,0,0]</t>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5519,9 +5519,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0,0,0.6060606061,0,0,0,0]</t>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5542,9 +5542,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0,0,0.6060606061,0,0,0,0]</t>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5565,9 +5565,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0,0,0.6767676768,0,0,0,0]</t>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5588,9 +5588,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.0202020202,0,0.7070707071,0,0,0,0]</t>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>[1.0052654455,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5611,9 +5611,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.1414141414,0,0.5656565657,0,0,0,0]</t>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>[6.8484589401,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -5634,9 +5634,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.1414141414,0,0.0808080808,0,0.4646464646,0,0]</t>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>[6.6790764626,0,3.8166151215,0,0.4770768902]</t>
         </is>
       </c>
     </row>
@@ -5657,9 +5657,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0505050505,0.0707070707,0,0.4747474747,0,0]</t>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.652688179,3.7137634506,0,3.1832258148]</t>
         </is>
       </c>
     </row>
@@ -5680,9 +5680,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0101010101,0.0707070707,0,0.0808080808,0.3737373737,0]</t>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5225418941,3.6577932584,0,4.1803351524]</t>
         </is>
       </c>
     </row>
@@ -5703,9 +5703,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0303030303,0.0808080808,0,0.0707070707,0.3232323232,0]</t>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.6416861848,4.377829826,0,3.8306010978]</t>
         </is>
       </c>
     </row>
@@ -5726,9 +5726,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0,0.0707070707,0,0.0303030303,0.3939393939,0]</t>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.9300445962,0,1.684304827]</t>
         </is>
       </c>
     </row>
@@ -5749,9 +5749,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0101010101,0.0707070707,0,0.0202020202,0.404040404,0]</t>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5696645028,3.9876515197,0,1.1393290056]</t>
         </is>
       </c>
     </row>
@@ -5772,9 +5772,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0.0404040404,0,0.0808080808,0,0.0101010101,0.3737373737,0]</t>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t>[2.1749447188,0,4.3498894377,0,0.5437361797]</t>
         </is>
       </c>
     </row>
@@ -5795,9 +5795,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0.0202020202,0.0808080808,0,0.0303030303,0.3636363636,0]</t>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1143334832,4.4573339327,0,1.6715002248]</t>
         </is>
       </c>
     </row>
@@ -5818,9 +5818,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0.0303030303,0,0.0808080808,0,0.0505050505,0.3232323232,0]</t>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.3413823828,0,2.7133639893]</t>
         </is>
       </c>
     </row>
@@ -5841,9 +5841,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.5050505051,0,0.0707070707,0,0.0606060606,0.3636363636,0]</t>
+      <c r="F235" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.8955568955,0,3.3390487676]</t>
         </is>
       </c>
     </row>
@@ -5864,9 +5864,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.4949494949,0,0.0707070707,0,0.0606060606,0.3737373737,0]</t>
+      <c r="F236" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.8309107611,0,3.2836377952]</t>
         </is>
       </c>
     </row>
@@ -5887,9 +5887,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.0707070707,0,0.0404040404,0.404040404,0]</t>
+      <c r="F237" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.0244404262,0,2.2996802436]</t>
         </is>
       </c>
     </row>
@@ -5910,9 +5910,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0404040404,0.0707070707,0,0.0404040404,0.3838383838,0]</t>
+      <c r="F238" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.2452909292,3.9292591261,0,2.2452909292]</t>
         </is>
       </c>
     </row>
@@ -5933,9 +5933,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E239" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0,0.0707070707,0,0.0101010101,0.4242424242,0]</t>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.8568866749,0,0.5509838107]</t>
         </is>
       </c>
     </row>
@@ -5956,9 +5956,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0202020202,0.0707070707,0,0.0202020202,0.4242424242,0]</t>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1295056138,3.9532696483,0,1.1295056138]</t>
         </is>
       </c>
     </row>
@@ -5979,9 +5979,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E241" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0101010101,0.0808080808,0,0.0303030303,0.3838383838,0]</t>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5234996007,4.1879968052,0,1.570498802]</t>
         </is>
       </c>
     </row>
@@ -6002,9 +6002,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0505050505,0.101010101,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F242" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.8709648429,3.7419296859,0,0.3741929686]</t>
         </is>
       </c>
     </row>
@@ -6025,9 +6025,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0606060606,0.101010101,0,0,0.1818181818,0]</t>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.3912336198,3.9853893663,0,0]</t>
         </is>
       </c>
     </row>
@@ -6048,9 +6048,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0303030303,0.101010101,0,0.1313131313,0,0]</t>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1007844716,3.6692815721,0,0]</t>
         </is>
       </c>
     </row>
@@ -6071,9 +6071,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.2323232323,0,0,0,0]</t>
+      <c r="F245" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6094,9 +6094,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.3232323232,0,0,0,0]</t>
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6117,9 +6117,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E247" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0,0.5050505051,0,0,0,0]</t>
+      <c r="F247" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6140,9 +6140,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0.0404040404,0,0.5555555556,0,0,0,0]</t>
+      <c r="F248" s="4" t="inlineStr">
+        <is>
+          <t>[1.5027494447,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6163,9 +6163,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0.1515151515,0,0.4343434343,0,0,0,0]</t>
+      <c r="F249" s="4" t="inlineStr">
+        <is>
+          <t>[5.8109880549,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6186,9 +6186,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0.1616161616,0,0.0808080808,0.0606060606,0.2727272727,0,0]</t>
+      <c r="F250" s="4" t="inlineStr">
+        <is>
+          <t>[6.1702647154,0,3.0851323577,2.3138492683,0]</t>
         </is>
       </c>
     </row>
@@ -6209,9 +6209,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0.1212121212,0,0.0909090909,0.0606060606,0,0.2525252525,0]</t>
+      <c r="F251" s="4" t="inlineStr">
+        <is>
+          <t>[4.3961155918,0,3.2970866938,2.1980577959,0]</t>
         </is>
       </c>
     </row>
@@ -6232,9 +6232,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0606060606,0,0.0808080808,0.1515151515,0,0.2424242424,0]</t>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>[2.2281079936,0,2.9708106581,5.570269984,0]</t>
         </is>
       </c>
     </row>
@@ -6255,9 +6255,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E253" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0808080808,0,0.0808080808,0.1717171717,0,0.202020202,0]</t>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>[2.8216820096,0,2.8216820096,5.9960742705,0]</t>
         </is>
       </c>
     </row>
@@ -6278,9 +6278,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0.1313131313,0,0.0909090909,0.1212121212,0,0.2929292929,0]</t>
+      <c r="F254" s="4" t="inlineStr">
+        <is>
+          <t>[4.4595923916,0,3.0874101172,4.116546823,0]</t>
         </is>
       </c>
     </row>
@@ -6301,9 +6301,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.101010101,0,0.101010101,0.1212121212,0,0.3838383838,0]</t>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>[3.0590925053,0,3.0590925053,3.6709110064,0]</t>
         </is>
       </c>
     </row>
@@ -6324,9 +6324,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.101010101,0,0.101010101,0.1616161616,0,0.2828282828,0]</t>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>[2.8995503911,0,2.8995503911,4.6392806258,0]</t>
         </is>
       </c>
     </row>
@@ -6347,9 +6347,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.101010101,0,0.1111111111,0.1616161616,0,0.303030303,0]</t>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.2313620408,4.7001629684,0]</t>
         </is>
       </c>
     </row>
@@ -6370,9 +6370,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.4444444444,0,0.101010101,0.1414141414,0,0.3131313131,0]</t>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,4.2556243921,0]</t>
         </is>
       </c>
     </row>
@@ -6393,9 +6393,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7272727273,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F259" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.290300146]</t>
         </is>
       </c>
     </row>
@@ -6416,9 +6416,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7070707071,0,0.0404040404,0.2525252525,0]</t>
+      <c r="F260" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.1262405076]</t>
         </is>
       </c>
     </row>
@@ -6439,9 +6439,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E261" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0202020202,0.1212121212,0,0.0303030303,0.2727272727,0]</t>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.58981905,3.5389142997,0,0.8847285749]</t>
         </is>
       </c>
     </row>
@@ -6462,9 +6462,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E262" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0,0.1111111111,0,0.0303030303,0.3131313131,0]</t>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.279623062,0,0.8944426533]</t>
         </is>
       </c>
     </row>
@@ -6485,9 +6485,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0101010101,0.1111111111,0,0.0606060606,0.2929292929,0]</t>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.280665029,3.0873153189,0,1.683990174]</t>
         </is>
       </c>
     </row>
@@ -6508,9 +6508,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E264" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0101010101,0.1111111111,0,0.0101010101,0.3434343434,0]</t>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.2995169276,3.294686204,0,0.2995169276]</t>
         </is>
       </c>
     </row>
@@ -6531,9 +6531,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E265" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0101010101,0.1313131313,0,0.0404040404,0.202020202,0]</t>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.24670519,3.2071674701,0,0.98682076]</t>
         </is>
       </c>
     </row>
@@ -6554,9 +6554,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E266" s="4" t="inlineStr">
-        <is>
-          <t>[0.1818181818,0,0.4444444444,0.1515151515,0,0.0202020202,0.202020202,0]</t>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>[0,9.9624338764,3.396284276,0,0.4528379035]</t>
         </is>
       </c>
     </row>
@@ -6577,9 +6577,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E267" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.0606060606,0.3838383838,0.1515151515,0,0.0505050505,0.1414141414,0]</t>
+      <c r="F267" s="4" t="inlineStr">
+        <is>
+          <t>[1.3485479266,8.540803535,3.3713698164,0,1.1237899388]</t>
         </is>
       </c>
     </row>
@@ -6600,9 +6600,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E268" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.0202020202,0.3838383838,0.1616161616,0,0.1212121212,0.0606060606,0]</t>
+      <c r="F268" s="4" t="inlineStr">
+        <is>
+          <t>[0.4122042225,7.8318802271,3.2976337798,0,2.4732253349]</t>
         </is>
       </c>
     </row>
@@ -6623,9 +6623,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E269" s="4" t="inlineStr">
-        <is>
-          <t>[0.1919191919,0.0404040404,0,0.6464646465,0,0,0.1212121212,0]</t>
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>[0.8366962176,0,13.3871394811,0,0]</t>
         </is>
       </c>
     </row>
@@ -6646,9 +6646,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E270" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.0303030303,0,0.5858585859,0,0,0.1313131313,0]</t>
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>[0.6017680312,0,11.6341819374,0,0]</t>
         </is>
       </c>
     </row>
@@ -6669,9 +6669,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E271" s="4" t="inlineStr">
-        <is>
-          <t>[0.1212121212,0.101010101,0,0.1111111111,0.101010101,0,0.5656565657,0]</t>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>[1.9711290238,0,2.1682419261,1.9711290238,0]</t>
         </is>
       </c>
     </row>
@@ -6692,9 +6692,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E272" s="4" t="inlineStr">
-        <is>
-          <t>[0.1414141414,0.0505050505,0,0.1111111111,0.0909090909,0,0.6060606061,0]</t>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>[0.9719822269,0,2.1383608992,1.7495680084,0]</t>
         </is>
       </c>
     </row>
@@ -6715,9 +6715,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E273" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0101010101,0.5858585859,0,0,0,0]</t>
+      <c r="F273" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.153654537,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -6738,9 +6738,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0.0101010101,0.1313131313,0,0.3535353535,0,0]</t>
+      <c r="F274" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.1934605566,2.5149872357,0,0]</t>
         </is>
       </c>
     </row>
@@ -6761,9 +6761,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E275" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0.0101010101,0.1111111111,0,0.0202020202,0.3535353535,0]</t>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.2225264987,2.4477914852,0,0.4450529973]</t>
         </is>
       </c>
     </row>
@@ -6784,9 +6784,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E276" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.1111111111,0,0.0202020202,0.3535353535,0]</t>
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.6110296644,0,0.4747326663]</t>
         </is>
       </c>
     </row>
@@ -6807,9 +6807,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E277" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0202020202,0.1111111111,0,0.0202020202,0.2929292929,0]</t>
+      <c r="F277" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.445395426,2.4496748428,0,0.445395426]</t>
         </is>
       </c>
     </row>
@@ -6830,9 +6830,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E278" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0101010101,0.1111111111,0,0,0.2525252525,0]</t>
+      <c r="F278" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.2304265722,2.5346922941,0,0]</t>
         </is>
       </c>
     </row>
@@ -6853,9 +6853,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E279" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0202020202,0.0707070707,0,0.0303030303,0.202020202,0]</t>
+      <c r="F279" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.6593547865,2.3077417526,0,0.9890321797]</t>
         </is>
       </c>
     </row>
@@ -6876,9 +6876,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E280" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0.0101010101,0.0707070707,0,0,0.202020202,0]</t>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3464597708,2.4252183958,0,0]</t>
         </is>
       </c>
     </row>
@@ -6899,9 +6899,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E281" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.0606060606,0,0.0202020202,0.1616161616,0]</t>
+      <c r="F281" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.3767490113,0,0.7922496704]</t>
         </is>
       </c>
     </row>
@@ -6922,9 +6922,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7575757576,0,0.0606060606,0,0,0.1818181818,0]</t>
+      <c r="F282" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.4425457068,0,0]</t>
         </is>
       </c>
     </row>
@@ -6945,9 +6945,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E283" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7474747475,0,0.0606060606,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.4742268439,0,0.4123711406]</t>
         </is>
       </c>
     </row>
@@ -6968,9 +6968,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E284" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.0606060606,0,0.0101010101,0.202020202,0]</t>
+      <c r="F284" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.5417764782,0,0.423629413]</t>
         </is>
       </c>
     </row>
@@ -6991,9 +6991,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E285" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0.0303030303,0.0606060606,0,0.0202020202,0.101010101,0]</t>
+      <c r="F285" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.125888818,2.251777636,0,0.7505925453]</t>
         </is>
       </c>
     </row>
@@ -7014,9 +7014,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E286" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0.0202020202,0.0707070707,0,0.0202020202,0.0707070707,0]</t>
+      <c r="F286" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7302864542,2.5560025896,0,0.7302864542]</t>
         </is>
       </c>
     </row>
@@ -7037,9 +7037,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E287" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0.0202020202,0.0606060606,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7650517378,2.2951552133,0,0.3825258689]</t>
         </is>
       </c>
     </row>
@@ -7060,9 +7060,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E288" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0606060606,0,0.0202020202,0.1414141414,0]</t>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.3059372869,0,0.7686457623]</t>
         </is>
       </c>
     </row>
@@ -7083,9 +7083,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E289" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0202020202,0.0606060606,0,0,0.1919191919,0]</t>
+      <c r="F289" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8145877257,2.4437631771,0,0]</t>
         </is>
       </c>
     </row>
@@ -7106,9 +7106,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E290" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0.0303030303,0.0606060606,0,0,0.2222222222,0]</t>
+      <c r="F290" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2607944199,2.5215888399,0,0]</t>
         </is>
       </c>
     </row>
@@ -7129,9 +7129,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E291" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0303030303,0.0606060606,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F291" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.3488941167,2.6977882334,0,0.4496313722]</t>
         </is>
       </c>
     </row>
@@ -7152,9 +7152,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E292" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0303030303,0.0505050505,0,0.0505050505,0.2121212121,0]</t>
+      <c r="F292" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.3142470464,2.190411744,0,2.190411744]</t>
         </is>
       </c>
     </row>
@@ -7175,9 +7175,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E293" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0404040404,0.0505050505,0,0,0.2828282828,0]</t>
+      <c r="F293" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.7784706108,2.2230882635,0,0]</t>
         </is>
       </c>
     </row>
@@ -7198,9 +7198,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E294" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.3131313131,0,0,0,0]</t>
+      <c r="F294" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7221,9 +7221,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E295" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0,0.3535353535,0,0,0,0]</t>
+      <c r="F295" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7244,9 +7244,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E296" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0,0.5555555556,0,0,0,0]</t>
+      <c r="F296" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7267,9 +7267,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E297" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0.0101010101,0,0.595959596,0,0,0,0]</t>
+      <c r="F297" s="4" t="inlineStr">
+        <is>
+          <t>[0.4859426992,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7290,9 +7290,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E298" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0.1515151515,0,0.4545454545,0,0,0,0]</t>
+      <c r="F298" s="4" t="inlineStr">
+        <is>
+          <t>[7.3759415362,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7313,9 +7313,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E299" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0,0.1919191919,0,0.2626262626,0,0]</t>
+      <c r="F299" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.0801350334,0,0]</t>
         </is>
       </c>
     </row>
@@ -7336,9 +7336,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E300" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0,0.2121212121,0,0.0101010101,0.2323232323,0]</t>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.2164959023,0,0.4864998049]</t>
         </is>
       </c>
     </row>
@@ -7359,9 +7359,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E301" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.2222222222,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.9181879472,0,0.4962812703]</t>
         </is>
       </c>
     </row>
@@ -7382,9 +7382,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E302" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.2121212121,0,0,0.2121212121,0]</t>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.2823664532,0,0]</t>
         </is>
       </c>
     </row>
@@ -7405,9 +7405,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E303" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0,0.202020202,0,0,0.2424242424,0]</t>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.8240466614,0,0]</t>
         </is>
       </c>
     </row>
@@ -7428,9 +7428,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E304" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0,0.1818181818,0,0,0.1919191919,0]</t>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.627753885,0,0]</t>
         </is>
       </c>
     </row>
@@ -7451,9 +7451,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E305" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0,0.1717171717,0,0.0101010101,0.2222222222,0]</t>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.3071266378,0,0.6063015669]</t>
         </is>
       </c>
     </row>
@@ -7474,9 +7474,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E306" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0,0.1717171717,0,0.0202020202,0.1818181818,0]</t>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.1006846077,0,1.1883158362]</t>
         </is>
       </c>
     </row>
@@ -7497,9 +7497,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E307" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0,0.1818181818,0,0,0.2222222222,0]</t>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.6500161627,0,0]</t>
         </is>
       </c>
     </row>
@@ -7520,9 +7520,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E308" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7878787879,0.0101010101,0,0.202020202,0]</t>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0.5904511621,0]</t>
         </is>
       </c>
     </row>
@@ -7543,9 +7543,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E309" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.797979798,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.5932874522]</t>
         </is>
       </c>
     </row>
@@ -7566,9 +7566,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E310" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7777777778,0,0.0202020202,0.202020202,0]</t>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.1951735408]</t>
         </is>
       </c>
     </row>
@@ -7589,9 +7589,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E311" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0.0404040404,0.0505050505,0,0.0101010101,0.202020202,0]</t>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.4002210112,3.000276264,0,0.6000552528]</t>
         </is>
       </c>
     </row>
@@ -7612,9 +7612,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.1818181818,0.0505050505,0,0.0101010101,0.2323232323,0]</t>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>[0,10.7559241966,2.9877567213,0,0.5975513443]</t>
         </is>
       </c>
     </row>
@@ -7635,9 +7635,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E313" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0.1717171717,0.0505050505,0,0.0404040404,0.1919191919,0]</t>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>[0,10.1946738849,2.9984334956,0,2.3987467965]</t>
         </is>
       </c>
     </row>
@@ -7658,9 +7658,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E314" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.1616161616,0.0505050505,0,0.0404040404,0.1919191919,0]</t>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>[0,9.285575357,2.9017422991,0,2.3213938393]</t>
         </is>
       </c>
     </row>
@@ -7681,9 +7681,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E315" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.1717171717,0.0404040404,0,0.0505050505,0.202020202,0]</t>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>[0,9.9910048274,2.3508246653,0,2.9385308316]</t>
         </is>
       </c>
     </row>
@@ -7704,9 +7704,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E316" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.1515151515,0.0404040404,0,0.0505050505,0.2222222222,0]</t>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>[0,8.8610007648,2.3629335373,0,2.9536669216]</t>
         </is>
       </c>
     </row>
@@ -7727,9 +7727,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E317" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0.1919191919,0.0505050505,0,0.0505050505,0.1717171717,0]</t>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>[0,11.2575477738,2.962512572,0,2.962512572]</t>
         </is>
       </c>
     </row>
@@ -7750,9 +7750,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E318" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0.0101010101,0.1313131313,0.0303030303,0,0.2828282828,0.1313131313,0]</t>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>[0.580900498,7.5517064737,1.7427014939,0,16.2652139433]</t>
         </is>
       </c>
     </row>
@@ -7773,9 +7773,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E319" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0.0101010101,0,0.1717171717,0,0,0.4242424242,0]</t>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>[0.5910825684,0,10.0484036621,0,0]</t>
         </is>
       </c>
     </row>
@@ -7796,9 +7796,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E320" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0.0101010101,0,0.1515151515,0,0,0.4444444444,0]</t>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>[0.5890100104,0,8.8351501564,0,0]</t>
         </is>
       </c>
     </row>
@@ -7819,9 +7819,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E321" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0.0101010101,0,0.5454545455,0,0,0,0]</t>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>[0.5295174095,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7842,9 +7842,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E322" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0.4545454545,0,0.1717171717,0,0,0,0]</t>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>[24.9313045557,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -7865,9 +7865,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E323" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0,0.0505050505,0,0.1313131313,0,0]</t>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.7637232507,0,0]</t>
         </is>
       </c>
     </row>
@@ -7888,9 +7888,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E324" s="4" t="inlineStr">
-        <is>
-          <t>[0.8282828283,0,0.0303030303,0.0505050505,0,0,0.0909090909,0]</t>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.6542148742,2.7570247904,0,0]</t>
         </is>
       </c>
     </row>
@@ -7911,9 +7911,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E325" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0,0.0202020202,0.0505050505,0,0.0101010101,0.1111111111,0]</t>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0984034744,2.746008686,0,0.5492017372]</t>
         </is>
       </c>
     </row>
@@ -7934,9 +7934,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E326" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0,0.0101010101,0.0505050505,0,0.0303030303,0.101010101,0]</t>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5461910692,2.7309553459,0,1.6385732075]</t>
         </is>
       </c>
     </row>
@@ -7957,9 +7957,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E327" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0.0101010101,0.0505050505,0,0.0404040404,0.0808080808,0]</t>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5461303403,2.7306517014,0,2.1845213611]</t>
         </is>
       </c>
     </row>
@@ -7980,9 +7980,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E328" s="4" t="inlineStr">
-        <is>
-          <t>[0.797979798,0,0.0303030303,0.0707070707,0,0.0101010101,0.0909090909,0]</t>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.4243485435,3.3234799348,0,0.4747828478]</t>
         </is>
       </c>
     </row>
@@ -8003,9 +8003,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E329" s="4" t="inlineStr">
-        <is>
-          <t>[0.797979798,0,0.0202020202,0.0707070707,0,0.0202020202,0.0909090909,0]</t>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8734460767,3.0570612683,0,0.8734460767]</t>
         </is>
       </c>
     </row>
@@ -8026,9 +8026,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E330" s="4" t="inlineStr">
-        <is>
-          <t>[0.8484848485,0,0,0.0707070707,0,0.0101010101,0.0707070707,0]</t>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0482045752,0,0.4354577965]</t>
         </is>
       </c>
     </row>
@@ -8049,9 +8049,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E331" s="4" t="inlineStr">
-        <is>
-          <t>[0.8282828283,0,0.0303030303,0.0707070707,0,0.0202020202,0.0505050505,0]</t>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2911796568,3.0127525326,0,0.8607864379]</t>
         </is>
       </c>
     </row>
@@ -8072,9 +8072,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E332" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0.0707070707,0.0606060606,0,0.0101010101,0.0707070707,0]</t>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.0890866829,2.6477885853,0,0.4412980976]</t>
         </is>
       </c>
     </row>
@@ -8095,9 +8095,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0202020202,0.0606060606,0,0.0404040404,0.1212121212,0]</t>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8948862723,2.684658817,0,1.7897725447]</t>
         </is>
       </c>
     </row>
@@ -8118,9 +8118,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E334" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0404040404,0.0606060606,0,0.0505050505,0.1111111111,0]</t>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.8163290403,2.7244935605,0,2.2704113004]</t>
         </is>
       </c>
     </row>
@@ -8141,9 +8141,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E335" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0.0101010101,0.0606060606,0,0.0404040404,0.101010101,0]</t>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4486639858,2.6919839147,0,1.7946559431]</t>
         </is>
       </c>
     </row>
@@ -8164,9 +8164,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E336" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.101010101,0,0,0.1414141414,0]</t>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.4037724781,0,0]</t>
         </is>
       </c>
     </row>
@@ -8187,9 +8187,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0,0.0808080808,0,0,0.1313131313,0]</t>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.4735858338,0,0]</t>
         </is>
       </c>
     </row>
@@ -8210,9 +8210,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E338" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0606060606,0,0,0.1616161616,0]</t>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.6825592859,0,0]</t>
         </is>
       </c>
     </row>
@@ -8233,9 +8233,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E339" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.0909090909,0,0,0.1515151515,0]</t>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.9519411585,0,0]</t>
         </is>
       </c>
     </row>
@@ -8256,9 +8256,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E340" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0808080808,0,0,0.1414141414,0]</t>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5095763746,0,0]</t>
         </is>
       </c>
     </row>
@@ -8279,9 +8279,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E341" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0,0.1818181818,0,0,0.1212121212,0]</t>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,7.6868271854,0,0]</t>
         </is>
       </c>
     </row>
@@ -8302,9 +8302,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E342" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.3131313131,0,0,0,0]</t>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8325,9 +8325,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E343" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.4848484848,0,0,0,0]</t>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8348,9 +8348,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E344" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0,0,0.7676767677,0,0,0,0]</t>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8371,9 +8371,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E345" s="4" t="inlineStr">
-        <is>
-          <t>[0.1212121212,0.101010101,0,0.7777777778,0,0,0,0]</t>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>[4.4827569013,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8394,9 +8394,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E346" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0.5656565657,0,0.202020202,0,0,0,0]</t>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>[23.5967514464,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8417,9 +8417,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E347" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.5151515152,0,0.0606060606,0.0303030303,0.1818181818,0,0]</t>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>[23.121394564,0,2.7201640664,1.3600820332,0]</t>
         </is>
       </c>
     </row>
@@ -8440,9 +8440,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E348" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.5252525253,0,0.0606060606,0,0.0404040404,0.1515151515,0]</t>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>[22.7728236001,0,2.6276334923,0,1.7517556615]</t>
         </is>
       </c>
     </row>
@@ -8463,9 +8463,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E349" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0.5454545455,0,0.0606060606,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>[22.8704130035,0,2.5411570004,0,0.4235261667]</t>
         </is>
       </c>
     </row>
@@ -8486,9 +8486,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E350" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0.5252525253,0,0.0606060606,0,0.0303030303,0.1515151515,0]</t>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>[22.7733621657,0,2.6276956345,0,1.3138478173]</t>
         </is>
       </c>
     </row>
@@ -8509,9 +8509,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E351" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.5454545455,0,0.0606060606,0,0.0101010101,0.1616161616,0]</t>
+      <c r="F351" s="4" t="inlineStr">
+        <is>
+          <t>[23.9078268032,0,2.6564252004,0,0.4427375334]</t>
         </is>
       </c>
     </row>
@@ -8532,9 +8532,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E352" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.5151515152,0,0.0606060606,0,0.0202020202,0.1818181818,0]</t>
+      <c r="F352" s="4" t="inlineStr">
+        <is>
+          <t>[22.9530108044,0,2.7003542123,0,0.9001180708]</t>
         </is>
       </c>
     </row>
@@ -8555,9 +8555,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E353" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0.5454545455,0,0.0606060606,0,0.0202020202,0.1414141414,0]</t>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>[23.1280405601,0,2.5697822845,0,0.8565940948]</t>
         </is>
       </c>
     </row>
@@ -8578,9 +8578,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E354" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.5555555556,0,0.0606060606,0,0,0.1717171717,0]</t>
+      <c r="F354" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.5714628774,0,0]</t>
         </is>
       </c>
     </row>
@@ -8601,9 +8601,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E355" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0,0.0707070707,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.4797681285,0,0.3542525898]</t>
         </is>
       </c>
     </row>
@@ -8624,9 +8624,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E356" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.6666666667,0,0.0707070707,0,0.0505050505,0.2121212121,0]</t>
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.5136981819,0,1.7954987014]</t>
         </is>
       </c>
     </row>
@@ -8647,9 +8647,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E357" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.696969697,0,0.0909090909,0,0,0.2121212121,0]</t>
+      <c r="F357" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1421575478,0,0]</t>
         </is>
       </c>
     </row>
@@ -8670,9 +8670,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E358" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.6262626263,0,0.0909090909,0,0,0.2828282828,0]</t>
+      <c r="F358" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.4097615333,0,0]</t>
         </is>
       </c>
     </row>
@@ -8693,9 +8693,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E359" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.0808080808,0,0,0.303030303,0]</t>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1361522489,0,0]</t>
         </is>
       </c>
     </row>
@@ -8716,9 +8716,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E360" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0,0.0909090909,0,0,0.2525252525,0]</t>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3132661054,0,0]</t>
         </is>
       </c>
     </row>
@@ -8739,9 +8739,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E361" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0,0.0808080808,0,0,0.2929292929,0]</t>
+      <c r="F361" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1116702002,0,0]</t>
         </is>
       </c>
     </row>
@@ -8762,9 +8762,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E362" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0,0.0707070707,0,0,0.3939393939,0]</t>
+      <c r="F362" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0896794798,0,0]</t>
         </is>
       </c>
     </row>
@@ -8785,9 +8785,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E363" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.0707070707,0,0,0.404040404,0]</t>
+      <c r="F363" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.2477184987,0,0]</t>
         </is>
       </c>
     </row>
@@ -8808,9 +8808,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E364" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0606060606,0,0,0.3737373737,0]</t>
+      <c r="F364" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.6168779222,0,0]</t>
         </is>
       </c>
     </row>
@@ -8831,9 +8831,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E365" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0,0.0707070707,0,0,0.3333333333,0]</t>
+      <c r="F365" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.9188619712,0,0]</t>
         </is>
       </c>
     </row>
@@ -8854,9 +8854,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E366" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.0404040404,0,0.2323232323,0,0,0.3737373737,0]</t>
+      <c r="F366" s="4" t="inlineStr">
+        <is>
+          <t>[1.7300757688,0,9.9479356708,0,0]</t>
         </is>
       </c>
     </row>
@@ -8877,9 +8877,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E367" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.0404040404,0,0.2121212121,0,0,0.3939393939,0]</t>
+      <c r="F367" s="4" t="inlineStr">
+        <is>
+          <t>[1.7432973674,0,9.1523111786,0,0]</t>
         </is>
       </c>
     </row>
@@ -8900,9 +8900,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E368" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.0404040404,0,0.6060606061,0,0,0,0]</t>
+      <c r="F368" s="4" t="inlineStr">
+        <is>
+          <t>[1.7859028221,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8923,9 +8923,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E369" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.1212121212,0,0.5555555556,0,0,0,0]</t>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>[5.1022969379,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -8946,9 +8946,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E370" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0,0.2525252525,0,0.303030303,0,0]</t>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.7687179741,0,0]</t>
         </is>
       </c>
     </row>
@@ -8969,9 +8969,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E371" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0,0,0.2525252525,0,0.0101010101,0.303030303,0]</t>
+      <c r="F371" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.9861111872,0,0.4394444475]</t>
         </is>
       </c>
     </row>
@@ -8992,9 +8992,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E372" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0,0,0.2828282828,0,0.0101010101,0.2727272727,0]</t>
+      <c r="F372" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,12.0452887966,0,0.4301888856]</t>
         </is>
       </c>
     </row>
@@ -9015,9 +9015,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E373" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.2727272727,0,0.0303030303,0.2727272727,0]</t>
+      <c r="F373" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,11.7465166549,0,1.3051685172]</t>
         </is>
       </c>
     </row>
@@ -9038,9 +9038,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E374" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0.0303030303,0.0707070707,0,0,0.303030303,0]</t>
+      <c r="F374" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.3367607523,3.1191084221,0,0]</t>
         </is>
       </c>
     </row>
@@ -9061,9 +9061,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E375" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0404040404,0.0606060606,0,0.0404040404,0.2525252525,0]</t>
+      <c r="F375" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.7497706715,2.6246560073,0,1.7497706715]</t>
         </is>
       </c>
     </row>
@@ -9084,9 +9084,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E376" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.0707070707,0,0.0202020202,0.2222222222,0]</t>
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4565861486,3.1961030399,0,0.9131722971]</t>
         </is>
       </c>
     </row>
@@ -9107,9 +9107,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E377" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0202020202,0.0606060606,0,0.0303030303,0.2828282828,0]</t>
+      <c r="F377" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9501830172,2.8505490516,0,1.4252745258]</t>
         </is>
       </c>
     </row>
@@ -9130,9 +9130,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E378" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0202020202,0.0606060606,0,0.0505050505,0.2424242424,0]</t>
+      <c r="F378" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.932210679,2.796632037,0,2.3305266975]</t>
         </is>
       </c>
     </row>
@@ -9153,9 +9153,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E379" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0101010101,0.0606060606,0,0.0303030303,0.2424242424,0]</t>
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4559968882,2.735981329,0,1.3679906645]</t>
         </is>
       </c>
     </row>
@@ -9176,9 +9176,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E380" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.696969697,0,0.0404040404,0.2626262626,0]</t>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.7991056917]</t>
         </is>
       </c>
     </row>
@@ -9199,9 +9199,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E381" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0.0202020202,0.0606060606,0,0.0404040404,0.303030303,0]</t>
+      <c r="F381" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.946299435,2.8388983049,0,1.89259887]</t>
         </is>
       </c>
     </row>
@@ -9222,9 +9222,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E382" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0303030303,0.0606060606,0,0.0101010101,0.3131313131,0]</t>
+      <c r="F382" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.4088563184,2.8177126367,0,0.4696187728]</t>
         </is>
       </c>
     </row>
@@ -9245,9 +9245,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E383" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0101010101,0.0606060606,0,0.0404040404,0.2727272727,0]</t>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4567644962,2.7405869774,0,1.8270579849]</t>
         </is>
       </c>
     </row>
@@ -9268,9 +9268,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E384" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0101010101,0.0606060606,0,0.0404040404,0.2828282828,0]</t>
+      <c r="F384" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.452097344,2.7125840639,0,1.8083893759]</t>
         </is>
       </c>
     </row>
@@ -9291,9 +9291,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E385" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0.0505050505,0.0606060606,0,0.0101010101,0.3131313131,0]</t>
+      <c r="F385" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.3319903512,2.7983884214,0,0.4663980702]</t>
         </is>
       </c>
     </row>
@@ -9314,9 +9314,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E386" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0101010101,0.0505050505,0,0.0202020202,0.3333333333,0]</t>
+      <c r="F386" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4725423292,2.3627116462,0,0.9450846585]</t>
         </is>
       </c>
     </row>
@@ -9337,9 +9337,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E387" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0,0.0606060606,0,0,0.2929292929,0]</t>
+      <c r="F387" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.5884032433,0,0]</t>
         </is>
       </c>
     </row>
@@ -9360,9 +9360,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E388" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0.0202020202,0.0707070707,0,0.0101010101,0.2121212121,0]</t>
+      <c r="F388" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7885770851,2.7600197978,0,0.3942885425]</t>
         </is>
       </c>
     </row>
@@ -9383,9 +9383,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E389" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0303030303,0.2121212121,0,0,0,0]</t>
+      <c r="F389" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1591464798,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -9406,9 +9406,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E390" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0505050505,0.0707070707,0,0.202020202,0,0]</t>
+      <c r="F390" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.933608326,2.7070516564,0,2.7070516564]</t>
         </is>
       </c>
     </row>
@@ -9429,9 +9429,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E391" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0,0.3333333333,0,0.0101010101,0,0]</t>
+      <c r="F391" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,13.2135259051,0,0]</t>
         </is>
       </c>
     </row>
@@ -9452,9 +9452,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E392" s="4" t="inlineStr">
-        <is>
-          <t>[0.9090909091,0,0,0.0808080808,0,0.0101010101,0,0]</t>
+      <c r="F392" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -9475,9 +9475,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E393" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0.1515151515,0,0.2323232323,0,0,0.2626262626,0]</t>
+      <c r="F393" s="4" t="inlineStr">
+        <is>
+          <t>[5.9203299651,0,9.0778392798,0,0]</t>
         </is>
       </c>
     </row>
@@ -9498,9 +9498,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E394" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0.0404040404,0,0.0303030303,0.1919191919,0,0.2222222222,0]</t>
+      <c r="F394" s="4" t="inlineStr">
+        <is>
+          <t>[1.3081866416,0,0.9811399812,6.2138865475,0]</t>
         </is>
       </c>
     </row>
@@ -9521,9 +9521,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E395" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0,0.2626262626,0,0,0,0]</t>
+      <c r="F395" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -9544,9 +9544,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E396" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0.0101010101,0.0303030303,0,0.1414141414,0,0]</t>
+      <c r="F396" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4946416658,1.4839249974,0,0.4946416658]</t>
         </is>
       </c>
     </row>
@@ -9567,9 +9567,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E397" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0404040404,0,0,0.1818181818,0]</t>
+      <c r="F397" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.132881183,0,0]</t>
         </is>
       </c>
     </row>
@@ -9590,9 +9590,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E398" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0.0202020202,0,0.0404040404,0,0,0.1717171717,0]</t>
+      <c r="F398" s="4" t="inlineStr">
+        <is>
+          <t>[1.1457030906,0,2.2914061813,0,0]</t>
         </is>
       </c>
     </row>
@@ -9613,9 +9613,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E399" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0,0,0.0303030303,0,0.0202020202,0.1414141414,0]</t>
+      <c r="F399" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.6905714174,0,1.1270476116]</t>
         </is>
       </c>
     </row>
@@ -9636,9 +9636,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E400" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0.0202020202,0,0.0303030303,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F400" s="4" t="inlineStr">
+        <is>
+          <t>[1.1243541441,0,1.6865312161,0,0.562177072]</t>
         </is>
       </c>
     </row>
@@ -9659,9 +9659,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E401" s="4" t="inlineStr">
-        <is>
-          <t>[0.7878787879,0,0,0.0303030303,0,0,0.1818181818,0]</t>
+      <c r="F401" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7374945126,0,0]</t>
         </is>
       </c>
     </row>
@@ -9682,9 +9682,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E402" s="4" t="inlineStr">
-        <is>
-          <t>[0.8080808081,0,0,0.0303030303,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F402" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7014765868,0,0.5671588623]</t>
         </is>
       </c>
     </row>
@@ -9705,9 +9705,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E403" s="4" t="inlineStr">
-        <is>
-          <t>[0.8181818182,0,0,0.0404040404,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F403" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.2272908277,0,0.5568227069]</t>
         </is>
       </c>
     </row>
@@ -9728,9 +9728,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E404" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7878787879,0,0.0303030303,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F404" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7434222632,0,0.5811407544]</t>
         </is>
       </c>
     </row>
@@ -9751,9 +9751,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E405" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.8080808081,0,0.0303030303,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F405" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.6809046618,0,0.5603015539]</t>
         </is>
       </c>
     </row>
@@ -9774,9 +9774,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E406" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0101010101,0.0303030303,0,0,0.202020202,0]</t>
+      <c r="F406" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5935708824,1.7807126471,0,0]</t>
         </is>
       </c>
     </row>
@@ -9797,9 +9797,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E407" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.0303030303,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F407" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7579998222,0,0.5859999407]</t>
         </is>
       </c>
     </row>
@@ -9820,9 +9820,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E408" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0,0.0303030303,0,0.0101010101,0.2121212121,0]</t>
+      <c r="F408" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.790736973,0,0.5969123243]</t>
         </is>
       </c>
     </row>
@@ -9843,9 +9843,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E409" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0101010101,0.0404040404,0,0,0.1919191919,0]</t>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5855979938,2.3423919753,0,0]</t>
         </is>
       </c>
     </row>
@@ -9866,9 +9866,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E410" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.0303030303,0,0.0101010101,0.202020202,0]</t>
+      <c r="F410" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7903361355,0,0.5967787118]</t>
         </is>
       </c>
     </row>
@@ -9889,9 +9889,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E411" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0,0.0303030303,0,0.0202020202,0.2323232323,0]</t>
+      <c r="F411" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.8947701264,0,1.2631800842]</t>
         </is>
       </c>
     </row>
@@ -9912,9 +9912,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E412" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0,0.0707070707,0,0.0101010101,0.1616161616,0]</t>
+      <c r="F412" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.1968780823,0,0.5995540118]</t>
         </is>
       </c>
     </row>
@@ -9935,9 +9935,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E413" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0,0.101010101,0,0,0.1515151515,0]</t>
+      <c r="F413" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.0599400057,0,0]</t>
         </is>
       </c>
     </row>
@@ -9958,9 +9958,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E414" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0,0,0.4141414141,0,0,0.2222222222,0]</t>
+      <c r="F414" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.7127587228,0,0]</t>
         </is>
       </c>
     </row>
@@ -9981,9 +9981,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E415" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0,0,0.4141414141,0,0,0.2121212121,0]</t>
+      <c r="F415" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.3455389449,0,0]</t>
         </is>
       </c>
     </row>
@@ -10004,9 +10004,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E416" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0,0,0.6464646465,0,0,0,0]</t>
+      <c r="F416" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10027,9 +10027,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E417" s="4" t="inlineStr">
-        <is>
-          <t>[0.1919191919,0.1414141414,0,0.6666666667,0,0,0,0]</t>
+      <c r="F417" s="4" t="inlineStr">
+        <is>
+          <t>[8.5967681406,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10050,9 +10050,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E418" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.3838383838,0,0.2929292929,0,0,0,0]</t>
+      <c r="F418" s="4" t="inlineStr">
+        <is>
+          <t>[23.2834152274,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10073,9 +10073,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E419" s="4" t="inlineStr">
-        <is>
-          <t>[0.3434343434,0.3838383838,0,0.0303030303,0.101010101,0.1414141414,0,0]</t>
+      <c r="F419" s="4" t="inlineStr">
+        <is>
+          <t>[22.7491462695,0,1.7959852318,5.9866174393,0]</t>
         </is>
       </c>
     </row>
@@ -10096,9 +10096,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E420" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.3939393939,0,0.0303030303,0.101010101,0.0101010101,0.1414141414,0]</t>
+      <c r="F420" s="4" t="inlineStr">
+        <is>
+          <t>[23.4075238216,0,1.8005787555,6.001929185,0.6001929185]</t>
         </is>
       </c>
     </row>
@@ -10119,9 +10119,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E421" s="4" t="inlineStr">
-        <is>
-          <t>[0.3333333333,0.404040404,0,0.0303030303,0.101010101,0.0101010101,0.1212121212,0]</t>
+      <c r="F421" s="4" t="inlineStr">
+        <is>
+          <t>[23.7335793418,0,1.7800184506,5.9333948354,0.5933394835]</t>
         </is>
       </c>
     </row>
@@ -10142,9 +10142,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E422" s="4" t="inlineStr">
-        <is>
-          <t>[0.3333333333,0.3939393939,0,0.0202020202,0.1212121212,0.0101010101,0.1212121212,0]</t>
+      <c r="F422" s="4" t="inlineStr">
+        <is>
+          <t>[23.1514208846,0,1.1872523531,7.1235141183,0.5936261765]</t>
         </is>
       </c>
     </row>
@@ -10165,9 +10165,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E423" s="4" t="inlineStr">
-        <is>
-          <t>[0.3333333333,0.3939393939,0,0.0303030303,0.0909090909,0.0202020202,0.1313131313,0]</t>
+      <c r="F423" s="4" t="inlineStr">
+        <is>
+          <t>[23.1962941872,0,1.7843303221,5.3529909663,1.1895535481]</t>
         </is>
       </c>
     </row>
@@ -10188,9 +10188,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E424" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0.101010101,0,0.0404040404,0,0,0.1515151515,0]</t>
+      <c r="F424" s="4" t="inlineStr">
+        <is>
+          <t>[5.8561951603,0,2.3424780641,0,0]</t>
         </is>
       </c>
     </row>
@@ -10211,9 +10211,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E425" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0.0909090909,0,0.0404040404,0,0.0202020202,0.1313131313,0]</t>
+      <c r="F425" s="4" t="inlineStr">
+        <is>
+          <t>[5.0820376619,0,2.2586834053,0,1.1293417026]</t>
         </is>
       </c>
     </row>
@@ -10234,9 +10234,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E426" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0404040404,0,0.0303030303,0.1515151515,0]</t>
+      <c r="F426" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.0782807419,0,1.5587105564]</t>
         </is>
       </c>
     </row>
@@ -10257,9 +10257,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E427" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0101010101,0.0505050505,0,0.0404040404,0.1515151515,0]</t>
+      <c r="F427" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4411360056,2.2056800278,0,1.7645440222]</t>
         </is>
       </c>
     </row>
@@ -10280,9 +10280,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E428" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0101010101,0.0505050505,0,0.0202020202,0.1818181818,0]</t>
+      <c r="F428" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4519342855,2.2596714274,0,0.903868571]</t>
         </is>
       </c>
     </row>
@@ -10303,9 +10303,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E429" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0.0202020202,0.0505050505,0,0.0101010101,0.202020202,0]</t>
+      <c r="F429" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9057208852,2.2643022131,0,0.4528604426]</t>
         </is>
       </c>
     </row>
@@ -10326,9 +10326,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E430" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0202020202,0.0505050505,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F430" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8676292724,2.169073181,0,0.4338146362]</t>
         </is>
       </c>
     </row>
@@ -10349,9 +10349,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E431" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.0505050505,0,0.0101010101,0.2525252525,0]</t>
+      <c r="F431" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4767924849,2.3839624243,0,0.4767924849]</t>
         </is>
       </c>
     </row>
@@ -10372,9 +10372,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E432" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0101010101,0.0505050505,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F432" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4507627404,2.2538137018,0,0.4507627404]</t>
         </is>
       </c>
     </row>
@@ -10395,9 +10395,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E433" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0,0.0404040404,0,0,0.3232323232,0]</t>
+      <c r="F433" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.1242362973,0,0]</t>
         </is>
       </c>
     </row>
@@ -10418,9 +10418,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E434" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0101010101,0.0404040404,0,0.0101010101,0.3535353535,0]</t>
+      <c r="F434" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5639124055,2.2556496222,0,0.5639124055]</t>
         </is>
       </c>
     </row>
@@ -10441,9 +10441,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E435" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0101010101,0.0404040404,0,0.0101010101,0.3535353535,0]</t>
+      <c r="F435" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5586523941,2.2346095762,0,0.5586523941]</t>
         </is>
       </c>
     </row>
@@ -10464,9 +10464,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E436" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0.0101010101,0.0404040404,0,0.3838383838,0,0]</t>
+      <c r="F436" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5954040681,2.3816162724,0,0.5954040681]</t>
         </is>
       </c>
     </row>
@@ -10487,9 +10487,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E437" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0303030303,0.0404040404,0,0.0101010101,0.3939393939,0]</t>
+      <c r="F437" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.8132646489,2.4176861985,0,0.6044215496]</t>
         </is>
       </c>
     </row>
@@ -10510,9 +10510,9 @@
           <t>CD</t>
         </is>
       </c>
-      <c r="E438" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0.0101010101,0.0303030303,0,0.4343434343,0,0]</t>
+      <c r="F438" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.6351543341,1.9054630022,0,0]</t>
         </is>
       </c>
     </row>
@@ -10533,9 +10533,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E439" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0,0,0.2727272727,0,0,0.4141414141,0]</t>
+      <c r="F439" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.094529407,0,0]</t>
         </is>
       </c>
     </row>
@@ -10556,9 +10556,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E440" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0,0,0.696969697,0,0,0,0]</t>
+      <c r="F440" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10579,9 +10579,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E441" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0.0101010101,0,0.7272727273,0,0,0,0]</t>
+      <c r="F441" s="4" t="inlineStr">
+        <is>
+          <t>[0.6320818374,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10602,9 +10602,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E442" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.2424242424,0,0.5454545455,0,0,0,0]</t>
+      <c r="F442" s="4" t="inlineStr">
+        <is>
+          <t>[15.9698222021,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -10625,9 +10625,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E443" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0,0.2222222222,0,0.2828282828,0,0]</t>
+      <c r="F443" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,13.9535801339,0,0]</t>
         </is>
       </c>
     </row>
@@ -10648,9 +10648,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E444" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.2222222222,0.0202020202,0,0.2727272727,0]</t>
+      <c r="F444" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.1684104154,1.2880373105,0]</t>
         </is>
       </c>
     </row>
@@ -10671,9 +10671,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E445" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.2626262626,0,0,0.2626262626,0]</t>
+      <c r="F445" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,16.7516337053,0,0]</t>
         </is>
       </c>
     </row>
@@ -10694,9 +10694,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E446" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0,0.2323232323,0,0,0.2626262626,0]</t>
+      <c r="F446" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.1479248256,0,0]</t>
         </is>
       </c>
     </row>
@@ -10717,9 +10717,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E447" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.2424242424,0.0303030303,0,0.2424242424,0]</t>
+      <c r="F447" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.1544032169,1.8943004021,0]</t>
         </is>
       </c>
     </row>
@@ -10740,9 +10740,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E448" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.2525252525,0,0,0.2727272727,0]</t>
+      <c r="F448" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,16.1248238244,0,0]</t>
         </is>
       </c>
     </row>
@@ -10763,9 +10763,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E449" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.2525252525,0,0,0.2626262626,0]</t>
+      <c r="F449" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.7224177514,0,0]</t>
         </is>
       </c>
     </row>
@@ -10786,9 +10786,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E450" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0404040404,0.0505050505,0,0,0.2727272727,0]</t>
+      <c r="F450" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.5124330886,3.1405413608,0,0]</t>
         </is>
       </c>
     </row>
@@ -10809,9 +10809,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E451" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0101010101,0.0606060606,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F451" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5819470569,3.4916823415,0,0.5819470569]</t>
         </is>
       </c>
     </row>
@@ -10832,9 +10832,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E452" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.0606060606,0,0.0202020202,0.2424242424,0]</t>
+      <c r="F452" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.4283151514,0,1.1427717171]</t>
         </is>
       </c>
     </row>
@@ -10855,9 +10855,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E453" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0101010101,0.0505050505,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F453" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5819785777,2.9098928884,0,0.5819785777]</t>
         </is>
       </c>
     </row>
@@ -10878,9 +10878,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E454" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.0707070707,0,0.0505050505,0.202020202,0]</t>
+      <c r="F454" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.0217116232,0,2.8726511594]</t>
         </is>
       </c>
     </row>
@@ -10901,9 +10901,9 @@
           <t>CD</t>
         </is>
       </c>
-      <c r="E455" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0909090909,0.0707070707,0,0.0303030303,0.1414141414,0]</t>
+      <c r="F455" s="4" t="inlineStr">
+        <is>
+          <t>[0,5.1456679658,4.0021861956,0,1.7152226553]</t>
         </is>
       </c>
     </row>
@@ -10924,9 +10924,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E456" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.2929292929,0,0.4444444444,0,0,0.2626262626,0]</t>
+      <c r="F456" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.590595479,0,0]</t>
         </is>
       </c>
     </row>
@@ -10947,9 +10947,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E457" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0,0.4141414141,0,0,0.3131313131,0]</t>
+      <c r="F457" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.6425172077,0,0]</t>
         </is>
       </c>
     </row>
@@ -10970,9 +10970,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E458" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0,0.3838383838,0,0,0.3434343434,0]</t>
+      <c r="F458" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,23.8301192105,0,0]</t>
         </is>
       </c>
     </row>
@@ -10993,9 +10993,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E459" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0,0.404040404,0,0,0.3232323232,0]</t>
+      <c r="F459" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,25.2128906833,0,0]</t>
         </is>
       </c>
     </row>
@@ -11016,9 +11016,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E460" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0,0,0.404040404,0,0,0.303030303,0]</t>
+      <c r="F460" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.4731358872,0,0]</t>
         </is>
       </c>
     </row>
@@ -11039,9 +11039,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E461" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0,0,0.4444444444,0,0,0.2727272727,0]</t>
+      <c r="F461" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,25.8722582476,0,0]</t>
         </is>
       </c>
     </row>
@@ -11062,9 +11062,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E462" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0,0,0.404040404,0,0,0.303030303,0]</t>
+      <c r="F462" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.1507690038,0,0]</t>
         </is>
       </c>
     </row>
@@ -11085,9 +11085,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E463" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0,0,0.3838383838,0,0,0.3535353535,0]</t>
+      <c r="F463" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,24.5576751487,0,0]</t>
         </is>
       </c>
     </row>
@@ -11108,9 +11108,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E464" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0,0.7272727273,0,0,0,0]</t>
+      <c r="F464" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11131,9 +11131,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E465" s="4" t="inlineStr">
-        <is>
-          <t>[0.1919191919,0.101010101,0,0.7070707071,0,0,0,0]</t>
+      <c r="F465" s="4" t="inlineStr">
+        <is>
+          <t>[5.9374242935,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11154,9 +11154,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E466" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.3434343434,0,0.3838383838,0,0,0,0]</t>
+      <c r="F466" s="4" t="inlineStr">
+        <is>
+          <t>[20.668328137,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11177,9 +11177,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E467" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.3434343434,0,0.0505050505,0,0.3232323232,0,0]</t>
+      <c r="F467" s="4" t="inlineStr">
+        <is>
+          <t>[20.6245008222,0,3.0330148268,0,2.4264118614]</t>
         </is>
       </c>
     </row>
@@ -11200,9 +11200,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E468" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.3535353535,0,0.0505050505,0,0.0606060606,0.2424242424,0]</t>
+      <c r="F468" s="4" t="inlineStr">
+        <is>
+          <t>[20.3303527316,0,2.9043361045,0,3.4852033254]</t>
         </is>
       </c>
     </row>
@@ -11223,9 +11223,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E469" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.3535353535,0,0.0505050505,0,0.0202020202,0.2929292929,0]</t>
+      <c r="F469" s="4" t="inlineStr">
+        <is>
+          <t>[21.1913200094,0,3.0273314299,0,1.210932572]</t>
         </is>
       </c>
     </row>
@@ -11246,9 +11246,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E470" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.3434343434,0,0.0606060606,0,0.0202020202,0.2929292929,0]</t>
+      <c r="F470" s="4" t="inlineStr">
+        <is>
+          <t>[20.6082752546,0,3.6367544567,0,1.2122514856]</t>
         </is>
       </c>
     </row>
@@ -11269,9 +11269,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E471" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0.3737373737,0,0.0505050505,0,0,0.3131313131,0]</t>
+      <c r="F471" s="4" t="inlineStr">
+        <is>
+          <t>[23.4239918004,0,3.1654042974,0,0]</t>
         </is>
       </c>
     </row>
@@ -11292,9 +11292,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E472" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.3838383838,0,0.0606060606,0,0,0.2727272727,0]</t>
+      <c r="F472" s="4" t="inlineStr">
+        <is>
+          <t>[22.9361846647,0,3.6215028418,0,0]</t>
         </is>
       </c>
     </row>
@@ -11315,9 +11315,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E473" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.3939393939,0,0.0606060606,0,0.0202020202,0.3131313131,0]</t>
+      <c r="F473" s="4" t="inlineStr">
+        <is>
+          <t>[21.0970688111,0,3.245702894,0,1.0819009647]</t>
         </is>
       </c>
     </row>
@@ -11338,9 +11338,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E474" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0.0404040404,0.0707070707,0,0.0303030303,0.2626262626,0]</t>
+      <c r="F474" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.0061432244,3.5107506427,0,1.5046074183]</t>
         </is>
       </c>
     </row>
@@ -11361,9 +11361,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E475" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0.0101010101,0.0707070707,0,0.0808080808,0.3636363636,0]</t>
+      <c r="F475" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4522209836,3.1655468849,0,3.6177678685]</t>
         </is>
       </c>
     </row>
@@ -11384,9 +11384,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E476" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.4848484848,0,0.0707070707,0,0.0202020202,0.4242424242,0]</t>
+      <c r="F476" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1903560275,0,0.9115302936]</t>
         </is>
       </c>
     </row>
@@ -11407,9 +11407,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E477" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.4949494949,0,0.0808080808,0,0,0.4242424242,0]</t>
+      <c r="F477" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.4524257501,0,0]</t>
         </is>
       </c>
     </row>
@@ -11430,9 +11430,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E478" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0,0.0606060606,0.0707070707,0,0.101010101,0.3737373737,0]</t>
+      <c r="F478" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.4425219717,2.849608967,0,4.0708699528]</t>
         </is>
       </c>
     </row>
@@ -11453,9 +11453,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E479" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0808080808,0.0808080808,0,0.0202020202,0.4141414141,0]</t>
+      <c r="F479" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.4225942264,3.4225942264,0,0.8556485566]</t>
         </is>
       </c>
     </row>
@@ -11476,9 +11476,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E480" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0,0.0707070707,0.0707070707,0,0.0606060606,0.4242424242,0]</t>
+      <c r="F480" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.0387480792,3.0387480792,0,2.6046412108]</t>
         </is>
       </c>
     </row>
@@ -11499,9 +11499,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E481" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0.0202020202,0.0707070707,0,0.1111111111,0.3434343434,0]</t>
+      <c r="F481" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7225530238,2.5289355834,0,3.974041631]</t>
         </is>
       </c>
     </row>
@@ -11522,9 +11522,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E482" s="4" t="inlineStr">
-        <is>
-          <t>[0.1515151515,0,0.2727272727,0.0808080808,0,0,0.4949494949,0]</t>
+      <c r="F482" s="4" t="inlineStr">
+        <is>
+          <t>[0,10.0742181762,2.9849535337,0,0]</t>
         </is>
       </c>
     </row>
@@ -11545,9 +11545,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E483" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0,0.2727272727,0.0808080808,0,0.0404040404,0.3939393939,0]</t>
+      <c r="F483" s="4" t="inlineStr">
+        <is>
+          <t>[0,8.7247055877,2.5850979519,0,1.292548976]</t>
         </is>
       </c>
     </row>
@@ -11568,9 +11568,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E484" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0,0.2828282828,0.0909090909,0,0,0.3939393939,0]</t>
+      <c r="F484" s="4" t="inlineStr">
+        <is>
+          <t>[0,8.6540049783,2.7816444573,0,0]</t>
         </is>
       </c>
     </row>
@@ -11591,9 +11591,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E485" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0,0.3131313131,0.0909090909,0,0.0303030303,0.3535353535,0]</t>
+      <c r="F485" s="4" t="inlineStr">
+        <is>
+          <t>[0,9.4094411015,2.731773223,0,0.9105910743]</t>
         </is>
       </c>
     </row>
@@ -11614,9 +11614,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E486" s="4" t="inlineStr">
-        <is>
-          <t>[0.202020202,0,0.3131313131,0.0808080808,0,0,0.404040404,0]</t>
+      <c r="F486" s="4" t="inlineStr">
+        <is>
+          <t>[0,9.9300861099,2.5626028671,0,0]</t>
         </is>
       </c>
     </row>
@@ -11637,9 +11637,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E487" s="4" t="inlineStr">
-        <is>
-          <t>[0.2424242424,0,0.2727272727,0.0808080808,0,0.404040404,0,0]</t>
+      <c r="F487" s="4" t="inlineStr">
+        <is>
+          <t>[0,8.8406193525,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11660,9 +11660,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E488" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.0303030303,0,0.0606060606,0,0.6868686869,0,0]</t>
+      <c r="F488" s="4" t="inlineStr">
+        <is>
+          <t>[0.8956617629,0,1.7913235257,0,0]</t>
         </is>
       </c>
     </row>
@@ -11683,9 +11683,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E489" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.1111111111,0,0.6666666667,0,0,0,0]</t>
+      <c r="F489" s="4" t="inlineStr">
+        <is>
+          <t>[3.1177400382,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11706,9 +11706,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E490" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.0505050505,0,0.0707070707,0.3838383838,0.2424242424,0,0]</t>
+      <c r="F490" s="4" t="inlineStr">
+        <is>
+          <t>[1.4855929583,0,2.0798301417,11.2905064835,0]</t>
         </is>
       </c>
     </row>
@@ -11729,9 +11729,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E491" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.0909090909,0,0.0606060606,0.2727272727,0,0.303030303,0]</t>
+      <c r="F491" s="4" t="inlineStr">
+        <is>
+          <t>[2.947443714,0,1.964962476,8.8423311419,0]</t>
         </is>
       </c>
     </row>
@@ -11752,9 +11752,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E492" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.0606060606,0,0.0606060606,0.2929292929,0,0.2727272727,0]</t>
+      <c r="F492" s="4" t="inlineStr">
+        <is>
+          <t>[2.0225783856,0,2.0225783856,9.7757955305,0]</t>
         </is>
       </c>
     </row>
@@ -11775,9 +11775,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E493" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.0404040404,0,0.0606060606,0.2828282828,0,0.303030303,0]</t>
+      <c r="F493" s="4" t="inlineStr">
+        <is>
+          <t>[1.4195024342,0,2.1292536514,9.9365170397,0]</t>
         </is>
       </c>
     </row>
@@ -11798,9 +11798,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E494" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.0909090909,0,0.0606060606,0.2727272727,0,0.2626262626,0]</t>
+      <c r="F494" s="4" t="inlineStr">
+        <is>
+          <t>[3.0805556932,0,2.0537037955,9.2416670796,0]</t>
         </is>
       </c>
     </row>
@@ -11821,9 +11821,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E495" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.101010101,0,0.0505050505,0.3131313131,0,0.2525252525,0]</t>
+      <c r="F495" s="4" t="inlineStr">
+        <is>
+          <t>[3.3682212686,0,1.6841106343,10.4414859328,0]</t>
         </is>
       </c>
     </row>
@@ -11844,9 +11844,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E496" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.3333333333,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F496" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,11.7250498358,0,0.3553045405]</t>
         </is>
       </c>
     </row>
@@ -11867,9 +11867,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E497" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.3434343434,0,0.0202020202,0.2222222222,0]</t>
+      <c r="F497" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.2210040137,0,0.7093080011]</t>
         </is>
       </c>
     </row>
@@ -11890,9 +11890,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E498" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0,0,0.303030303,0,0.0202020202,0.2424242424,0]</t>
+      <c r="F498" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.8726211095,0,0.7098096888]</t>
         </is>
       </c>
     </row>
@@ -11913,9 +11913,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E499" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8080808081,0,0,0.1919191919,0]</t>
+      <c r="F499" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -11936,9 +11936,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E500" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7474747475,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F500" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.3493735684]</t>
         </is>
       </c>
     </row>
@@ -11959,9 +11959,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E501" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.7474747475,0,0.0303030303,0.2222222222,0]</t>
+      <c r="F501" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.9900666559]</t>
         </is>
       </c>
     </row>
@@ -11982,9 +11982,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E502" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0808080808,0.0909090909,0,0,0.202020202,0]</t>
+      <c r="F502" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.6068525229,2.9327090883,0,0]</t>
         </is>
       </c>
     </row>
@@ -12005,9 +12005,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E503" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0707070707,0.0808080808,0,0.0202020202,0.2121212121,0]</t>
+      <c r="F503" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.2968417672,2.6249620197,0,0.6562405049]</t>
         </is>
       </c>
     </row>
@@ -12028,9 +12028,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E504" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0606060606,0.101010101,0,0.0202020202,0.1515151515,0]</t>
+      <c r="F504" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.8398189721,3.0663649535,0,0.6132729907]</t>
         </is>
       </c>
     </row>
@@ -12051,9 +12051,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E505" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0505050505,0.101010101,0,0.0101010101,0.1111111111,0]</t>
+      <c r="F505" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.4634779192,2.9269558384,0,0.2926955838]</t>
         </is>
       </c>
     </row>
@@ -12074,9 +12074,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E506" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0808080808,0.101010101,0,0.0303030303,0.1111111111,0]</t>
+      <c r="F506" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.3479420681,2.9349275851,0,0.8804782755]</t>
         </is>
       </c>
     </row>
@@ -12097,9 +12097,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E507" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0606060606,0.0808080808,0,0,0.2525252525,0]</t>
+      <c r="F507" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.0841029086,2.7788038781,0,0]</t>
         </is>
       </c>
     </row>
@@ -12120,9 +12120,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E508" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0.0707070707,0.0909090909,0,0.0202020202,0.1515151515,0]</t>
+      <c r="F508" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.220996818,2.8555673374,0,0.6345705194]</t>
         </is>
       </c>
     </row>
@@ -12143,9 +12143,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E509" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.1313131313,0,0,0.1919191919,0]</t>
+      <c r="F509" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.2373301143,0,0]</t>
         </is>
       </c>
     </row>
@@ -12166,9 +12166,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E510" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0,0.2424242424,0,0,0.303030303,0]</t>
+      <c r="F510" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.0059892638,0,0]</t>
         </is>
       </c>
     </row>
@@ -12189,9 +12189,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E511" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.5757575758,0,0,0,0]</t>
+      <c r="F511" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12212,9 +12212,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E512" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0.0404040404,0,0.5757575758,0,0,0,0]</t>
+      <c r="F512" s="4" t="inlineStr">
+        <is>
+          <t>[1.3121207288,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12235,9 +12235,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E513" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0.0909090909,0,0.4848484848,0,0,0,0]</t>
+      <c r="F513" s="4" t="inlineStr">
+        <is>
+          <t>[2.9924859436,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12258,9 +12258,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E514" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0606060606,0,0.0707070707,0.2727272727,0.1313131313,0,0]</t>
+      <c r="F514" s="4" t="inlineStr">
+        <is>
+          <t>[1.8543855306,0,2.1634497857,8.3447348876,0]</t>
         </is>
       </c>
     </row>
@@ -12281,9 +12281,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E515" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0.0909090909,0,0.0707070707,0.2222222222,0,0.1616161616,0]</t>
+      <c r="F515" s="4" t="inlineStr">
+        <is>
+          <t>[2.8007182144,0,2.178336389,6.8462000797,0]</t>
         </is>
       </c>
     </row>
@@ -12304,9 +12304,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E516" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0.1111111111,0,0.0707070707,0.2222222222,0,0.1616161616,0]</t>
+      <c r="F516" s="4" t="inlineStr">
+        <is>
+          <t>[3.4439194189,0,2.1915850847,6.8878388378,0]</t>
         </is>
       </c>
     </row>
@@ -12327,9 +12327,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E517" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0.0808080808,0,0.0707070707,0.2727272727,0,0.1212121212,0]</t>
+      <c r="F517" s="4" t="inlineStr">
+        <is>
+          <t>[2.4852224298,0,2.1745696261,8.3876257007,0]</t>
         </is>
       </c>
     </row>
@@ -12350,9 +12350,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E518" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0.101010101,0,0.0606060606,0.2222222222,0,0.2121212121,0]</t>
+      <c r="F518" s="4" t="inlineStr">
+        <is>
+          <t>[3.5098914915,0,2.1059348949,7.7217612814,0]</t>
         </is>
       </c>
     </row>
@@ -12373,9 +12373,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E519" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0707070707,0,0.0707070707,0.2323232323,0.0101010101,0.1515151515,0]</t>
+      <c r="F519" s="4" t="inlineStr">
+        <is>
+          <t>[2.2813976334,0,2.2813976334,7.4960207956,0.3259139476]</t>
         </is>
       </c>
     </row>
@@ -12396,9 +12396,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E520" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0.0808080808,0,0.0707070707,0.2626262626,0,0.1313131313,0]</t>
+      <c r="F520" s="4" t="inlineStr">
+        <is>
+          <t>[2.5866050361,0,2.2632794066,8.4064663672,0]</t>
         </is>
       </c>
     </row>
@@ -12419,9 +12419,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E521" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0.1313131313,0,0.0606060606,0.2525252525,0,0.1717171717,0]</t>
+      <c r="F521" s="4" t="inlineStr">
+        <is>
+          <t>[4.2473169695,0,1.9603001398,8.167917249,0]</t>
         </is>
       </c>
     </row>
@@ -12442,9 +12442,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E522" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.2929292929,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F522" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0287022603,0,0.3365224734]</t>
         </is>
       </c>
     </row>
@@ -12465,9 +12465,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E523" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8080808081,0,0.0505050505,0.1414141414,0]</t>
+      <c r="F523" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.6582678063]</t>
         </is>
       </c>
     </row>
@@ -12488,9 +12488,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E524" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.797979798,0,0.0606060606,0.1414141414,0]</t>
+      <c r="F524" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.9423397963]</t>
         </is>
       </c>
     </row>
@@ -12511,9 +12511,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E525" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0.0303030303,0.0909090909,0,0.0303030303,0.1616161616,0]</t>
+      <c r="F525" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.9934500107,2.980350032,0,0.9934500107]</t>
         </is>
       </c>
     </row>
@@ -12534,9 +12534,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E526" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0202020202,0.0808080808,0,0.0303030303,0.2121212121,0]</t>
+      <c r="F526" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7031900993,2.8127603972,0,1.054785149]</t>
         </is>
       </c>
     </row>
@@ -12557,9 +12557,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E527" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0404040404,0.0909090909,0,0.0606060606,0.1313131313,0]</t>
+      <c r="F527" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.3617979197,3.0640453193,0,2.0426968795]</t>
         </is>
       </c>
     </row>
@@ -12580,9 +12580,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E528" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.1212121212,0,0.0202020202,0.2424242424,0]</t>
+      <c r="F528" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.4384535385,0,0.7397422564]</t>
         </is>
       </c>
     </row>
@@ -12603,9 +12603,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E529" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0,0.0808080808,0,0,0.3333333333,0]</t>
+      <c r="F529" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.2273945719,0,0]</t>
         </is>
       </c>
     </row>
@@ -12626,9 +12626,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E530" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0,0.101010101,0,0,0.303030303,0]</t>
+      <c r="F530" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.9077454783,0,0]</t>
         </is>
       </c>
     </row>
@@ -12649,9 +12649,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E531" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0909090909,0,0,0.3434343434,0]</t>
+      <c r="F531" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.6492824168,0,0]</t>
         </is>
       </c>
     </row>
@@ -12672,9 +12672,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E532" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.0707070707,0,0,0.4141414141,0]</t>
+      <c r="F532" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.1190540039,0,0]</t>
         </is>
       </c>
     </row>
@@ -12695,9 +12695,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E533" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0,0.4444444444,0,0,0,0]</t>
+      <c r="F533" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12718,9 +12718,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E534" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.4848484848,0,0,0,0]</t>
+      <c r="F534" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12741,9 +12741,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E535" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.4848484848,0,0,0,0]</t>
+      <c r="F535" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12764,9 +12764,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E536" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.0303030303,0,0.7474747475,0,0,0,0]</t>
+      <c r="F536" s="4" t="inlineStr">
+        <is>
+          <t>[1.2969343652,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12787,9 +12787,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E537" s="4" t="inlineStr">
-        <is>
-          <t>[0.1212121212,0.3333333333,0,0.5454545455,0,0,0,0]</t>
+      <c r="F537" s="4" t="inlineStr">
+        <is>
+          <t>[14.040534541,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -12810,9 +12810,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E538" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0,0.3434343434,0,0.2121212121,0,0]</t>
+      <c r="F538" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.5568453793,0,0]</t>
         </is>
       </c>
     </row>
@@ -12833,9 +12833,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E539" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.3131313131,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F539" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.7397603025,0,0.4754761388]</t>
         </is>
       </c>
     </row>
@@ -12856,9 +12856,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E540" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.303030303,0,0.0101010101,0.2121212121,0]</t>
+      <c r="F540" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.1080651266,0,0.5036021709]</t>
         </is>
       </c>
     </row>
@@ -12879,9 +12879,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E541" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.303030303,0,0.0101010101,0.1616161616,0]</t>
+      <c r="F541" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.9712298561,0,0.5323743285]</t>
         </is>
       </c>
     </row>
@@ -12902,9 +12902,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E542" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.2727272727,0,0,0.1515151515,0]</t>
+      <c r="F542" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.4103680357,0,0]</t>
         </is>
       </c>
     </row>
@@ -12925,9 +12925,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E543" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0,0.2525252525,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F543" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.8850945104,0,0.5954037804]</t>
         </is>
       </c>
     </row>
@@ -12948,9 +12948,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E544" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0,0.2626262626,0.0202020202,0,0.1111111111,0]</t>
+      <c r="F544" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,15.556399464,1.1966461126,0]</t>
         </is>
       </c>
     </row>
@@ -12971,9 +12971,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E545" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0,0.2323232323,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F545" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,14.6127311235,0,0.6353361358]</t>
         </is>
       </c>
     </row>
@@ -12994,9 +12994,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E546" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.2626262626,0,0,0.1616161616,0]</t>
+      <c r="F546" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.9695174445,0,0]</t>
         </is>
       </c>
     </row>
@@ -13017,9 +13017,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E547" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8686868687,0,0.0101010101,0.1212121212,0]</t>
+      <c r="F547" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.5934493646]</t>
         </is>
       </c>
     </row>
@@ -13040,9 +13040,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E548" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8383838384,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F548" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.6088444445]</t>
         </is>
       </c>
     </row>
@@ -13063,9 +13063,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E549" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8686868687,0,0,0.1313131313,0]</t>
+      <c r="F549" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13086,9 +13086,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E550" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.0606060606,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F550" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.7486885789,0,0.6247814298]</t>
         </is>
       </c>
     </row>
@@ -13109,9 +13109,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E551" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0707070707,0.0606060606,0,0.0101010101,0.1313131313,0]</t>
+      <c r="F551" s="4" t="inlineStr">
+        <is>
+          <t>[0,4.1826905204,3.5851633032,0,0.5975272172]</t>
         </is>
       </c>
     </row>
@@ -13132,9 +13132,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E552" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0,0.1616161616,0,0,0.1414141414,0]</t>
+      <c r="F552" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.5532032802,0,0]</t>
         </is>
       </c>
     </row>
@@ -13155,9 +13155,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E553" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0,0.1313131313,0,0,0.202020202,0]</t>
+      <c r="F553" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.2688607663,0,0]</t>
         </is>
       </c>
     </row>
@@ -13178,9 +13178,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E554" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.1616161616,0,0,0.1515151515,0]</t>
+      <c r="F554" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.8177898442,0,0]</t>
         </is>
       </c>
     </row>
@@ -13201,9 +13201,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E555" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0,0.1717171717,0,0,0.1515151515,0]</t>
+      <c r="F555" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.3109463215,0,0]</t>
         </is>
       </c>
     </row>
@@ -13224,9 +13224,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E556" s="4" t="inlineStr">
-        <is>
-          <t>[0.7676767677,0,0,0.1616161616,0,0,0.0707070707,0]</t>
+      <c r="F556" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.6744398681,0,0]</t>
         </is>
       </c>
     </row>
@@ -13247,9 +13247,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E557" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.202020202,0,0,0.0202020202,0]</t>
+      <c r="F557" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.7418829054,0,0]</t>
         </is>
       </c>
     </row>
@@ -13270,9 +13270,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E558" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0,0.202020202,0,0,0.0202020202,0]</t>
+      <c r="F558" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,7.0241156535,0,0]</t>
         </is>
       </c>
     </row>
@@ -13293,9 +13293,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E559" s="4" t="inlineStr">
-        <is>
-          <t>[0.797979798,0,0,0.202020202,0,0,0,0]</t>
+      <c r="F559" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13316,9 +13316,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E560" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0,0.6161616162,0,0,0,0]</t>
+      <c r="F560" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13339,9 +13339,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E561" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.0303030303,0,0.7171717172,0,0,0,0]</t>
+      <c r="F561" s="4" t="inlineStr">
+        <is>
+          <t>[1.5623890348,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13362,9 +13362,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E562" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.4646464646,0,0.2424242424,0,0,0,0]</t>
+      <c r="F562" s="4" t="inlineStr">
+        <is>
+          <t>[24.3062258259,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13385,9 +13385,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E563" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.4848484848,0,0.0505050505,0,0.1919191919,0,0]</t>
+      <c r="F563" s="4" t="inlineStr">
+        <is>
+          <t>[24.9510057738,0,2.5990631014,0,1.0396252406]</t>
         </is>
       </c>
     </row>
@@ -13408,9 +13408,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E564" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0.4949494949,0,0.0606060606,0,0,0.1717171717,0]</t>
+      <c r="F564" s="4" t="inlineStr">
+        <is>
+          <t>[25.2570542019,0,3.0927005145,0,0]</t>
         </is>
       </c>
     </row>
@@ -13431,9 +13431,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E565" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.4848484848,0,0.0505050505,0,0.0303030303,0.1515151515,0]</t>
+      <c r="F565" s="4" t="inlineStr">
+        <is>
+          <t>[24.3708108637,0,2.5386261316,0,1.523175679]</t>
         </is>
       </c>
     </row>
@@ -13454,9 +13454,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E566" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.4545454545,0,0.0505050505,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F566" s="4" t="inlineStr">
+        <is>
+          <t>[25.0447764297,0,2.7827529366,0,0.5565505873]</t>
         </is>
       </c>
     </row>
@@ -13477,9 +13477,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E567" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.4444444444,0,0.0505050505,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F567" s="4" t="inlineStr">
+        <is>
+          <t>[23.7941177542,0,2.7038770175,0,0.5407754035]</t>
         </is>
       </c>
     </row>
@@ -13500,9 +13500,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E568" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.4343434343,0,0.0505050505,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F568" s="4" t="inlineStr">
+        <is>
+          <t>[24.2935977399,0,2.8248369465,0,0.5649673893]</t>
         </is>
       </c>
     </row>
@@ -13523,9 +13523,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E569" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.4444444444,0,0.0505050505,0,0.0202020202,0.1717171717,0]</t>
+      <c r="F569" s="4" t="inlineStr">
+        <is>
+          <t>[24.0998230679,0,2.7386162577,0,1.0954465031]</t>
         </is>
       </c>
     </row>
@@ -13546,9 +13546,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E570" s="4" t="inlineStr">
-        <is>
-          <t>[0.3232323232,0.4343434343,0,0.0404040404,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F570" s="4" t="inlineStr">
+        <is>
+          <t>[23.8128914127,0,2.2151526896,0,0.5537881724]</t>
         </is>
       </c>
     </row>
@@ -13569,9 +13569,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E571" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7575757576,0,0.0505050505,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F571" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.807957303,0,0.5615914606]</t>
         </is>
       </c>
     </row>
@@ -13592,9 +13592,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E572" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.797979798,0,0.0101010101,0.1919191919,0]</t>
+      <c r="F572" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.5603124427]</t>
         </is>
       </c>
     </row>
@@ -13615,9 +13615,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E573" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0303030303,0.0404040404,0,0.0101010101,0.1616161616,0]</t>
+      <c r="F573" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.657529059,2.2100387453,0,0.5525096863]</t>
         </is>
       </c>
     </row>
@@ -13638,9 +13638,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E574" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0202020202,0.0505050505,0,0,0.1818181818,0]</t>
+      <c r="F574" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0776200861,2.6940502152,0,0]</t>
         </is>
       </c>
     </row>
@@ -13661,9 +13661,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E575" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0101010101,0.0505050505,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F575" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5463473051,2.7317365256,0,0.5463473051]</t>
         </is>
       </c>
     </row>
@@ -13684,9 +13684,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E576" s="4" t="inlineStr">
-        <is>
-          <t>[0.7575757576,0,0.0101010101,0.0505050505,0,0,0.1818181818,0]</t>
+      <c r="F576" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5476320161,2.7381600807,0,0]</t>
         </is>
       </c>
     </row>
@@ -13707,9 +13707,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E577" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0303030303,0.0505050505,0,0,0.1818181818,0]</t>
+      <c r="F577" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.630037066,2.7167284433,0,0]</t>
         </is>
       </c>
     </row>
@@ -13730,9 +13730,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E578" s="4" t="inlineStr">
-        <is>
-          <t>[0.8383838384,0,0.0101010101,0.0505050505,0,0.0404040404,0.0606060606,0]</t>
+      <c r="F578" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.496959615,2.4847980749,0,1.9878384599]</t>
         </is>
       </c>
     </row>
@@ -13753,9 +13753,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E579" s="4" t="inlineStr">
-        <is>
-          <t>[0.8383838384,0,0.0101010101,0.0505050505,0,0.0505050505,0.0505050505,0]</t>
+      <c r="F579" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4991271637,2.4956358186,0,2.4956358186]</t>
         </is>
       </c>
     </row>
@@ -13776,9 +13776,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E580" s="4" t="inlineStr">
-        <is>
-          <t>[0.7777777778,0,0.0707070707,0.0505050505,0,0.0606060606,0.0404040404,0]</t>
+      <c r="F580" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.5023073989,2.5016481421,0,3.0019777705]</t>
         </is>
       </c>
     </row>
@@ -13799,9 +13799,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E581" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0,0.5252525253,0.0505050505,0,0.1313131313,0.0101010101,0]</t>
+      <c r="F581" s="4" t="inlineStr">
+        <is>
+          <t>[0,24.9986561725,2.4037169397,0,6.2496640431]</t>
         </is>
       </c>
     </row>
@@ -13822,9 +13822,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E582" s="4" t="inlineStr">
-        <is>
-          <t>[0.2727272727,0,0,0.5757575758,0,0,0.1515151515,0]</t>
+      <c r="F582" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,28.3994537644,0,0]</t>
         </is>
       </c>
     </row>
@@ -13845,9 +13845,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E583" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0,0,0.595959596,0,0,0.1111111111,0]</t>
+      <c r="F583" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,26.1097225925,0,0]</t>
         </is>
       </c>
     </row>
@@ -13868,9 +13868,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E584" s="4" t="inlineStr">
-        <is>
-          <t>[0.1717171717,0.1414141414,0,0,0,0,0.6868686869,0]</t>
+      <c r="F584" s="4" t="inlineStr">
+        <is>
+          <t>[6.1878010542,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13891,9 +13891,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E585" s="4" t="inlineStr">
-        <is>
-          <t>[0.1616161616,0.1313131313,0,0.7070707071,0,0,0,0]</t>
+      <c r="F585" s="4" t="inlineStr">
+        <is>
+          <t>[5.964056626,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13914,9 +13914,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E586" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.4646464646,0,0.2424242424,0,0,0,0]</t>
+      <c r="F586" s="4" t="inlineStr">
+        <is>
+          <t>[20.0597066013,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -13937,9 +13937,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E587" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.4545454545,0,0.0404040404,0,0.1919191919,0,0]</t>
+      <c r="F587" s="4" t="inlineStr">
+        <is>
+          <t>[19.7842538532,0,1.7586003425,0,1.3189502569]</t>
         </is>
       </c>
     </row>
@@ -13960,9 +13960,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E588" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0.4545454545,0,0.0404040404,0,0.0202020202,0.1919191919,0]</t>
+      <c r="F588" s="4" t="inlineStr">
+        <is>
+          <t>[20.1838803812,0,1.7941227005,0,0.8970613503]</t>
         </is>
       </c>
     </row>
@@ -13983,9 +13983,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E589" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0.4545454545,0,0.0303030303,0,0.0606060606,0.1515151515,0]</t>
+      <c r="F589" s="4" t="inlineStr">
+        <is>
+          <t>[19.8675564225,0,1.3245037615,0,2.649007523]</t>
         </is>
       </c>
     </row>
@@ -14006,9 +14006,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E590" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0.4646464646,0,0.0404040404,0,0.0404040404,0.1515151515,0]</t>
+      <c r="F590" s="4" t="inlineStr">
+        <is>
+          <t>[19.6311537812,0,1.7070568505,0,1.7070568505]</t>
         </is>
       </c>
     </row>
@@ -14029,9 +14029,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E591" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0.4545454545,0,0.0303030303,0,0.0505050505,0.1616161616,0]</t>
+      <c r="F591" s="4" t="inlineStr">
+        <is>
+          <t>[19.8623207083,0,1.3241547139,0,2.2069245231]</t>
         </is>
       </c>
     </row>
@@ -14052,9 +14052,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E592" s="4" t="inlineStr">
-        <is>
-          <t>[0.3131313131,0.4545454545,0,0.0404040404,0,0.0303030303,0.1616161616,0]</t>
+      <c r="F592" s="4" t="inlineStr">
+        <is>
+          <t>[19.9205568435,0,1.7707161639,0,1.3280371229]</t>
         </is>
       </c>
     </row>
@@ -14075,9 +14075,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E593" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.4848484848,0,0.0404040404,0,0.0505050505,0.1414141414,0]</t>
+      <c r="F593" s="4" t="inlineStr">
+        <is>
+          <t>[19.6543468143,0,1.6378622345,0,2.0473277932]</t>
         </is>
       </c>
     </row>
@@ -14098,9 +14098,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E594" s="4" t="inlineStr">
-        <is>
-          <t>[0.2323232323,0.4949494949,0,0.0404040404,0,0.0505050505,0.1818181818,0]</t>
+      <c r="F594" s="4" t="inlineStr">
+        <is>
+          <t>[19.8898318612,0,1.6236597438,0,2.0295746797]</t>
         </is>
       </c>
     </row>
@@ -14121,9 +14121,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E595" s="4" t="inlineStr">
-        <is>
-          <t>[0.7474747475,0,0.0404040404,0.0505050505,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F595" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.6437945509,2.0547431886,0,0.4109486377]</t>
         </is>
       </c>
     </row>
@@ -14144,9 +14144,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E596" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.7070707071,0,0.0404040404,0,0.101010101,0.1515151515,0]</t>
+      <c r="F596" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.5966434919,0,3.9916087297]</t>
         </is>
       </c>
     </row>
@@ -14167,9 +14167,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E597" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.6767676768,0,0.0404040404,0,0.0404040404,0.2424242424,0]</t>
+      <c r="F597" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.6064148595,0,1.6064148595]</t>
         </is>
       </c>
     </row>
@@ -14190,9 +14190,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E598" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0,0.0404040404,0,0.0404040404,0.2828282828,0]</t>
+      <c r="F598" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.7175447507,0,1.7175447507]</t>
         </is>
       </c>
     </row>
@@ -14213,9 +14213,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E599" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0303030303,0,0.0303030303,0.3737373737,0]</t>
+      <c r="F599" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.4333000717,0,1.4333000717]</t>
         </is>
       </c>
     </row>
@@ -14236,9 +14236,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E600" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0303030303,0,0.0303030303,0.3737373737,0]</t>
+      <c r="F600" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.4816139302,0,1.4816139302]</t>
         </is>
       </c>
     </row>
@@ -14259,9 +14259,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E601" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0303030303,0,0.0303030303,0.3737373737,0]</t>
+      <c r="F601" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.4436532501,0,1.4436532501]</t>
         </is>
       </c>
     </row>
@@ -14282,9 +14282,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E602" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0,0.0303030303,0,0.0404040404,0.3434343434,0]</t>
+      <c r="F602" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.3865847518,0,1.8487796691]</t>
         </is>
       </c>
     </row>
@@ -14305,9 +14305,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E603" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0,0.0404040404,0,0.0303030303,0.3636363636,0]</t>
+      <c r="F603" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.8953983547,0,1.421548766]</t>
         </is>
       </c>
     </row>
@@ -14328,9 +14328,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E604" s="4" t="inlineStr">
-        <is>
-          <t>[0.5757575758,0,0,0.0303030303,0,0.0404040404,0.3535353535,0]</t>
+      <c r="F604" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,1.4439705922,0,1.925294123]</t>
         </is>
       </c>
     </row>
@@ -14351,9 +14351,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E605" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.0404040404,0,0.3434343434,0,0]</t>
+      <c r="F605" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14374,9 +14374,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E606" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0,0.0505050505,0,0,0.404040404,0]</t>
+      <c r="F606" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0.9547684222,0,0]</t>
         </is>
       </c>
     </row>
@@ -14397,9 +14397,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E607" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.4747474747,0,0,0,0]</t>
+      <c r="F607" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14420,9 +14420,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E608" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0,0,0.7878787879,0,0,0,0]</t>
+      <c r="F608" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14443,9 +14443,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E609" s="4" t="inlineStr">
-        <is>
-          <t>[0.202020202,0.2222222222,0,0.5757575758,0,0,0,0]</t>
+      <c r="F609" s="4" t="inlineStr">
+        <is>
+          <t>[10.5722094959,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14466,9 +14466,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E610" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.3434343434,0,0.2424242424,0,0]</t>
+      <c r="F610" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,16.8947236981,0,0]</t>
         </is>
       </c>
     </row>
@@ -14489,9 +14489,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E611" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.404040404,0.1111111111,0,0.0606060606,0]</t>
+      <c r="F611" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,19.136095853,5.2624263596,0]</t>
         </is>
       </c>
     </row>
@@ -14512,9 +14512,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E612" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.404040404,0.0808080808,0,0.0909090909,0]</t>
+      <c r="F612" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,19.0397861367,3.8079572273,0]</t>
         </is>
       </c>
     </row>
@@ -14535,9 +14535,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E613" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0,0,0.3434343434,0.1414141414,0,0.0808080808,0]</t>
+      <c r="F613" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,16.2964942788,6.7103211736,0]</t>
         </is>
       </c>
     </row>
@@ -14558,9 +14558,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E614" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.3838383838,0.1212121212,0,0.0707070707,0]</t>
+      <c r="F614" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,17.5574857846,5.5444691951,0]</t>
         </is>
       </c>
     </row>
@@ -14581,9 +14581,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E615" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.3535353535,0.1414141414,0,0.0909090909,0]</t>
+      <c r="F615" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,16.9027981674,6.761119267,0]</t>
         </is>
       </c>
     </row>
@@ -14604,9 +14604,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E616" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0,0.3939393939,0.1212121212,0,0.101010101,0]</t>
+      <c r="F616" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,17.6785488692,5.4395534982,0]</t>
         </is>
       </c>
     </row>
@@ -14627,9 +14627,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E617" s="4" t="inlineStr">
-        <is>
-          <t>[0.2929292929,0,0,0.4444444444,0.1818181818,0,0.0808080808,0]</t>
+      <c r="F617" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,17.2578827325,7.060042936,0]</t>
         </is>
       </c>
     </row>
@@ -14650,9 +14650,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E618" s="4" t="inlineStr">
-        <is>
-          <t>[0.303030303,0,0,0.4444444444,0.1515151515,0,0.101010101,0]</t>
+      <c r="F618" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,12.5135743232,5.865737964,0]</t>
         </is>
       </c>
     </row>
@@ -14673,9 +14673,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E619" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6363636364,0.202020202,0,0.1616161616,0]</t>
+      <c r="F619" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14696,9 +14696,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E620" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.9191919192,0,0.0101010101,0.0707070707,0]</t>
+      <c r="F620" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.2925540148]</t>
         </is>
       </c>
     </row>
@@ -14719,9 +14719,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E621" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8686868687,0,0.0505050505,0.0808080808,0]</t>
+      <c r="F621" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.425950037]</t>
         </is>
       </c>
     </row>
@@ -14742,9 +14742,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E622" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0.0808080808,0.0707070707,0,0.0101010101,0.3939393939,0]</t>
+      <c r="F622" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.5065111709,3.0681972745,0,0.4383138964]</t>
         </is>
       </c>
     </row>
@@ -14765,9 +14765,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E623" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0404040404,0.0606060606,0,0,0.4747474747,0]</t>
+      <c r="F623" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.9417462335,2.9126193503,0,0]</t>
         </is>
       </c>
     </row>
@@ -14788,9 +14788,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E624" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0.0101010101,0.0606060606,0,0.0505050505,0.4949494949,0]</t>
+      <c r="F624" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5098942454,3.0593654724,0,2.549471227]</t>
         </is>
       </c>
     </row>
@@ -14811,9 +14811,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E625" s="4" t="inlineStr">
-        <is>
-          <t>[0.3737373737,0,0.0101010101,0.0505050505,0,0.0707070707,0.4949494949,0]</t>
+      <c r="F625" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5210530178,2.6052650889,0,3.6473711244]</t>
         </is>
       </c>
     </row>
@@ -14834,9 +14834,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E626" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0,0.0101010101,0.0505050505,0,0.0606060606,0.5151515152,0]</t>
+      <c r="F626" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.5268242884,2.634121442,0,3.1609457304]</t>
         </is>
       </c>
     </row>
@@ -14857,9 +14857,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E627" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0,0,0.0505050505,0,0.0808080808,0.5151515152,0]</t>
+      <c r="F627" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,2.7284043002,0,4.3654468804]</t>
         </is>
       </c>
     </row>
@@ -14880,9 +14880,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E628" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0,0.0606060606,0,0,0.5555555556,0]</t>
+      <c r="F628" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0968951739,0,0]</t>
         </is>
       </c>
     </row>
@@ -14903,9 +14903,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E629" s="4" t="inlineStr">
-        <is>
-          <t>[0.3838383838,0,0,0.0707070707,0,0,0.5454545455,0]</t>
+      <c r="F629" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5937334041,0,0]</t>
         </is>
       </c>
     </row>
@@ -14926,9 +14926,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E630" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0,0.0606060606,0,0,0.5353535354,0]</t>
+      <c r="F630" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0.5037099101,0,0]</t>
         </is>
       </c>
     </row>
@@ -14949,9 +14949,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E631" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.5858585859,0,0,0,0]</t>
+      <c r="F631" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14972,9 +14972,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E632" s="4" t="inlineStr">
-        <is>
-          <t>[0.1313131313,0.0707070707,0,0.797979798,0,0,0,0]</t>
+      <c r="F632" s="4" t="inlineStr">
+        <is>
+          <t>[3.7308798891,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -14995,9 +14995,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E633" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.101010101,0,0.6767676768,0,0,0,0]</t>
+      <c r="F633" s="4" t="inlineStr">
+        <is>
+          <t>[5.0303349438,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -15018,9 +15018,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E634" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.1212121212,0,0.0505050505,0.1818181818,0.4242424242,0,0]</t>
+      <c r="F634" s="4" t="inlineStr">
+        <is>
+          <t>[5.9544249109,0,2.4810103795,8.9316373663,0]</t>
         </is>
       </c>
     </row>
@@ -15041,9 +15041,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E635" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.1212121212,0,0.0505050505,0.1818181818,0,0.4343434343,0]</t>
+      <c r="F635" s="4" t="inlineStr">
+        <is>
+          <t>[6.3116213573,0,2.6298422322,9.467432036,0]</t>
         </is>
       </c>
     </row>
@@ -15064,9 +15064,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E636" s="4" t="inlineStr">
-        <is>
-          <t>[0.202020202,0.1111111111,0,0.0505050505,0.202020202,0,0.4343434343,0]</t>
+      <c r="F636" s="4" t="inlineStr">
+        <is>
+          <t>[5.6622349779,0,2.5737431718,10.294972687,0]</t>
         </is>
       </c>
     </row>
@@ -15087,9 +15087,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E637" s="4" t="inlineStr">
-        <is>
-          <t>[0.1919191919,0.1313131313,0,0.0505050505,0.1515151515,0,0.4747474747,0]</t>
+      <c r="F637" s="4" t="inlineStr">
+        <is>
+          <t>[6.8168423807,0,2.6218624541,7.8655873623,0]</t>
         </is>
       </c>
     </row>
@@ -15110,9 +15110,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E638" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.101010101,0,0.0404040404,0.1919191919,0,0.4444444444,0]</t>
+      <c r="F638" s="4" t="inlineStr">
+        <is>
+          <t>[5.1177917983,0,2.0471167193,9.7238044167,0]</t>
         </is>
       </c>
     </row>
@@ -15133,9 +15133,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E639" s="4" t="inlineStr">
-        <is>
-          <t>[0.2222222222,0.1111111111,0,0.0505050505,0.1818181818,0,0.4343434343,0]</t>
+      <c r="F639" s="4" t="inlineStr">
+        <is>
+          <t>[5.4598912872,0,2.4817687669,8.9343675609,0]</t>
         </is>
       </c>
     </row>
@@ -15156,9 +15156,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E640" s="4" t="inlineStr">
-        <is>
-          <t>[0.202020202,0.101010101,0,0.0404040404,0.2323232323,0,0.4242424242,0]</t>
+      <c r="F640" s="4" t="inlineStr">
+        <is>
+          <t>[5.206061559,0,2.0824246236,11.9739415857,0]</t>
         </is>
       </c>
     </row>
@@ -15179,9 +15179,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E641" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.1919191919,0,0.0707070707,0.1212121212,0,0.404040404,0]</t>
+      <c r="F641" s="4" t="inlineStr">
+        <is>
+          <t>[8.4065268475,0,3.0971414701,5.3093853773,0]</t>
         </is>
       </c>
     </row>
@@ -15202,9 +15202,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E642" s="4" t="inlineStr">
-        <is>
-          <t>[0.1717171717,0.1919191919,0,0.0808080808,0.1212121212,0,0.4343434343,0]</t>
+      <c r="F642" s="4" t="inlineStr">
+        <is>
+          <t>[8.1064483294,0,3.4132414019,5.1198621028,0]</t>
         </is>
       </c>
     </row>
@@ -15225,9 +15225,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E643" s="4" t="inlineStr">
-        <is>
-          <t>[0,0.3838383838,0,0.0909090909,0.1414141414,0,0.3838383838,0]</t>
+      <c r="F643" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -15248,9 +15248,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E644" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.595959596,0,0.0101010101,0.3939393939,0]</t>
+      <c r="F644" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.4137874516]</t>
         </is>
       </c>
     </row>
@@ -15271,9 +15271,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E645" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.595959596,0,0.0101010101,0.3939393939,0]</t>
+      <c r="F645" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.4104601625]</t>
         </is>
       </c>
     </row>
@@ -15294,9 +15294,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E646" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0.0202020202,0.0909090909,0,0.0202020202,0.3939393939,0]</t>
+      <c r="F646" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.8445786861,3.8006040872,0,0.8445786861]</t>
         </is>
       </c>
     </row>
@@ -15317,9 +15317,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E647" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0.0404040404,0.101010101,0,0,0.404040404,0]</t>
+      <c r="F647" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.5617665542,3.9044163856,0,0]</t>
         </is>
       </c>
     </row>
@@ -15340,9 +15340,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E648" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0.0101010101,0.101010101,0,0,0.404040404,0]</t>
+      <c r="F648" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4145801826,4.1458018265,0,0]</t>
         </is>
       </c>
     </row>
@@ -15363,9 +15363,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E649" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0.0606060606,0.0909090909,0,0.0202020202,0.3838383838,0]</t>
+      <c r="F649" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.4260516771,3.6390775157,0,0.8086838924]</t>
         </is>
       </c>
     </row>
@@ -15386,9 +15386,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E650" s="4" t="inlineStr">
-        <is>
-          <t>[0.3535353535,0,0.1818181818,0.1111111111,0,0.0404040404,0.3131313131,0]</t>
+      <c r="F650" s="4" t="inlineStr">
+        <is>
+          <t>[0,6.4756608676,3.957348308,0,1.4390357484]</t>
         </is>
       </c>
     </row>
@@ -15409,9 +15409,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E651" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0.0808080808,0.101010101,0,0.0808080808,0.2525252525,0]</t>
+      <c r="F651" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.6600918147,3.3251147684,0,2.6600918147]</t>
         </is>
       </c>
     </row>
@@ -15432,9 +15432,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E652" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.1414141414,0.1111111111,0,0.0505050505,0.2727272727,0]</t>
+      <c r="F652" s="4" t="inlineStr">
+        <is>
+          <t>[0,4.6920348225,3.6865987891,0,1.6757267223]</t>
         </is>
       </c>
     </row>
@@ -15455,9 +15455,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E653" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.1818181818,0,0,0.3434343434,0]</t>
+      <c r="F653" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.787224165,0,0]</t>
         </is>
       </c>
     </row>
@@ -15478,9 +15478,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E654" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.202020202,0,0,0.3232323232,0]</t>
+      <c r="F654" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.5425529792,0,0]</t>
         </is>
       </c>
     </row>
@@ -15501,9 +15501,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E655" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0,0.5555555556,0,0,0,0]</t>
+      <c r="F655" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -15524,9 +15524,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E656" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0.0202020202,0,0.7171717172,0,0,0,0]</t>
+      <c r="F656" s="4" t="inlineStr">
+        <is>
+          <t>[0.6083573177,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -15547,9 +15547,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E657" s="4" t="inlineStr">
-        <is>
-          <t>[0.2626262626,0.0606060606,0,0.6767676768,0,0,0,0]</t>
+      <c r="F657" s="4" t="inlineStr">
+        <is>
+          <t>[2.04821251,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -15570,9 +15570,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E658" s="4" t="inlineStr">
-        <is>
-          <t>[0.2828282828,0.1313131313,0,0.101010101,0.1212121212,0.3636363636,0,0]</t>
+      <c r="F658" s="4" t="inlineStr">
+        <is>
+          <t>[4.0068952274,0,3.082227098,3.6986725176,0]</t>
         </is>
       </c>
     </row>
@@ -15593,9 +15593,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E659" s="4" t="inlineStr">
-        <is>
-          <t>[0.2525252525,0.1919191919,0,0.1111111111,0.0707070707,0.0202020202,0.3535353535,0]</t>
+      <c r="F659" s="4" t="inlineStr">
+        <is>
+          <t>[5.8012208628,0,3.3586015522,2.1372918968,0.6106548277]</t>
         </is>
       </c>
     </row>
@@ -15616,9 +15616,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E660" s="4" t="inlineStr">
-        <is>
-          <t>[0.2424242424,0.1717171717,0,0.101010101,0.0707070707,0.0101010101,0.404040404,0]</t>
+      <c r="F660" s="4" t="inlineStr">
+        <is>
+          <t>[5.5926369104,0,3.2897864179,2.3028504925,0.3289786418]</t>
         </is>
       </c>
     </row>
@@ -15639,9 +15639,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E661" s="4" t="inlineStr">
-        <is>
-          <t>[0.2121212121,0.1717171717,0,0.0909090909,0.0707070707,0.0202020202,0.4343434343,0]</t>
+      <c r="F661" s="4" t="inlineStr">
+        <is>
+          <t>[5.8744489153,0,3.1100023669,2.4188907298,0.6911116371]</t>
         </is>
       </c>
     </row>
@@ -15662,9 +15662,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E662" s="4" t="inlineStr">
-        <is>
-          <t>[0.1111111111,0.2727272727,0,0.0909090909,0.0808080808,0.0101010101,0.4343434343,0]</t>
+      <c r="F662" s="4" t="inlineStr">
+        <is>
+          <t>[9.2935604385,0,3.0978534795,2.7536475373,0.3442059422]</t>
         </is>
       </c>
     </row>
@@ -15685,9 +15685,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E663" s="4" t="inlineStr">
-        <is>
-          <t>[0.4141414141,0,0,0.2323232323,0,0,0.3535353535,0]</t>
+      <c r="F663" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,7.0991897221,0,0]</t>
         </is>
       </c>
     </row>
@@ -15708,9 +15708,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E664" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0,0.2222222222,0,0.0202020202,0.3535353535,0]</t>
+      <c r="F664" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.660121402,0,0.605465582]</t>
         </is>
       </c>
     </row>
@@ -15731,9 +15731,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E665" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0.0101010101,0.0909090909,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F665" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3854102726,3.4686924531,0,0.3854102726]</t>
         </is>
       </c>
     </row>
@@ -15754,9 +15754,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E666" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0,0.0909090909,0,0.0202020202,0.2626262626,0]</t>
+      <c r="F666" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5179763256,0,0.7817725168]</t>
         </is>
       </c>
     </row>
@@ -15777,9 +15777,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E667" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0202020202,0.0909090909,0,0.0101010101,0.2424242424,0]</t>
+      <c r="F667" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7834226429,3.5254018929,0,0.3917113214]</t>
         </is>
       </c>
     </row>
@@ -15800,9 +15800,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E668" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6565656566,0,0.0303030303,0.3131313131,0]</t>
+      <c r="F668" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,1.2447245026]</t>
         </is>
       </c>
     </row>
@@ -15823,9 +15823,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E669" s="4" t="inlineStr">
-        <is>
-          <t>[0.5656565657,0,0.0101010101,0.0808080808,0,0.0404040404,0.303030303,0]</t>
+      <c r="F669" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.4052750648,3.2422005188,0,1.6211002594]</t>
         </is>
       </c>
     </row>
@@ -15846,9 +15846,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E670" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0303030303,0.101010101,0,0.0505050505,0.202020202,0]</t>
+      <c r="F670" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.0194788033,3.3982626776,0,1.6991313388]</t>
         </is>
       </c>
     </row>
@@ -15869,9 +15869,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E671" s="4" t="inlineStr">
-        <is>
-          <t>[0.6464646465,0,0.0404040404,0.101010101,0,0.0202020202,0.1919191919,0]</t>
+      <c r="F671" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2729242698,3.1823106745,0,0.6364621349]</t>
         </is>
       </c>
     </row>
@@ -15892,9 +15892,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E672" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0.0202020202,0.0808080808,0,0.0404040404,0.2626262626,0]</t>
+      <c r="F672" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.6904949181,2.7619796725,0,1.3809898363]</t>
         </is>
       </c>
     </row>
@@ -15915,9 +15915,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E673" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0,0.0909090909,0,0,0.3232323232,0]</t>
+      <c r="F673" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.4446300071,0,0]</t>
         </is>
       </c>
     </row>
@@ -15938,9 +15938,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E674" s="4" t="inlineStr">
-        <is>
-          <t>[0.5555555556,0,0.0101010101,0.0909090909,0,0,0.3434343434,0]</t>
+      <c r="F674" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3816857278,3.4351715498,0,0]</t>
         </is>
       </c>
     </row>
@@ -15961,9 +15961,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E675" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0.0202020202,0.0808080808,0,0.0101010101,0.2929292929,0]</t>
+      <c r="F675" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7479051857,2.9916207428,0,0.3739525928]</t>
         </is>
       </c>
     </row>
@@ -15984,9 +15984,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E676" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0202020202,0.0909090909,0,0.0808080808,0.1919191919,0]</t>
+      <c r="F676" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7119546692,3.2037960115,0,2.8478186769]</t>
         </is>
       </c>
     </row>
@@ -16007,9 +16007,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E677" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0.0303030303,0.1111111111,0.0808080808,0,0.0404040404,0.2626262626,0]</t>
+      <c r="F677" s="4" t="inlineStr">
+        <is>
+          <t>[1.1027155169,4.0432902287,2.9405747118,0,1.4702873559]</t>
         </is>
       </c>
     </row>
@@ -16030,9 +16030,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E678" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.1515151515,0.0909090909,0,0.1313131313,0.1313131313,0]</t>
+      <c r="F678" s="4" t="inlineStr">
+        <is>
+          <t>[0,5.3980723877,3.2388434326,0,4.6783294026]</t>
         </is>
       </c>
     </row>
@@ -16053,9 +16053,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E679" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0.0101010101,0,0.0707070707,0.0101010101,0.1414141414,0.303030303,0]</t>
+      <c r="F679" s="4" t="inlineStr">
+        <is>
+          <t>[0.3802943342,0,2.6620603393,0.3802943342,5.3241206785]</t>
         </is>
       </c>
     </row>
@@ -16076,9 +16076,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E680" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0.0101010101,0,0.0707070707,0.0101010101,0.4646464646,0,0]</t>
+      <c r="F680" s="4" t="inlineStr">
+        <is>
+          <t>[0.387754709,0,2.714282963,0.387754709,0]</t>
         </is>
       </c>
     </row>
@@ -16099,9 +16099,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E681" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0.0505050505,0,0.4444444444,0,0,0,0]</t>
+      <c r="F681" s="4" t="inlineStr">
+        <is>
+          <t>[1.750594194,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -16122,9 +16122,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E682" s="4" t="inlineStr">
-        <is>
-          <t>[0.5151515152,0,0,0.2929292929,0,0.1919191919,0,0]</t>
+      <c r="F682" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.6788531871,0,0]</t>
         </is>
       </c>
     </row>
@@ -16145,9 +16145,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E683" s="4" t="inlineStr">
-        <is>
-          <t>[0.5353535354,0,0,0.2424242424,0,0.0202020202,0.202020202,0]</t>
+      <c r="F683" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,8.6797330533,0,0.7233110878]</t>
         </is>
       </c>
     </row>
@@ -16168,9 +16168,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E684" s="4" t="inlineStr">
-        <is>
-          <t>[0.5454545455,0,0,0.2727272727,0,0.0101010101,0.1717171717,0]</t>
+      <c r="F684" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,9.7946445104,0,0.3627646115]</t>
         </is>
       </c>
     </row>
@@ -16191,9 +16191,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E685" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0,0.2727272727,0,0.0303030303,0.1919191919,0]</t>
+      <c r="F685" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,10.3066094105,0,1.1451788234]</t>
         </is>
       </c>
     </row>
@@ -16214,9 +16214,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E686" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0,0.3333333333,0,0.0101010101,0.1515151515,0]</t>
+      <c r="F686" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,12.0865623718,0,0.3662594658]</t>
         </is>
       </c>
     </row>
@@ -16237,9 +16237,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E687" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0,0,0.1212121212,0,0,0.1717171717,0]</t>
+      <c r="F687" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.6321601904,0,0]</t>
         </is>
       </c>
     </row>
@@ -16260,9 +16260,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E688" s="4" t="inlineStr">
-        <is>
-          <t>[0.7373737374,0,0.0101010101,0.0909090909,0,0,0.1616161616,0]</t>
+      <c r="F688" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3893893099,3.5045037895,0,0]</t>
         </is>
       </c>
     </row>
@@ -16283,9 +16283,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E689" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0,0.101010101,0,0.0303030303,0.1414141414,0]</t>
+      <c r="F689" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.784850094,0,1.1354550282]</t>
         </is>
       </c>
     </row>
@@ -16306,9 +16306,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E690" s="4" t="inlineStr">
-        <is>
-          <t>[0.6868686869,0,0,0.0909090909,0,0.0505050505,0.1717171717,0]</t>
+      <c r="F690" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5148200729,0,1.9526778183]</t>
         </is>
       </c>
     </row>
@@ -16329,9 +16329,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E691" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0,0.0909090909,0,0.0303030303,0.1818181818,0]</t>
+      <c r="F691" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5063368927,0,1.1687789642]</t>
         </is>
       </c>
     </row>
@@ -16352,9 +16352,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E692" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.8484848485,0,0.0101010101,0.1414141414,0]</t>
+      <c r="F692" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.3674778826]</t>
         </is>
       </c>
     </row>
@@ -16375,9 +16375,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E693" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6262626263,0,0.0101010101,0.3636363636,0]</t>
+      <c r="F693" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.4800995916]</t>
         </is>
       </c>
     </row>
@@ -16398,9 +16398,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E694" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0505050505,0.0606060606,0,0,0.4646464646,0]</t>
+      <c r="F694" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.9743796254,3.5692555504,0,0]</t>
         </is>
       </c>
     </row>
@@ -16421,9 +16421,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E695" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0101010101,0.0505050505,0,0.0202020202,0.5151515152,0]</t>
+      <c r="F695" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.6319711133,3.1598555663,0,1.2639422265]</t>
         </is>
       </c>
     </row>
@@ -16444,9 +16444,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E696" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0.0202020202,0.0606060606,0,0.0303030303,0.4444444444,0]</t>
+      <c r="F696" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1476723184,3.4430169551,0,1.7215084776]</t>
         </is>
       </c>
     </row>
@@ -16467,9 +16467,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E697" s="4" t="inlineStr">
-        <is>
-          <t>[0.404040404,0,0.0202020202,0.0606060606,0,0,0.5151515152,0]</t>
+      <c r="F697" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2543538324,3.7630614972,0,0]</t>
         </is>
       </c>
     </row>
@@ -16490,9 +16490,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E698" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0202020202,0.0606060606,0,0.0101010101,0.4848484848,0]</t>
+      <c r="F698" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2298690749,3.6896072246,0,0.6149345374]</t>
         </is>
       </c>
     </row>
@@ -16513,9 +16513,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E699" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0,0.0505050505,0,0.0101010101,0.5151515152,0]</t>
+      <c r="F699" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0645745106,0,0.6129149021]</t>
         </is>
       </c>
     </row>
@@ -16536,9 +16536,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E700" s="4" t="inlineStr">
-        <is>
-          <t>[0.4343434343,0.0101010101,0.0101010101,0.0606060606,0,0.0202020202,0.4646464646,0]</t>
+      <c r="F700" s="4" t="inlineStr">
+        <is>
+          <t>[0.6042000992,0.6042000992,3.6252005955,0,1.2084001985]</t>
         </is>
       </c>
     </row>
@@ -16559,9 +16559,9 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="E701" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0,0.0606060606,0.0101010101,0.0202020202,0.4545454545,0]</t>
+      <c r="F701" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.5658952007,0.5943158668,1.1886317336]</t>
         </is>
       </c>
     </row>
@@ -16582,9 +16582,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E702" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0,0.0707070707,0,0,0.4646464646,0]</t>
+      <c r="F702" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.0198897375,0,0]</t>
         </is>
       </c>
     </row>
@@ -16605,9 +16605,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E703" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0,0.1111111111,0,0.4343434343,0,0]</t>
+      <c r="F703" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.4489067856,0,0]</t>
         </is>
       </c>
     </row>
@@ -16628,9 +16628,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E704" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.0707070707,0,0.4444444444,0,0]</t>
+      <c r="F704" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.248229413,0,0]</t>
         </is>
       </c>
     </row>
@@ -16651,9 +16651,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E705" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.1111111111,0,0.0202020202,0.3939393939,0]</t>
+      <c r="F705" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.5084800581,0,1.1833600106]</t>
         </is>
       </c>
     </row>
@@ -16674,9 +16674,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E706" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0,0.0808080808,0,0,0.4343434343,0]</t>
+      <c r="F706" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.6914557182,0,0]</t>
         </is>
       </c>
     </row>
@@ -16697,9 +16697,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E707" s="4" t="inlineStr">
-        <is>
-          <t>[0.4747474747,0,0,0.101010101,0,0.0101010101,0.4141414141,0]</t>
+      <c r="F707" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.9208182294,0,0.5920818229]</t>
         </is>
       </c>
     </row>
@@ -16720,9 +16720,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E708" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0101010101,0.0606060606,0,0.0202020202,0.4444444444,0]</t>
+      <c r="F708" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.6193094483,3.7158566901,0,1.2386188967]</t>
         </is>
       </c>
     </row>
@@ -16743,9 +16743,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E709" s="4" t="inlineStr">
-        <is>
-          <t>[0.4646464646,0,0.0101010101,0.0606060606,0,0.0101010101,0.4545454545,0]</t>
+      <c r="F709" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.607562087,3.6453725218,0,0.607562087]</t>
         </is>
       </c>
     </row>
@@ -16766,9 +16766,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E710" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0,0.0808080808,0,0,0.4646464646,0]</t>
+      <c r="F710" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.3430707412,0,0]</t>
         </is>
       </c>
     </row>
@@ -16789,9 +16789,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E711" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0,0,0.101010101,0,0.0202020202,0.5151515152,0]</t>
+      <c r="F711" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.7983704907,0,0.9596740981]</t>
         </is>
       </c>
     </row>
@@ -16812,9 +16812,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E712" s="4" t="inlineStr">
-        <is>
-          <t>[0.3939393939,0,0,0.101010101,0,0.0303030303,0.4747474747,0]</t>
+      <c r="F712" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,4.6418997853,0,1.3925699356]</t>
         </is>
       </c>
     </row>
@@ -16835,9 +16835,9 @@
           <t>DC</t>
         </is>
       </c>
-      <c r="E713" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.5050505051,0.0404040404,0,0.4545454545,0]</t>
+      <c r="F713" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,1.9841169967,0]</t>
         </is>
       </c>
     </row>
@@ -16858,9 +16858,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E714" s="4" t="inlineStr">
-        <is>
-          <t>[0.3636363636,0,0,0.1717171717,0,0,0.4646464646,0]</t>
+      <c r="F714" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,6.5959303468,0,0]</t>
         </is>
       </c>
     </row>
@@ -16881,9 +16881,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E715" s="4" t="inlineStr">
-        <is>
-          <t>[0.5050505051,0,0.0202020202,0.0707070707,0,0.0202020202,0.3838383838,0]</t>
+      <c r="F715" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.1680231194,4.0880809179,0,1.1680231194]</t>
         </is>
       </c>
     </row>
@@ -16904,9 +16904,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E716" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.5454545455,0,0.0404040404,0.4141414141,0]</t>
+      <c r="F716" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,2.3241878995]</t>
         </is>
       </c>
     </row>
@@ -16927,9 +16927,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E717" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0,0.0202020202,0.0606060606,0,0.0404040404,0.4343434343,0]</t>
+      <c r="F717" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.2014864559,3.6044593676,0,2.4029729117]</t>
         </is>
       </c>
     </row>
@@ -16950,9 +16950,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E718" s="4" t="inlineStr">
-        <is>
-          <t>[0.5858585859,0,0.0707070707,0.0808080808,0,0.0202020202,0.2424242424,0]</t>
+      <c r="F718" s="4" t="inlineStr">
+        <is>
+          <t>[0,3.1699819206,3.6228364807,0,0.9057091202]</t>
         </is>
       </c>
     </row>
@@ -16973,9 +16973,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E719" s="4" t="inlineStr">
-        <is>
-          <t>[0.6565656566,0,0.0707070707,0.0909090909,0,0.0505050505,0.1313131313,0]</t>
+      <c r="F719" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.8590453683,3.6759154736,0,2.0421752631]</t>
         </is>
       </c>
     </row>
@@ -16996,9 +16996,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E720" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0404040404,0.0909090909,0,0.0101010101,0.1818181818,0]</t>
+      <c r="F720" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.5583829403,3.5063616156,0,0.3895957351]</t>
         </is>
       </c>
     </row>
@@ -17019,9 +17019,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E721" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0.0202020202,0.0909090909,0,0.0707070707,0.1212121212,0]</t>
+      <c r="F721" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7467988857,3.3605949856,0,2.6137960999]</t>
         </is>
       </c>
     </row>
@@ -17042,9 +17042,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E722" s="4" t="inlineStr">
-        <is>
-          <t>[0.7272727273,0,0.0101010101,0.101010101,0,0.0606060606,0.101010101,0]</t>
+      <c r="F722" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3544688934,3.5446889344,0,2.1268133606]</t>
         </is>
       </c>
     </row>
@@ -17065,9 +17065,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E723" s="4" t="inlineStr">
-        <is>
-          <t>[0.6767676768,0,0.0101010101,0.0909090909,0,0.0606060606,0.1616161616,0]</t>
+      <c r="F723" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.401298402,3.6116856177,0,2.4077904118]</t>
         </is>
       </c>
     </row>
@@ -17088,9 +17088,9 @@
           <t>DD</t>
         </is>
       </c>
-      <c r="E724" s="4" t="inlineStr">
-        <is>
-          <t>[0.696969697,0,0.0101010101,0.0909090909,0,0.1515151515,0.0505050505,0]</t>
+      <c r="F724" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3714598891,3.3431390018,0,5.5718983364]</t>
         </is>
       </c>
     </row>
@@ -17111,9 +17111,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E725" s="4" t="inlineStr">
-        <is>
-          <t>[0.6666666667,0,0,0.1313131313,0,0,0.202020202,0]</t>
+      <c r="F725" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,5.0442970679,0,0]</t>
         </is>
       </c>
     </row>
@@ -17134,9 +17134,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E726" s="4" t="inlineStr">
-        <is>
-          <t>[0.7171717172,0,0,0.2828282828,0,0,0,0]</t>
+      <c r="F726" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -17157,9 +17157,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E727" s="4" t="inlineStr">
-        <is>
-          <t>[0.7070707071,0,0,0.2929292929,0,0,0,0]</t>
+      <c r="F727" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -17180,9 +17180,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E728" s="4" t="inlineStr">
-        <is>
-          <t>[0.4444444444,0.0707070707,0,0.4848484848,0,0,0,0]</t>
+      <c r="F728" s="4" t="inlineStr">
+        <is>
+          <t>[2.9378928627,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -17203,9 +17203,9 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="E729" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0.1414141414,0,0.404040404,0,0,0,0]</t>
+      <c r="F729" s="4" t="inlineStr">
+        <is>
+          <t>[5.3896988343,0,0,0,0]</t>
         </is>
       </c>
     </row>
@@ -17226,9 +17226,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E730" s="4" t="inlineStr">
-        <is>
-          <t>[0.6060606061,0,0.0101010101,0.0909090909,0,0.2929292929,0,0]</t>
+      <c r="F730" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3754315522,3.37888397,0,0]</t>
         </is>
       </c>
     </row>
@@ -17249,9 +17249,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E731" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0101010101,0.0909090909,0,0,0.2828282828,0]</t>
+      <c r="F731" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3896853843,3.5071684586,0,0]</t>
         </is>
       </c>
     </row>
@@ -17272,9 +17272,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E732" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0202020202,0.0808080808,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F732" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.7587090618,3.0348362474,0,0.3793545309]</t>
         </is>
       </c>
     </row>
@@ -17295,9 +17295,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E733" s="4" t="inlineStr">
-        <is>
-          <t>[0.6363636364,0,0.0101010101,0.0808080808,0,0.0101010101,0.2626262626,0]</t>
+      <c r="F733" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3794137796,3.0353102368,0,0.3794137796]</t>
         </is>
       </c>
     </row>
@@ -17318,9 +17318,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E734" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0,0.0808080808,0,0.0101010101,0.2929292929,0]</t>
+      <c r="F734" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.0867585918,0,0.385844824]</t>
         </is>
       </c>
     </row>
@@ -17341,9 +17341,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E735" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0101010101,0.0909090909,0,0,0.2727272727,0]</t>
+      <c r="F735" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3709422633,3.3384803698,0,0]</t>
         </is>
       </c>
     </row>
@@ -17364,9 +17364,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E736" s="4" t="inlineStr">
-        <is>
-          <t>[0.6262626263,0,0.0101010101,0.0909090909,0,0,0.2727272727,0]</t>
+      <c r="F736" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3734578935,3.3611210412,0,0]</t>
         </is>
       </c>
     </row>
@@ -17387,9 +17387,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E737" s="4" t="inlineStr">
-        <is>
-          <t>[0.595959596,0,0.0404040404,0.0808080808,0,0,0.2828282828,0]</t>
+      <c r="F737" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.558045563,3.116091126,0,0]</t>
         </is>
       </c>
     </row>
@@ -17410,9 +17410,9 @@
           <t>MC</t>
         </is>
       </c>
-      <c r="E738" s="4" t="inlineStr">
-        <is>
-          <t>[0.6161616162,0,0.0101010101,0.0808080808,0,0.0101010101,0.2828282828,0]</t>
+      <c r="F738" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3873686031,3.0989488247,0,0.3873686031]</t>
         </is>
       </c>
     </row>
@@ -17433,9 +17433,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E739" s="4" t="inlineStr">
-        <is>
-          <t>[0,0,0,0.6161616162,0,0.0101010101,0.3737373737,0]</t>
+      <c r="F739" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,0,0,0.2801517751]</t>
         </is>
       </c>
     </row>
@@ -17456,9 +17456,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E740" s="4" t="inlineStr">
-        <is>
-          <t>[0.4242424242,0,0.0606060606,0.101010101,0,0.0202020202,0.3939393939,0]</t>
+      <c r="F740" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.8109171578,3.0181952631,0,0.6036390526]</t>
         </is>
       </c>
     </row>
@@ -17479,9 +17479,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E741" s="4" t="inlineStr">
-        <is>
-          <t>[0.5252525253,0,0,0.1212121212,0,0,0.3535353535,0]</t>
+      <c r="F741" s="4" t="inlineStr">
+        <is>
+          <t>[0,0,3.3314357959,0,0]</t>
         </is>
       </c>
     </row>
@@ -17502,9 +17502,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E742" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0101010101,0.1111111111,0,0,0.3838383838,0]</t>
+      <c r="F742" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.3020299046,3.3223289502,0,0]</t>
         </is>
       </c>
     </row>
@@ -17525,9 +17525,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E743" s="4" t="inlineStr">
-        <is>
-          <t>[0.4545454545,0,0.0505050505,0.1212121212,0,0.0101010101,0.3636363636,0]</t>
+      <c r="F743" s="4" t="inlineStr">
+        <is>
+          <t>[0,1.3228957833,3.1749498798,0,0.2645791567]</t>
         </is>
       </c>
     </row>
@@ -17548,9 +17548,9 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E744" s="4" t="inlineStr">
-        <is>
-          <t>[0.4848484848,0,0.0808080808,0.1111111111,0,0.0303030303,0.2929292929,0]</t>
+      <c r="F744" s="4" t="inlineStr">
+        <is>
+          <t>[0,2.1923359417,3.0144619198,0,0.8221259781]</t>
         </is>
       </c>
     </row>
@@ -17571,9 +17571,9 @@
           <t>NU</t>
         </is>
       </c>
-      <c r="E745" s="4" t="inlineStr">
-        <is>
-          <t>[0.4949494949,0,0.0101010101,0.1111111111,0,0,0.3838383838,0]</t>
+      <c r="F745" s="4" t="inlineStr">
+        <is>
+          <t>[0,0.297199419,3.2691936089,0,0]</t>
         </is>
       </c>
     </row>

--- a/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
+++ b/Figure_Plot/figure_plot_4_a_b/source_data/dsfunction_May2025_exact_V5_k20_classified.xlsx
@@ -15988,7 +15988,7 @@
       </c>
       <c r="F598" s="4" t="inlineStr">
         <is>
-          <t>[0,16.6315309082,1.750687464,0,1.313015598]</t>
+          <t>[0,0,1.750687464,0,1.313015598]</t>
         </is>
       </c>
     </row>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="F599" s="4" t="inlineStr">
         <is>
-          <t>[0,16.7827991083,1.3607674953,0,1.8143566604]</t>
+          <t>[0,0,1.3607674953,0,1.8143566604]</t>
         </is>
       </c>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="F600" s="4" t="inlineStr">
         <is>
-          <t>[0,17.8011135412,1.3693164262,0,1.825755235]</t>
+          <t>[0,0,1.3693164262,0,1.825755235]</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="F601" s="4" t="inlineStr">
         <is>
-          <t>[0,16.8011129209,1.4400953932,0,1.4400953932]</t>
+          <t>[0,0,1.4400953932,0,1.4400953932]</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="F602" s="4" t="inlineStr">
         <is>
-          <t>[0,17.0457152914,1.4204762743,0,1.8939683657]</t>
+          <t>[0,0,1.4204762743,0,1.8939683657]</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="F603" s="4" t="inlineStr">
         <is>
-          <t>[0,16.8625319601,1.4453598823,0,1.4453598823]</t>
+          <t>[0,0,1.4453598823,0,1.4453598823]</t>
         </is>
       </c>
     </row>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="F604" s="4" t="inlineStr">
         <is>
-          <t>[0,16.9755098227,1.4146258186,0,1.4146258186]</t>
+          <t>[0,0,1.4146258186,0,1.4146258186]</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="D605" s="4" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="E605" t="n">
@@ -16170,7 +16170,7 @@
       </c>
       <c r="F605" s="4" t="inlineStr">
         <is>
-          <t>[0,20.4297334611,1.9456889011,0,0]</t>
+          <t>[0,0,1.9456889011,0,0]</t>
         </is>
       </c>
     </row>
